--- a/2026/ITALIA/Agosto/Agosto ITALIA.xlsx
+++ b/2026/ITALIA/Agosto/Agosto ITALIA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\ITALIA\Agosto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\ITALIA\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAE10A59-633E-4D67-8B66-951B30FCAD8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57DDDAA1-0C6E-4756-BC02-0D7F964C585F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="4" r:id="rId1"/>
@@ -19,14 +19,19 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$O$127</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$147</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$149</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="279">
   <si>
     <t>TOTAL</t>
   </si>
@@ -662,12 +667,6 @@
     <t xml:space="preserve">Fernando daniel Minxxo  / Osvaldo </t>
   </si>
   <si>
-    <t>Cuello Natalia - Desobstruccion lavadero 9C</t>
-  </si>
-  <si>
-    <t>Cuello Natalia - Desobstruccion lavadero 9D</t>
-  </si>
-  <si>
     <t>Efectivo</t>
   </si>
   <si>
@@ -692,28 +691,149 @@
     <t>EN PROCESO DE EJECUCION</t>
   </si>
   <si>
-    <t>InOut Control - Comando control y camaras - JULIO</t>
-  </si>
-  <si>
-    <t>Casa ruan - Compra de materiales</t>
-  </si>
-  <si>
-    <t>Transf 13/07</t>
-  </si>
-  <si>
-    <t>Cuello Natalia - Desobstruccion lavadero 11A</t>
-  </si>
-  <si>
-    <t>Transf 23/07</t>
-  </si>
-  <si>
-    <t>Transf 06/07</t>
-  </si>
-  <si>
-    <t>Debito 13/07</t>
-  </si>
-  <si>
-    <t>Correo Argentino - Envio 2 cartas documentos - Edificio lindero : situacion raices de arbol</t>
+    <t>En Juli0 2026 suben a $781.000</t>
+  </si>
+  <si>
+    <t>Gastos bancarios - Santander</t>
+  </si>
+  <si>
+    <t>Mantenimiento de cuenta - Banco Credicop + Gastos bancarios</t>
+  </si>
+  <si>
+    <t>ARCA - Plan de pago - Cuota 46/60</t>
+  </si>
+  <si>
+    <t>Daniela Dominguez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El en les de Julio abono la 4ta cuota de 7 </t>
+  </si>
+  <si>
+    <t>Deposito ya identificado mes anterior</t>
+  </si>
+  <si>
+    <t>Punitorios mal cobrados</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En julio abona la 4ta cuota de 10 - Consta de 10 Cuotas de $165.000 + expensas en curso </t>
+  </si>
+  <si>
+    <t xml:space="preserve">En julio abona la 4ta cuota de 24 - Consta de 24 cuotas de $33.000 + expensas en curso </t>
+  </si>
+  <si>
+    <t>En julio abono la cuota 7 de 24</t>
+  </si>
+  <si>
+    <t>AYSA</t>
+  </si>
+  <si>
+    <t>AYSA:</t>
+  </si>
+  <si>
+    <t>10A</t>
+  </si>
+  <si>
+    <t>10 A deposito $285.000 06/08 o 07/08</t>
+  </si>
+  <si>
+    <t>adabeleo19@gmail.com agregar a la cadena de mail</t>
+  </si>
+  <si>
+    <t>19 y Cochera con 00 centavos</t>
+  </si>
+  <si>
+    <t>10B</t>
+  </si>
+  <si>
+    <t>Transfirio $50.400 el 12/08 para sus extraordinarias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inicia un plan de pagos en donde abona $140.000 en el mes de julio - Y ademas consta de 9 cuotas de $130.000 </t>
+  </si>
+  <si>
+    <t>Inicia un plan de pagos en donde abona $140.000 en el mes de julio - Y ademas consta de 9 cuotas de $130.000 - Mes de agosto arranca debiendo abonar: $365.200,74</t>
+  </si>
+  <si>
+    <t>En la UF 19 viene figurando que tiene "dinero a favor pagando de mas" - Ese dinero a favor es en teoria para la cochera 100 - En Junio pago $33.780 de mas y en Julio pago $33.780 de mas tambien - De cochera debe abonar $6.236 y de UF (19) debe abonar $280.493,19 - 12043 de punitorios = $268.450,19 - Abonan el 14/08 creo un poco menos de lo que debian abonar : lo informan x mail</t>
+  </si>
+  <si>
+    <t>9d</t>
+  </si>
+  <si>
+    <t>Lucas Calviño 9D: Dice que tiene un deposito en el mes pasado por $320.000 sin identificar y este mes transfirió $172.200,65 - Queda con un saldo restante a abonar de 244.922</t>
+  </si>
+  <si>
+    <t>6f</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Angelica 6F: Transfirió $220.000 el 21/08
+</t>
+  </si>
+  <si>
+    <t>Mama me dijo que hay que revisar a un tal Rajmilevich</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t>VTO 17/09</t>
+  </si>
+  <si>
+    <t>PERÍODO: AGOSTO</t>
+  </si>
+  <si>
+    <t>InOut Control - Comando control y camaras - AGOSTO</t>
+  </si>
+  <si>
+    <t>Honorarios administracion - Se adeuda mes de AGOSTO</t>
+  </si>
+  <si>
+    <t>Gustavo Padron -  Sr. Contador - AGOSTO</t>
+  </si>
+  <si>
+    <t>Matafuegos FIRE - Bota neora s/ puntera OMBU</t>
+  </si>
+  <si>
+    <t>Roxana Goldemberg - Convenio pago 5E</t>
+  </si>
+  <si>
+    <t>Transf 21/08</t>
+  </si>
+  <si>
+    <t>Cuello Natalia - Desobstruccion emergencia de columna en cocina 4C</t>
+  </si>
+  <si>
+    <t>Cuello Natalia - Desobstruccion emergencia de columna en cocina 1B</t>
+  </si>
+  <si>
+    <t>Transf 13/08</t>
+  </si>
+  <si>
+    <t>Tramsf 12/08</t>
+  </si>
+  <si>
+    <t>Reparacion de llave de paso de gas en cocina - Desarme y lubircacion con grafito en la llave de paso por falta de lubricacion</t>
+  </si>
+  <si>
+    <t>Servisur - retiro de 29 luces de emergencia y reemplazo de las mismas</t>
+  </si>
+  <si>
+    <t>Transf 10/08</t>
+  </si>
+  <si>
+    <t>Suarez Agustin Ignacio - AGOSTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Galvan Zaffalon - Instalacion y puesta en marcha de bomba chupadora de calle e instalacion de cañeria con by pass </t>
+  </si>
+  <si>
+    <t>Transf 06/08</t>
+  </si>
+  <si>
+    <t>Debito 12/08</t>
+  </si>
+  <si>
+    <t>Transf 18/08</t>
   </si>
   <si>
     <r>
@@ -728,7 +848,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> A cuenta</t>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -738,195 +858,50 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> de trabajo de plomeria, albañileria y pintura - 8vo B cambio de desague cocina y lavadero - 8vo f cambio de desague de cocina, lavadero y albañileria - 8vo E cambio de desague de cocina, lavadero y albañileria - 6to c cambio de desague de cocina, lavadero y albañileria + llave de paso - 7mo C cambio de desague de cocina, lavadero y albañileria - 3ro D cambio de desague de cocina, lavadero y albañileria + cambio de cañeria agua fria cocina y lavadero + llaves de paso - 3ro C cambio de desague de cocina, lavadero + Cambio de cañeria agua fria y caliente cocina y lavadero + llaves de paso - 4to D cambio de llaves de paso agua fria y caliente - 1ro C reparacion de llave de paso</t>
+      <t xml:space="preserve"> Trabajo de plomeria, albañileria y pintura - 8vo B cambio de desague cocina y lavadero - 8vo f cambio de desague de cocina, lavadero y albañileria - 8vo E cambio de desague de cocina, lavadero y albañileria - 6to c cambio de desague de cocina, lavadero y albañileria + llave de paso - 7mo C cambio de desague de cocina, lavadero y albañileria - 3ro D cambio de desague de cocina, lavadero y albañileria + cambio de cañeria agua fria cocina y lavadero + llaves de paso - 3ro C cambio de desague de cocina, lavadero + Cambio de cañeria agua fria y caliente cocina y lavadero + llaves de paso - 4to D cambio de llaves de paso agua fria y caliente - 1ro C reparacion de llave de paso - Resta abonar $10.000.000</t>
     </r>
   </si>
   <si>
-    <t>En Juli0 2026 suben a $781.000</t>
-  </si>
-  <si>
-    <t>Grafica Tauge - Fotocopias BYN</t>
-  </si>
-  <si>
-    <t>Galvan Zaffalon - Compra de materiales para modificacion de cañeria entrada de agua con By pass</t>
-  </si>
-  <si>
-    <t>Transf 14/7</t>
-  </si>
-  <si>
-    <t>Suplencia Sra. Silvana</t>
-  </si>
-  <si>
-    <t>Feriado</t>
-  </si>
-  <si>
-    <t>Transf 15/07</t>
-  </si>
-  <si>
-    <t>Seguro Sra. Silvana</t>
-  </si>
-  <si>
-    <t>Transf 16/07</t>
-  </si>
-  <si>
-    <t>Romnatti carlos - Digitalizacion de reglamento entregado por el gestor</t>
-  </si>
-  <si>
-    <t>Transf 30/07</t>
-  </si>
-  <si>
-    <t>Ascensores Lema - Pago material placa ascensores</t>
-  </si>
-  <si>
-    <t>Gastos bancarios - Santander</t>
-  </si>
-  <si>
-    <t>Mantenimiento de cuenta - Banco Credicop + Gastos bancarios</t>
-  </si>
-  <si>
-    <t>ARCA - Plan de pago - Cuota 46/60</t>
-  </si>
-  <si>
-    <t>ARCA VEP - No se abona (explicacion en el cuerpo de expensas)</t>
-  </si>
-  <si>
-    <t>Maria Lorenzo - Transferencia 07/07</t>
-  </si>
-  <si>
-    <t>Daniela Dominguez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El en les de Julio abono la 4ta cuota de 7 </t>
-  </si>
-  <si>
-    <t>Cedeno Yormelyth - Transferencia 10/07</t>
-  </si>
-  <si>
-    <t>Scarpato Gabriela - Transferencia 12/07</t>
-  </si>
-  <si>
-    <t>Deposito ya identificado mes anterior</t>
-  </si>
-  <si>
-    <t>Punitorios mal cobrados</t>
-  </si>
-  <si>
-    <t xml:space="preserve">En julio abona la 4ta cuota de 10 - Consta de 10 Cuotas de $165.000 + expensas en curso </t>
-  </si>
-  <si>
-    <t xml:space="preserve">En julio abona la 4ta cuota de 24 - Consta de 24 cuotas de $33.000 + expensas en curso </t>
-  </si>
-  <si>
-    <t>En julio abono la cuota 7 de 24</t>
-  </si>
-  <si>
-    <t>AYSA</t>
-  </si>
-  <si>
-    <t>AYSA:</t>
-  </si>
-  <si>
-    <t>10A</t>
-  </si>
-  <si>
-    <t>10 A deposito $285.000 06/08 o 07/08</t>
-  </si>
-  <si>
-    <t>adabeleo19@gmail.com agregar a la cadena de mail</t>
-  </si>
-  <si>
-    <t>19 y Cochera con 00 centavos</t>
-  </si>
-  <si>
-    <t>10B</t>
-  </si>
-  <si>
-    <t>Transfirio $50.400 el 12/08 para sus extraordinarias</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inicia un plan de pagos en donde abona $140.000 en el mes de julio - Y ademas consta de 9 cuotas de $130.000 </t>
-  </si>
-  <si>
-    <t>Inicia un plan de pagos en donde abona $140.000 en el mes de julio - Y ademas consta de 9 cuotas de $130.000 - Mes de agosto arranca debiendo abonar: $365.200,74</t>
-  </si>
-  <si>
-    <t>En la UF 19 viene figurando que tiene "dinero a favor pagando de mas" - Ese dinero a favor es en teoria para la cochera 100 - En Junio pago $33.780 de mas y en Julio pago $33.780 de mas tambien - De cochera debe abonar $6.236 y de UF (19) debe abonar $280.493,19 - 12043 de punitorios = $268.450,19 - Abonan el 14/08 creo un poco menos de lo que debian abonar : lo informan x mail</t>
-  </si>
-  <si>
-    <t>9d</t>
-  </si>
-  <si>
-    <t>Lucas Calviño 9D: Dice que tiene un deposito en el mes pasado por $320.000 sin identificar y este mes transfirió $172.200,65 - Queda con un saldo restante a abonar de 244.922</t>
-  </si>
-  <si>
-    <t>6f</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Angelica 6F: Transfirió $220.000 el 21/08
-</t>
-  </si>
-  <si>
-    <t>Mama me dijo que hay que revisar a un tal Rajmilevich</t>
-  </si>
-  <si>
-    <t>?</t>
-  </si>
-  <si>
-    <t>VTO 17/09</t>
-  </si>
-  <si>
-    <t>PERÍODO: AGOSTO</t>
-  </si>
-  <si>
-    <t>InOut Control - Comando control y camaras - AGOSTO</t>
-  </si>
-  <si>
-    <t>Honorarios administracion - Se adeuda mes de AGOSTO</t>
-  </si>
-  <si>
-    <t>Gustavo Padron -  Sr. Contador - AGOSTO</t>
-  </si>
-  <si>
-    <t>Matafuegos FIRE - Bota neora s/ puntera OMBU</t>
-  </si>
-  <si>
-    <t>Roxana Goldemberg - Convenio pago 5E</t>
-  </si>
-  <si>
-    <t>Transf 21/08</t>
-  </si>
-  <si>
-    <t>Envio carta documento</t>
-  </si>
-  <si>
-    <t>Cuello Natalia - Desobstruccion emergencia de columna en cocina 4C</t>
-  </si>
-  <si>
-    <t>Transf 17/08</t>
-  </si>
-  <si>
-    <t>Cuello Natalia - Desobstruccion emergencia de columna en cocina 1B</t>
-  </si>
-  <si>
-    <t>Transf 13/08</t>
-  </si>
-  <si>
-    <t>Tramsf 12/08</t>
-  </si>
-  <si>
-    <t>Reparacion de llave de paso de gas en cocina - Desarme y lubircacion con grafito en la llave de paso por falta de lubricacion</t>
-  </si>
-  <si>
-    <t>Servisur - retiro de 29 luces de emergencia y reemplazo de las mismas</t>
-  </si>
-  <si>
-    <t>Transf 10/08</t>
-  </si>
-  <si>
-    <t>Suarez Agustin Ignacio - AGOSTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Galvan Zaffalon - Instalacion y puesta en marcha de bomba chupadora de calle e instalacion de cañeria con by pass </t>
+    <t>Abono ascensor - Lema Ascensores - Mano de obra colocacion plaqueta</t>
+  </si>
+  <si>
+    <t>Transf 19/08</t>
+  </si>
+  <si>
+    <t>Transf 26/08</t>
+  </si>
+  <si>
+    <t>ARCA VEP - Mes 6</t>
+  </si>
+  <si>
+    <t>ARCA VEP - Mes 7</t>
+  </si>
+  <si>
+    <t>Transf 28/08</t>
+  </si>
+  <si>
+    <t>Correo argentino - Envio cartas documento (4) - Contestacion 1B -  2B - Administracion "La vecindad" y Edificio lindero por medianera</t>
+  </si>
+  <si>
+    <t>Firma escribania Bayeto - Comodato porteria</t>
+  </si>
+  <si>
+    <t>Transf 31/08</t>
+  </si>
+  <si>
+    <t>Plan de pago 5E: Consta de 6 cuotas mensuales de $190.000 + expensas en curso</t>
+  </si>
+  <si>
+    <t>Plan de pago 10F: Cosnsta de 9 cuotas mensuales de $130.000 + expensas en curso</t>
+  </si>
+  <si>
+    <t>Roxana Goldemberg - Convenio pago 10F</t>
+  </si>
+  <si>
+    <t>1450000 en cada UF</t>
+  </si>
+  <si>
+    <t>Alexis Florentino</t>
   </si>
 </sst>
 </file>
@@ -1748,7 +1723,7 @@
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="338">
+  <cellXfs count="339">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2106,14 +2081,6 @@
     <xf numFmtId="167" fontId="16" fillId="11" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="17" fillId="11" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="17" fillId="11" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="10" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="8" fontId="10" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="8" fontId="10" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="44" fontId="10" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2159,62 +2126,152 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="14" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="10" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="10" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="10" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="10" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2222,12 +2279,6 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2258,84 +2309,6 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2357,14 +2330,17 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="18" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="7" fillId="14" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="8" fontId="7" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="7" fillId="14" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="14" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="8" fontId="7" fillId="14" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="14" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="7" fillId="14" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="14" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="22" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="3" builtinId="8"/>
@@ -2451,9 +2427,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2491,9 +2467,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2526,9 +2502,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2561,9 +2554,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2737,32 +2747,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E413A25D-5161-4141-BE0B-6E37A2A76CA5}">
-  <dimension ref="A1:M148"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M150"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" customWidth="1"/>
-    <col min="6" max="6" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.33203125" customWidth="1"/>
+    <col min="10" max="10" width="16.28515625" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
-      <c r="B1" s="270" t="s">
+      <c r="B1" s="275" t="s">
         <v>146</v>
       </c>
-      <c r="C1" s="270"/>
-      <c r="D1" s="270"/>
-      <c r="E1" s="271"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C1" s="275"/>
+      <c r="D1" s="275"/>
+      <c r="E1" s="276"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="9" t="s">
         <v>148</v>
@@ -2771,16 +2781,16 @@
       <c r="D2" s="3"/>
       <c r="E2" s="4"/>
     </row>
-    <row r="3" spans="1:5" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
-      <c r="B3" s="276" t="s">
+      <c r="B3" s="279" t="s">
         <v>188</v>
       </c>
-      <c r="C3" s="276"/>
-      <c r="D3" s="276"/>
-      <c r="E3" s="277"/>
-    </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="279"/>
+      <c r="D3" s="279"/>
+      <c r="E3" s="280"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>100</v>
       </c>
@@ -2791,12 +2801,12 @@
       <c r="D4" s="7"/>
       <c r="E4" s="8"/>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>147</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>271</v>
+        <v>245</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="3" t="s">
@@ -2804,7 +2814,7 @@
       </c>
       <c r="E5" s="10"/>
     </row>
-    <row r="6" spans="1:5" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="90" t="s">
         <v>137</v>
       </c>
@@ -2815,95 +2825,95 @@
       </c>
       <c r="E6" s="8"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="48"/>
-      <c r="B8" s="278" t="s">
-        <v>270</v>
-      </c>
-      <c r="C8" s="278"/>
+      <c r="B8" s="281" t="s">
+        <v>244</v>
+      </c>
+      <c r="C8" s="281"/>
       <c r="D8" s="48"/>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="48"/>
-      <c r="B9" s="278"/>
-      <c r="C9" s="278"/>
+      <c r="B9" s="281"/>
+      <c r="C9" s="281"/>
       <c r="D9" s="48"/>
       <c r="E9" s="48"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="48"/>
-      <c r="B10" s="278"/>
-      <c r="C10" s="278"/>
+      <c r="B10" s="281"/>
+      <c r="C10" s="281"/>
       <c r="D10" s="48"/>
       <c r="E10" s="48"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="48"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
       <c r="E11" s="48"/>
     </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="48"/>
       <c r="B12" s="48"/>
       <c r="C12" s="48"/>
       <c r="D12" s="48"/>
       <c r="E12" s="48"/>
     </row>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="279" t="s">
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="282" t="s">
         <v>103</v>
       </c>
-      <c r="B13" s="279"/>
-      <c r="C13" s="279"/>
-      <c r="D13" s="279"/>
-      <c r="E13" s="279"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="279"/>
-      <c r="B14" s="279"/>
-      <c r="C14" s="279"/>
-      <c r="D14" s="279"/>
-      <c r="E14" s="279"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="279"/>
-      <c r="B15" s="279"/>
-      <c r="C15" s="279"/>
-      <c r="D15" s="279"/>
-      <c r="E15" s="279"/>
-    </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="279"/>
-      <c r="B16" s="279"/>
-      <c r="C16" s="279"/>
-      <c r="D16" s="279"/>
-      <c r="E16" s="279"/>
-    </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="282"/>
+      <c r="C13" s="282"/>
+      <c r="D13" s="282"/>
+      <c r="E13" s="282"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="282"/>
+      <c r="B14" s="282"/>
+      <c r="C14" s="282"/>
+      <c r="D14" s="282"/>
+      <c r="E14" s="282"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="282"/>
+      <c r="B15" s="282"/>
+      <c r="C15" s="282"/>
+      <c r="D15" s="282"/>
+      <c r="E15" s="282"/>
+    </row>
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="282"/>
+      <c r="B16" s="282"/>
+      <c r="C16" s="282"/>
+      <c r="D16" s="282"/>
+      <c r="E16" s="282"/>
+    </row>
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="48"/>
       <c r="B17" s="48"/>
       <c r="C17" s="48"/>
       <c r="D17" s="48"/>
       <c r="E17" s="48"/>
     </row>
-    <row r="18" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="177"/>
       <c r="B18" s="48"/>
       <c r="C18" s="48"/>
       <c r="D18" s="48"/>
       <c r="E18" s="48"/>
     </row>
-    <row r="19" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="48"/>
       <c r="B19" s="48"/>
       <c r="C19" s="48"/>
       <c r="D19" s="48"/>
       <c r="E19" s="48"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="178" t="s">
         <v>104</v>
       </c>
@@ -2912,7 +2922,7 @@
       <c r="D20" s="58"/>
       <c r="E20" s="59"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="36" t="s">
         <v>138</v>
       </c>
@@ -2921,35 +2931,35 @@
       <c r="D21" s="117"/>
       <c r="E21" s="151"/>
     </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="272" t="s">
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="277" t="s">
         <v>161</v>
       </c>
-      <c r="B22" s="273"/>
+      <c r="B22" s="278"/>
       <c r="C22" s="181"/>
       <c r="D22" s="182">
-        <v>2337709.7000000002</v>
+        <v>2415207.52</v>
       </c>
       <c r="E22" s="152"/>
       <c r="H22" s="19"/>
     </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="272" t="s">
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="277" t="s">
         <v>162</v>
       </c>
-      <c r="B23" s="273"/>
+      <c r="B23" s="278"/>
       <c r="C23" s="181"/>
       <c r="D23" s="182">
-        <v>-508451.7</v>
+        <v>-525307.52</v>
       </c>
       <c r="E23" s="20"/>
       <c r="H23" s="19"/>
     </row>
-    <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="272" t="s">
+    <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="277" t="s">
         <v>1</v>
       </c>
-      <c r="B24" s="273"/>
+      <c r="B24" s="278"/>
       <c r="C24" s="181"/>
       <c r="D24" s="183">
         <v>0</v>
@@ -2962,7 +2972,7 @@
       </c>
       <c r="H24" s="19"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="184" t="s">
         <v>105</v>
       </c>
@@ -2971,10 +2981,10 @@
       <c r="D25" s="22"/>
       <c r="E25" s="153">
         <f>SUM(D22:D24)</f>
-        <v>1829258.0000000002</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+        <v>1889900</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="184" t="s">
         <v>176</v>
       </c>
@@ -2983,63 +2993,49 @@
       <c r="D26" s="22"/>
       <c r="E26" s="154"/>
     </row>
-    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="181"/>
       <c r="B27" s="181"/>
       <c r="C27" s="181"/>
       <c r="D27" s="35"/>
       <c r="E27" s="167"/>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="181"/>
       <c r="B28" s="181"/>
       <c r="C28" s="181"/>
       <c r="D28" s="35"/>
       <c r="E28" s="167"/>
     </row>
-    <row r="29" spans="1:8" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="181"/>
       <c r="B29" s="181"/>
       <c r="C29" s="181"/>
       <c r="D29" s="35"/>
       <c r="E29" s="167"/>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="181"/>
       <c r="B30" s="181"/>
       <c r="C30" s="181"/>
       <c r="D30" s="35"/>
       <c r="E30" s="155"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" s="181" t="s">
-        <v>231</v>
-      </c>
-      <c r="B31" s="181" t="s">
-        <v>232</v>
-      </c>
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="181"/>
+      <c r="B31" s="181"/>
       <c r="C31" s="181"/>
-      <c r="D31" s="35">
-        <v>125000</v>
-      </c>
-      <c r="E31" s="155" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="181" t="s">
-        <v>234</v>
-      </c>
+      <c r="D31" s="35"/>
+      <c r="E31" s="155"/>
+    </row>
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="181"/>
       <c r="B32" s="181"/>
       <c r="C32" s="181"/>
-      <c r="D32" s="35">
-        <v>5087</v>
-      </c>
-      <c r="E32" s="155" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D32" s="35"/>
+      <c r="E32" s="155"/>
+    </row>
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="184" t="s">
         <v>105</v>
       </c>
@@ -3048,10 +3044,10 @@
       <c r="D33" s="107"/>
       <c r="E33" s="156">
         <f>SUM(D29:D32)</f>
-        <v>130087</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="36" t="s">
         <v>139</v>
       </c>
@@ -3060,9 +3056,9 @@
       <c r="D34" s="22"/>
       <c r="E34" s="154"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="181" t="s">
-        <v>241</v>
+        <v>219</v>
       </c>
       <c r="B35" s="186"/>
       <c r="C35" s="186"/>
@@ -3070,1171 +3066,1123 @@
         <v>12214.52</v>
       </c>
       <c r="E35" s="155" t="str">
-        <f>E37</f>
-        <v>Debito 13/07</v>
+        <f>E38</f>
+        <v>Debito 12/08</v>
       </c>
       <c r="G35" s="66"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="181" t="s">
-        <v>242</v>
+        <v>268</v>
       </c>
       <c r="B36" s="186"/>
       <c r="C36" s="186"/>
-      <c r="D36" s="35">
-        <v>0</v>
-      </c>
-      <c r="E36" s="155"/>
+      <c r="D36" s="335">
+        <v>1488022.91</v>
+      </c>
+      <c r="E36" s="155" t="s">
+        <v>270</v>
+      </c>
       <c r="G36" s="66"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="181" t="s">
-        <v>141</v>
+        <v>269</v>
       </c>
       <c r="B37" s="186"/>
       <c r="C37" s="186"/>
-      <c r="D37" s="337">
-        <v>201343.09</v>
+      <c r="D37" s="335">
+        <v>1027794.88</v>
       </c>
       <c r="E37" s="155" t="s">
-        <v>224</v>
+        <v>270</v>
       </c>
       <c r="G37" s="66"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="181" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B38" s="186"/>
       <c r="C38" s="186"/>
-      <c r="D38" s="337">
-        <v>105196.9</v>
-      </c>
-      <c r="E38" s="155" t="str">
-        <f>E37</f>
-        <v>Debito 13/07</v>
-      </c>
-      <c r="G38" s="50"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D38" s="335">
+        <v>201343.09</v>
+      </c>
+      <c r="E38" s="155" t="s">
+        <v>262</v>
+      </c>
+      <c r="G38" s="66"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="181" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B39" s="186"/>
       <c r="C39" s="186"/>
-      <c r="D39" s="337">
-        <v>11688.54</v>
+      <c r="D39" s="335">
+        <v>105196.9</v>
       </c>
       <c r="E39" s="155" t="str">
-        <f>E37</f>
-        <v>Debito 13/07</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+        <f>E38</f>
+        <v>Debito 12/08</v>
+      </c>
+      <c r="G39" s="50"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="181" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="B40" s="186"/>
       <c r="C40" s="186"/>
-      <c r="D40" s="35"/>
-      <c r="E40" s="155"/>
-    </row>
-    <row r="41" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="184" t="s">
+      <c r="D40" s="335">
+        <v>11688.54</v>
+      </c>
+      <c r="E40" s="155" t="str">
+        <f>E38</f>
+        <v>Debito 12/08</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="181" t="s">
+        <v>149</v>
+      </c>
+      <c r="B41" s="186"/>
+      <c r="C41" s="186"/>
+      <c r="D41" s="35"/>
+      <c r="E41" s="155"/>
+    </row>
+    <row r="42" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="184" t="s">
         <v>140</v>
       </c>
-      <c r="B41" s="184"/>
-      <c r="C41" s="184"/>
-      <c r="D41" s="22"/>
-      <c r="E41" s="41">
-        <f>SUM(D35:D40)</f>
-        <v>330443.05</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A42" s="14" t="s">
+      <c r="B42" s="184"/>
+      <c r="C42" s="184"/>
+      <c r="D42" s="22"/>
+      <c r="E42" s="41">
+        <f>SUM(D35:D41)</f>
+        <v>2846260.84</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="B42" s="21"/>
-      <c r="C42" s="21"/>
-      <c r="D42" s="23"/>
-      <c r="E42" s="156"/>
-    </row>
-    <row r="43" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="280" t="s">
+      <c r="B43" s="21"/>
+      <c r="C43" s="21"/>
+      <c r="D43" s="23"/>
+      <c r="E43" s="156"/>
+    </row>
+    <row r="44" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="272" t="s">
         <v>183</v>
       </c>
-      <c r="B43" s="281"/>
-      <c r="C43" s="26"/>
-      <c r="D43" s="229">
+      <c r="B44" s="273"/>
+      <c r="C44" s="26"/>
+      <c r="D44" s="333">
         <v>7805</v>
-      </c>
-      <c r="E43" s="20" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="280" t="s">
-        <v>185</v>
-      </c>
-      <c r="B44" s="281"/>
-      <c r="C44" s="26"/>
-      <c r="D44" s="229">
-        <v>213891</v>
       </c>
       <c r="E44" s="20" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" s="21" t="s">
+    <row r="45" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="272" t="s">
+        <v>185</v>
+      </c>
+      <c r="B45" s="273"/>
+      <c r="C45" s="26"/>
+      <c r="D45" s="333">
+        <v>213891</v>
+      </c>
+      <c r="E45" s="20" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="B45" s="21"/>
-      <c r="C45" s="21"/>
-      <c r="D45" s="22"/>
-      <c r="E45" s="41">
-        <f>SUM(D43:D44)</f>
+      <c r="B46" s="21"/>
+      <c r="C46" s="21"/>
+      <c r="D46" s="22"/>
+      <c r="E46" s="41">
+        <f>SUM(D44:D45)</f>
         <v>221696</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" s="14" t="s">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="B46" s="27"/>
-      <c r="C46" s="27"/>
-      <c r="D46" s="28"/>
-      <c r="E46" s="157"/>
-    </row>
-    <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="29" t="s">
-        <v>109</v>
-      </c>
-      <c r="B47" s="29" t="s">
-        <v>168</v>
-      </c>
-      <c r="C47" s="29"/>
-      <c r="D47" s="30">
-        <v>1390852.75</v>
-      </c>
-      <c r="E47" s="118" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B47" s="27"/>
+      <c r="C47" s="27"/>
+      <c r="D47" s="28"/>
+      <c r="E47" s="157"/>
+    </row>
+    <row r="48" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="29" t="s">
         <v>109</v>
       </c>
       <c r="B48" s="29" t="s">
+        <v>168</v>
+      </c>
+      <c r="C48" s="29"/>
+      <c r="D48" s="332">
+        <v>568601.14</v>
+      </c>
+      <c r="E48" s="118" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="29" t="s">
+        <v>109</v>
+      </c>
+      <c r="B49" s="29" t="s">
         <v>170</v>
-      </c>
-      <c r="C48" s="29"/>
-      <c r="D48" s="30">
-        <v>36242.83</v>
-      </c>
-      <c r="E48" s="191" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="29" t="s">
-        <v>177</v>
-      </c>
-      <c r="B49" s="29" t="s">
-        <v>169</v>
       </c>
       <c r="C49" s="29"/>
       <c r="D49" s="30">
-        <v>0</v>
-      </c>
-      <c r="E49" s="20"/>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+        <v>36242.83</v>
+      </c>
+      <c r="E49" s="191" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="29" t="s">
-        <v>178</v>
-      </c>
-      <c r="B50" s="31"/>
+        <v>177</v>
+      </c>
+      <c r="B50" s="29" t="s">
+        <v>169</v>
+      </c>
       <c r="C50" s="29"/>
       <c r="D50" s="30">
         <v>0</v>
       </c>
       <c r="E50" s="20"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="280" t="s">
-        <v>110</v>
-      </c>
-      <c r="B51" s="281"/>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="29" t="s">
+        <v>178</v>
+      </c>
+      <c r="B51" s="31"/>
       <c r="C51" s="29"/>
       <c r="D51" s="30">
-        <v>5946930.7699999996</v>
-      </c>
-      <c r="E51" s="118" t="s">
-        <v>223</v>
-      </c>
-      <c r="F51">
-        <f>132000+148000+3942</f>
-        <v>283942</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="E51" s="20"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="272" t="s">
+        <v>110</v>
+      </c>
+      <c r="B52" s="273"/>
+      <c r="C52" s="29"/>
+      <c r="D52" s="332">
+        <v>5805252.4400000004</v>
+      </c>
+      <c r="E52" s="118" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="32" t="s">
         <v>111</v>
       </c>
-      <c r="B52" s="25"/>
-      <c r="C52" s="29"/>
-      <c r="D52" s="30"/>
-      <c r="E52" s="20"/>
-    </row>
-    <row r="53" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="21" t="s">
+      <c r="B53" s="25"/>
+      <c r="C53" s="29"/>
+      <c r="D53" s="30"/>
+      <c r="E53" s="20"/>
+    </row>
+    <row r="54" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="B53" s="21"/>
-      <c r="C53" s="21"/>
-      <c r="D53" s="33"/>
-      <c r="E53" s="158">
-        <f>SUM(D47:D52)</f>
-        <v>7374026.3499999996</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="14"/>
       <c r="B54" s="21"/>
       <c r="C54" s="21"/>
-      <c r="D54" s="22"/>
-      <c r="E54" s="159"/>
-    </row>
-    <row r="55" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="274" t="s">
+      <c r="D54" s="33"/>
+      <c r="E54" s="158">
+        <f>SUM(D48:D53)</f>
+        <v>6410096.4100000001</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="14"/>
+      <c r="B55" s="21"/>
+      <c r="C55" s="21"/>
+      <c r="D55" s="22"/>
+      <c r="E55" s="159"/>
+    </row>
+    <row r="56" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="266" t="s">
         <v>164</v>
       </c>
-      <c r="B55" s="275"/>
-      <c r="C55" s="29"/>
-      <c r="D55" s="334">
+      <c r="B56" s="267"/>
+      <c r="C56" s="29"/>
+      <c r="D56" s="332">
         <v>285000</v>
       </c>
-      <c r="E55" s="166" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="274" t="s">
-        <v>238</v>
-      </c>
-      <c r="B56" s="275"/>
-      <c r="C56" s="29"/>
-      <c r="D56" s="30">
-        <v>280000</v>
-      </c>
       <c r="E56" s="166" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="186.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="274" t="s">
-        <v>226</v>
-      </c>
-      <c r="B57" s="275"/>
+        <v>254</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="266" t="s">
+        <v>265</v>
+      </c>
+      <c r="B57" s="267"/>
       <c r="C57" s="29"/>
-      <c r="D57" s="30">
-        <v>1400000</v>
-      </c>
-      <c r="E57" s="166"/>
-      <c r="F57" s="50"/>
-    </row>
-    <row r="58" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="92" t="s">
-        <v>219</v>
-      </c>
-      <c r="B58" s="17"/>
+      <c r="D57" s="332">
+        <v>200000</v>
+      </c>
+      <c r="E57" s="166" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="186.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="266" t="s">
+        <v>264</v>
+      </c>
+      <c r="B58" s="267"/>
       <c r="C58" s="29"/>
-      <c r="D58" s="30">
-        <v>841000</v>
+      <c r="D58" s="332">
+        <v>3300000</v>
       </c>
       <c r="E58" s="166" t="s">
-        <v>233</v>
-      </c>
-      <c r="F58" s="50">
-        <f>39911.44+109035.44</f>
-        <v>148946.88</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="274" t="s">
-        <v>229</v>
-      </c>
-      <c r="B59" s="275"/>
+        <v>263</v>
+      </c>
+      <c r="F58" s="50"/>
+    </row>
+    <row r="59" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="B59" s="17"/>
       <c r="C59" s="29"/>
       <c r="D59" s="30">
-        <v>687000</v>
-      </c>
-      <c r="E59" s="34" t="s">
-        <v>230</v>
-      </c>
-      <c r="F59" s="50"/>
-    </row>
-    <row r="60" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="16" t="s">
-        <v>215</v>
+        <v>6990</v>
+      </c>
+      <c r="E59" s="34"/>
+      <c r="F59" s="218"/>
+    </row>
+    <row r="60" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="92" t="s">
+        <v>257</v>
       </c>
       <c r="B60" s="17"/>
       <c r="C60" s="29"/>
-      <c r="D60" s="30">
-        <v>6990</v>
-      </c>
-      <c r="E60" s="34"/>
-      <c r="F60" s="218"/>
-    </row>
-    <row r="61" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="92" t="s">
-        <v>209</v>
-      </c>
-      <c r="B61" s="17"/>
+      <c r="D60" s="332">
+        <v>638000</v>
+      </c>
+      <c r="E60" s="34" t="s">
+        <v>261</v>
+      </c>
+      <c r="F60" s="50"/>
+    </row>
+    <row r="61" spans="1:6" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="266" t="s">
+        <v>253</v>
+      </c>
+      <c r="B61" s="267"/>
       <c r="C61" s="29"/>
-      <c r="D61" s="30">
+      <c r="D61" s="332">
         <v>31400</v>
       </c>
       <c r="E61" s="34" t="s">
-        <v>235</v>
+        <v>263</v>
       </c>
       <c r="F61" s="50"/>
     </row>
-    <row r="62" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="92" t="s">
-        <v>221</v>
-      </c>
-      <c r="B62" s="17"/>
+    <row r="62" spans="1:6" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="266" t="s">
+        <v>252</v>
+      </c>
+      <c r="B62" s="267"/>
       <c r="C62" s="29"/>
-      <c r="D62" s="30">
+      <c r="D62" s="332">
         <v>31400</v>
       </c>
       <c r="E62" s="34" t="s">
-        <v>235</v>
+        <v>263</v>
       </c>
       <c r="F62" s="50"/>
     </row>
-    <row r="63" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="92" t="s">
-        <v>208</v>
-      </c>
-      <c r="B63" s="17"/>
+    <row r="63" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="266" t="s">
+        <v>256</v>
+      </c>
+      <c r="B63" s="267"/>
       <c r="C63" s="29"/>
-      <c r="D63" s="30">
-        <v>31400</v>
-      </c>
-      <c r="E63" s="34" t="s">
-        <v>235</v>
+      <c r="D63" s="332">
+        <v>90000</v>
+      </c>
+      <c r="E63" s="166" t="s">
+        <v>255</v>
       </c>
       <c r="F63" s="50"/>
     </row>
-    <row r="64" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="92" t="s">
-        <v>285</v>
+        <v>259</v>
       </c>
       <c r="B64" s="17"/>
       <c r="C64" s="29"/>
-      <c r="D64" s="334">
-        <v>638000</v>
-      </c>
-      <c r="E64" s="34" t="s">
-        <v>235</v>
+      <c r="D64" s="332">
+        <v>155300</v>
+      </c>
+      <c r="E64" s="166" t="s">
+        <v>258</v>
       </c>
       <c r="F64" s="50"/>
     </row>
-    <row r="65" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="274" t="s">
-        <v>281</v>
-      </c>
-      <c r="B65" s="275"/>
+    <row r="65" spans="1:7" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="266" t="s">
+        <v>260</v>
+      </c>
+      <c r="B65" s="267"/>
       <c r="C65" s="29"/>
-      <c r="D65" s="334">
-        <v>31400</v>
-      </c>
-      <c r="E65" s="34" t="s">
-        <v>280</v>
+      <c r="D65" s="332">
+        <v>500000</v>
+      </c>
+      <c r="E65" s="166" t="s">
+        <v>258</v>
       </c>
       <c r="F65" s="50"/>
     </row>
-    <row r="66" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="274" t="s">
-        <v>279</v>
-      </c>
-      <c r="B66" s="275"/>
+    <row r="66" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="266" t="s">
+        <v>249</v>
+      </c>
+      <c r="B66" s="267"/>
       <c r="C66" s="29"/>
-      <c r="D66" s="334">
-        <v>31400</v>
-      </c>
-      <c r="E66" s="34" t="s">
-        <v>280</v>
+      <c r="D66" s="332">
+        <v>27660.41</v>
+      </c>
+      <c r="E66" s="166" t="s">
+        <v>251</v>
       </c>
       <c r="F66" s="50"/>
     </row>
-    <row r="67" spans="1:7" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="274" t="s">
-        <v>284</v>
-      </c>
-      <c r="B67" s="275"/>
+    <row r="67" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="92" t="s">
+        <v>200</v>
+      </c>
+      <c r="B67" s="17"/>
       <c r="C67" s="29"/>
-      <c r="D67" s="334">
-        <v>90000</v>
+      <c r="D67" s="332">
+        <v>379800</v>
       </c>
       <c r="E67" s="166" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="F67" s="50"/>
     </row>
-    <row r="68" spans="1:7" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="92" t="s">
-        <v>287</v>
-      </c>
-      <c r="B68" s="17"/>
+    <row r="68" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="266" t="s">
+        <v>246</v>
+      </c>
+      <c r="B68" s="267"/>
       <c r="C68" s="29"/>
-      <c r="D68" s="334">
-        <v>155300</v>
+      <c r="D68" s="332">
+        <v>124611.12</v>
       </c>
       <c r="E68" s="166" t="s">
-        <v>286</v>
+        <v>267</v>
       </c>
       <c r="F68" s="50"/>
     </row>
-    <row r="69" spans="1:7" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="274" t="s">
-        <v>288</v>
-      </c>
-      <c r="B69" s="275"/>
-      <c r="C69" s="29"/>
-      <c r="D69" s="334">
-        <v>500000</v>
-      </c>
-      <c r="E69" s="166" t="s">
-        <v>286</v>
-      </c>
-      <c r="F69" s="50"/>
-    </row>
-    <row r="70" spans="1:7" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="92" t="s">
-        <v>228</v>
-      </c>
-      <c r="B70" s="17"/>
-      <c r="C70" s="29"/>
-      <c r="D70" s="30">
-        <v>7500</v>
-      </c>
-      <c r="E70" s="166" t="s">
-        <v>210</v>
-      </c>
-      <c r="F70" s="50"/>
-    </row>
-    <row r="71" spans="1:7" ht="66" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="274" t="s">
-        <v>275</v>
-      </c>
-      <c r="B71" s="275"/>
-      <c r="C71" s="29"/>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B69" s="14"/>
+      <c r="C69" s="14"/>
+      <c r="D69" s="36"/>
+      <c r="E69" s="41">
+        <f>SUM(D56:D68)</f>
+        <v>5770161.5300000003</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="B70" s="14"/>
+      <c r="C70" s="14"/>
+      <c r="D70" s="15"/>
+      <c r="E70" s="151"/>
+    </row>
+    <row r="71" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="266" t="s">
+        <v>247</v>
+      </c>
+      <c r="B71" s="267"/>
+      <c r="C71" s="18"/>
       <c r="D71" s="334">
-        <v>27660.41</v>
+        <v>781000</v>
       </c>
       <c r="E71" s="166" t="s">
-        <v>277</v>
-      </c>
-      <c r="F71" s="50"/>
-    </row>
-    <row r="72" spans="1:7" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="92" t="s">
-        <v>200</v>
-      </c>
-      <c r="B72" s="17"/>
-      <c r="C72" s="29"/>
-      <c r="D72" s="30">
-        <v>405300</v>
+        <v>258</v>
+      </c>
+      <c r="G71" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="266" t="s">
+        <v>271</v>
+      </c>
+      <c r="B72" s="267"/>
+      <c r="C72" s="18"/>
+      <c r="D72" s="336">
+        <f>24000+72000</f>
+        <v>96000</v>
       </c>
       <c r="E72" s="166" t="s">
-        <v>237</v>
-      </c>
-      <c r="F72" s="50"/>
-    </row>
-    <row r="73" spans="1:7" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="274" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="92" t="s">
+        <v>272</v>
+      </c>
+      <c r="B73" s="264"/>
+      <c r="C73" s="18"/>
+      <c r="D73" s="336">
+        <v>220000</v>
+      </c>
+      <c r="E73" s="166" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="B74" s="17"/>
+      <c r="C74" s="18"/>
+      <c r="D74" s="336">
+        <v>250000</v>
+      </c>
+      <c r="E74" s="166" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="92" t="s">
+        <v>248</v>
+      </c>
+      <c r="B75" s="17"/>
+      <c r="C75" s="18"/>
+      <c r="D75" s="336">
+        <v>50000</v>
+      </c>
+      <c r="E75" s="166" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="B76" s="21"/>
+      <c r="C76" s="21"/>
+      <c r="D76" s="22"/>
+      <c r="E76" s="153">
+        <f>SUM(D71:D75)</f>
+        <v>1397000</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="B77" s="37"/>
+      <c r="C77" s="21"/>
+      <c r="D77" s="38"/>
+      <c r="E77" s="41"/>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" s="29" t="s">
         <v>218</v>
       </c>
-      <c r="B73" s="275"/>
-      <c r="C73" s="29"/>
-      <c r="D73" s="30">
-        <v>124611.12</v>
-      </c>
-      <c r="E73" s="166" t="s">
-        <v>220</v>
-      </c>
-      <c r="F73" s="50"/>
-    </row>
-    <row r="74" spans="1:7" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="274" t="s">
-        <v>272</v>
-      </c>
-      <c r="B74" s="275"/>
-      <c r="C74" s="29"/>
-      <c r="D74" s="30">
-        <v>124611.12</v>
-      </c>
-      <c r="E74" s="166" t="s">
-        <v>220</v>
-      </c>
-      <c r="F74" s="50"/>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A75" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="B75" s="14"/>
-      <c r="C75" s="14"/>
-      <c r="D75" s="36"/>
-      <c r="E75" s="41">
-        <f>SUM(D55:D74)</f>
-        <v>5729972.6500000004</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A76" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="B76" s="14"/>
-      <c r="C76" s="14"/>
-      <c r="D76" s="15"/>
-      <c r="E76" s="151"/>
-    </row>
-    <row r="77" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="274" t="s">
-        <v>273</v>
-      </c>
-      <c r="B77" s="275"/>
-      <c r="C77" s="18"/>
-      <c r="D77" s="230">
-        <v>650000</v>
-      </c>
-      <c r="E77" s="166" t="s">
-        <v>220</v>
-      </c>
-      <c r="G77" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="274" t="s">
-        <v>225</v>
-      </c>
-      <c r="B78" s="275"/>
-      <c r="C78" s="18"/>
-      <c r="D78" s="231">
-        <v>50000</v>
-      </c>
-      <c r="E78" s="166" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="16" t="s">
-        <v>163</v>
-      </c>
-      <c r="B79" s="17"/>
-      <c r="C79" s="18"/>
-      <c r="D79" s="336">
-        <v>250000</v>
-      </c>
-      <c r="E79" s="166" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="92" t="s">
-        <v>236</v>
-      </c>
-      <c r="B80" s="17"/>
-      <c r="C80" s="18"/>
-      <c r="D80" s="231">
-        <v>484217.8</v>
-      </c>
-      <c r="E80" s="166" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="92" t="s">
-        <v>274</v>
-      </c>
-      <c r="B81" s="17"/>
-      <c r="C81" s="18"/>
-      <c r="D81" s="336">
-        <v>50000</v>
-      </c>
-      <c r="E81" s="166" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A82" s="21" t="s">
-        <v>105</v>
-      </c>
-      <c r="B82" s="21"/>
-      <c r="C82" s="21"/>
-      <c r="D82" s="22"/>
-      <c r="E82" s="153">
-        <f>SUM(D77:D81)</f>
-        <v>1484217.8</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A83" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="B83" s="37"/>
-      <c r="C83" s="21"/>
-      <c r="D83" s="38"/>
-      <c r="E83" s="41"/>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A84" s="29" t="s">
-        <v>240</v>
-      </c>
-      <c r="B84" s="91"/>
-      <c r="C84" s="91"/>
-      <c r="D84" s="232">
+      <c r="B78" s="91"/>
+      <c r="C78" s="91"/>
+      <c r="D78" s="337">
         <f>44612.24+65000-12214.52</f>
         <v>97397.719999999987</v>
       </c>
-      <c r="E84" s="160"/>
-    </row>
-    <row r="85" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="280" t="s">
-        <v>239</v>
-      </c>
-      <c r="B85" s="281"/>
-      <c r="C85" s="91"/>
-      <c r="D85" s="232">
-        <v>225591.15</v>
-      </c>
-      <c r="E85" s="160"/>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A86" s="39" t="s">
+      <c r="E78" s="160"/>
+    </row>
+    <row r="79" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="272" t="s">
+        <v>217</v>
+      </c>
+      <c r="B79" s="273"/>
+      <c r="C79" s="91"/>
+      <c r="D79" s="337">
+        <v>269207.65999999997</v>
+      </c>
+      <c r="E79" s="160"/>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80" s="39" t="s">
         <v>105</v>
       </c>
-      <c r="B86" s="39"/>
-      <c r="C86" s="39"/>
-      <c r="D86" s="40"/>
-      <c r="E86" s="41">
-        <f>SUM(D84:D85)</f>
-        <v>322988.87</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A87" s="29"/>
-      <c r="B87" s="29"/>
-      <c r="C87" s="29"/>
-      <c r="D87" s="42"/>
-      <c r="E87" s="43"/>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A88" s="44" t="s">
+      <c r="B80" s="39"/>
+      <c r="C80" s="39"/>
+      <c r="D80" s="40"/>
+      <c r="E80" s="41">
+        <f>SUM(D78:D79)</f>
+        <v>366605.37999999995</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" s="29"/>
+      <c r="B81" s="29"/>
+      <c r="C81" s="29"/>
+      <c r="D81" s="42"/>
+      <c r="E81" s="43"/>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" s="44" t="s">
         <v>115</v>
       </c>
-      <c r="B88" s="44"/>
-      <c r="C88" s="44"/>
-      <c r="D88" s="45"/>
-      <c r="E88" s="46">
+      <c r="B82" s="44"/>
+      <c r="C82" s="44"/>
+      <c r="D82" s="45"/>
+      <c r="E82" s="46">
         <v>1500000</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="47"/>
-      <c r="D89" s="48"/>
-      <c r="E89" s="49"/>
-      <c r="F89" s="50"/>
-    </row>
-    <row r="90" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="51" t="s">
+    <row r="83" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="47"/>
+      <c r="D83" s="48"/>
+      <c r="E83" s="49"/>
+      <c r="F83" s="50"/>
+    </row>
+    <row r="84" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="51" t="s">
         <v>116</v>
       </c>
-      <c r="B90" s="52"/>
-      <c r="C90" s="53"/>
-      <c r="D90" s="54"/>
-      <c r="E90" s="55">
-        <f>(SUM(E21:E88))</f>
-        <v>19171125.82</v>
-      </c>
-      <c r="F90" s="56"/>
-      <c r="G90" s="50"/>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D91" s="48"/>
-      <c r="E91" s="48"/>
-    </row>
-    <row r="92" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D92" s="48"/>
-      <c r="E92" s="48"/>
-      <c r="H92" s="57"/>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A93" s="11" t="s">
+      <c r="B84" s="52"/>
+      <c r="C84" s="53"/>
+      <c r="D84" s="54"/>
+      <c r="E84" s="55">
+        <f>(SUM(E21:E82))</f>
+        <v>20650156.259999998</v>
+      </c>
+      <c r="F84" s="56"/>
+      <c r="G84" s="50"/>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D85" s="48"/>
+      <c r="E85" s="48"/>
+    </row>
+    <row r="86" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D86" s="48"/>
+      <c r="E86" s="48"/>
+      <c r="H86" s="57"/>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="B93" s="12"/>
-      <c r="C93" s="13"/>
-      <c r="D93" s="58"/>
-      <c r="E93" s="59"/>
-    </row>
-    <row r="94" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="286"/>
-      <c r="B94" s="286"/>
-      <c r="C94" s="31"/>
-      <c r="D94" s="282"/>
-      <c r="E94" s="284"/>
-    </row>
-    <row r="95" spans="1:8" ht="1.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="286"/>
-      <c r="B95" s="286"/>
-      <c r="C95" s="31"/>
-      <c r="D95" s="283"/>
-      <c r="E95" s="285"/>
-    </row>
-    <row r="96" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="29"/>
-      <c r="B96" s="29"/>
-      <c r="D96" s="42"/>
-      <c r="E96" s="42"/>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A97" s="24"/>
-      <c r="B97" s="61"/>
-      <c r="C97" s="29"/>
-      <c r="D97" s="35"/>
-      <c r="E97" s="60"/>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A98" s="62" t="s">
+      <c r="B87" s="12"/>
+      <c r="C87" s="13"/>
+      <c r="D87" s="58"/>
+      <c r="E87" s="59"/>
+    </row>
+    <row r="88" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="274"/>
+      <c r="B88" s="274"/>
+      <c r="C88" s="31"/>
+      <c r="D88" s="268"/>
+      <c r="E88" s="270"/>
+    </row>
+    <row r="89" spans="1:8" ht="1.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="274"/>
+      <c r="B89" s="274"/>
+      <c r="C89" s="31"/>
+      <c r="D89" s="269"/>
+      <c r="E89" s="271"/>
+    </row>
+    <row r="90" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="29"/>
+      <c r="B90" s="29"/>
+      <c r="D90" s="42"/>
+      <c r="E90" s="42"/>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" s="24"/>
+      <c r="B91" s="61"/>
+      <c r="C91" s="29"/>
+      <c r="D91" s="35"/>
+      <c r="E91" s="60"/>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" s="62" t="s">
         <v>145</v>
       </c>
-      <c r="B98" s="63"/>
-      <c r="C98" s="63"/>
-      <c r="D98" s="116"/>
-      <c r="E98" s="161">
-        <f>SUM(D94:D97)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B92" s="63"/>
+      <c r="C92" s="63"/>
+      <c r="D92" s="116"/>
+      <c r="E92" s="161">
+        <f>SUM(D88:D91)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D93" s="48"/>
+      <c r="E93" s="48"/>
+    </row>
+    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D94" s="48"/>
+      <c r="E94" s="48"/>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" s="44" t="s">
+        <v>118</v>
+      </c>
+      <c r="B95" s="44"/>
+      <c r="C95" s="44"/>
+      <c r="D95" s="45"/>
+      <c r="E95" s="165">
+        <v>4500000</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D96" s="48"/>
+      <c r="E96" s="48"/>
+    </row>
+    <row r="97" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="51" t="s">
+        <v>119</v>
+      </c>
+      <c r="B97" s="52"/>
+      <c r="C97" s="53"/>
+      <c r="D97" s="54"/>
+      <c r="E97" s="55">
+        <f>E92+E95</f>
+        <v>4500000</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D98" s="48"/>
+      <c r="E98" s="48"/>
+    </row>
+    <row r="99" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="64" t="s">
+        <v>120</v>
+      </c>
+      <c r="B99" s="65">
+        <f>E84</f>
+        <v>20650156.259999998</v>
+      </c>
       <c r="D99" s="48"/>
       <c r="E99" s="48"/>
     </row>
-    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="64" t="s">
+        <v>121</v>
+      </c>
+      <c r="B100" s="65">
+        <f>E84-E82</f>
+        <v>19150156.259999998</v>
+      </c>
       <c r="D100" s="48"/>
       <c r="E100" s="48"/>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A101" s="44" t="s">
-        <v>118</v>
-      </c>
-      <c r="B101" s="44"/>
-      <c r="C101" s="44"/>
-      <c r="D101" s="45"/>
-      <c r="E101" s="165">
+    <row r="101" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="64" t="s">
+        <v>122</v>
+      </c>
+      <c r="B101" s="65">
+        <f>E97-E95</f>
+        <v>0</v>
+      </c>
+      <c r="D101" s="48"/>
+      <c r="E101" s="48"/>
+    </row>
+    <row r="102" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="64" t="s">
+        <v>123</v>
+      </c>
+      <c r="B102" s="65">
+        <f>E97</f>
         <v>4500000</v>
       </c>
-    </row>
-    <row r="102" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D102" s="48"/>
       <c r="E102" s="48"/>
     </row>
-    <row r="103" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A103" s="51" t="s">
-        <v>119</v>
-      </c>
-      <c r="B103" s="52"/>
-      <c r="C103" s="53"/>
-      <c r="D103" s="54"/>
-      <c r="E103" s="55">
-        <f>E98+E101</f>
-        <v>4500000</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D103" s="48"/>
+      <c r="E103" s="48"/>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D104" s="48"/>
       <c r="E104" s="48"/>
     </row>
-    <row r="105" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A105" s="64" t="s">
-        <v>120</v>
-      </c>
-      <c r="B105" s="65">
-        <f>E90</f>
-        <v>19171125.82</v>
-      </c>
+    <row r="105" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="284" t="s">
+        <v>172</v>
+      </c>
+      <c r="B105" s="284"/>
       <c r="D105" s="48"/>
       <c r="E105" s="48"/>
     </row>
-    <row r="106" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="64" t="s">
-        <v>121</v>
-      </c>
-      <c r="B106" s="65">
-        <f>E90-E88</f>
-        <v>17671125.82</v>
-      </c>
+    <row r="106" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="284"/>
+      <c r="B106" s="284"/>
       <c r="D106" s="48"/>
       <c r="E106" s="48"/>
     </row>
-    <row r="107" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A107" s="64" t="s">
-        <v>122</v>
-      </c>
-      <c r="B107" s="65">
-        <f>E103-E101</f>
-        <v>0</v>
-      </c>
+    <row r="107" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="284"/>
+      <c r="B107" s="284"/>
       <c r="D107" s="48"/>
       <c r="E107" s="48"/>
     </row>
-    <row r="108" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A108" s="64" t="s">
-        <v>123</v>
-      </c>
-      <c r="B108" s="65">
-        <f>E103</f>
-        <v>4500000</v>
-      </c>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D108" s="48"/>
       <c r="E108" s="48"/>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" s="284" t="s">
+        <v>274</v>
+      </c>
+      <c r="B109" s="284"/>
       <c r="D109" s="48"/>
       <c r="E109" s="48"/>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" s="284"/>
+      <c r="B110" s="284"/>
       <c r="D110" s="48"/>
       <c r="E110" s="48"/>
     </row>
-    <row r="111" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="269" t="s">
-        <v>172</v>
-      </c>
-      <c r="B111" s="269"/>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" s="284"/>
+      <c r="B111" s="284"/>
       <c r="D111" s="48"/>
       <c r="E111" s="48"/>
     </row>
-    <row r="112" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="269"/>
-      <c r="B112" s="269"/>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D112" s="48"/>
       <c r="E112" s="48"/>
     </row>
-    <row r="113" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="269"/>
-      <c r="B113" s="269"/>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A113" s="284" t="s">
+        <v>275</v>
+      </c>
+      <c r="B113" s="284"/>
       <c r="D113" s="48"/>
       <c r="E113" s="48"/>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114" s="284"/>
+      <c r="B114" s="284"/>
       <c r="D114" s="48"/>
       <c r="E114" s="48"/>
     </row>
-    <row r="115" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="269" t="s">
-        <v>199</v>
-      </c>
-      <c r="B115" s="269"/>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A115" s="284"/>
+      <c r="B115" s="284"/>
       <c r="D115" s="48"/>
       <c r="E115" s="48"/>
     </row>
-    <row r="116" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="269"/>
-      <c r="B116" s="269"/>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D116" s="48"/>
       <c r="E116" s="48"/>
     </row>
-    <row r="117" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="269"/>
-      <c r="B117" s="269"/>
+    <row r="117" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="284" t="s">
+        <v>199</v>
+      </c>
+      <c r="B117" s="284"/>
       <c r="D117" s="48"/>
       <c r="E117" s="48"/>
     </row>
-    <row r="118" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="284"/>
+      <c r="B118" s="284"/>
       <c r="D118" s="48"/>
       <c r="E118" s="48"/>
-      <c r="F118" s="217"/>
-    </row>
-    <row r="119" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="269" t="s">
-        <v>179</v>
-      </c>
-      <c r="B119" s="269"/>
+    </row>
+    <row r="119" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="284"/>
+      <c r="B119" s="284"/>
       <c r="D119" s="48"/>
       <c r="E119" s="48"/>
     </row>
-    <row r="120" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="269"/>
-      <c r="B120" s="269"/>
+    <row r="120" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D120" s="48"/>
       <c r="E120" s="48"/>
-    </row>
-    <row r="121" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="269"/>
-      <c r="B121" s="269"/>
+      <c r="F120" s="217"/>
+    </row>
+    <row r="121" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="284" t="s">
+        <v>179</v>
+      </c>
+      <c r="B121" s="284"/>
       <c r="D121" s="48"/>
       <c r="E121" s="48"/>
     </row>
-    <row r="122" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="284"/>
+      <c r="B122" s="284"/>
       <c r="D122" s="48"/>
       <c r="E122" s="48"/>
     </row>
-    <row r="123" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="269" t="s">
-        <v>182</v>
-      </c>
-      <c r="B123" s="269"/>
+    <row r="123" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="284"/>
+      <c r="B123" s="284"/>
       <c r="D123" s="48"/>
       <c r="E123" s="48"/>
     </row>
-    <row r="124" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="269"/>
-      <c r="B124" s="269"/>
+    <row r="124" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D124" s="48"/>
       <c r="E124" s="48"/>
     </row>
-    <row r="125" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="269"/>
-      <c r="B125" s="269"/>
+    <row r="125" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="284" t="s">
+        <v>182</v>
+      </c>
+      <c r="B125" s="284"/>
       <c r="D125" s="48"/>
       <c r="E125" s="48"/>
     </row>
-    <row r="126" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="284"/>
+      <c r="B126" s="284"/>
       <c r="D126" s="48"/>
       <c r="E126" s="48"/>
     </row>
-    <row r="127" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="269" t="s">
-        <v>181</v>
-      </c>
-      <c r="B127" s="269"/>
+    <row r="127" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="284"/>
+      <c r="B127" s="284"/>
       <c r="D127" s="48"/>
       <c r="E127" s="48"/>
     </row>
-    <row r="128" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="269"/>
-      <c r="B128" s="269"/>
+    <row r="128" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D128" s="48"/>
       <c r="E128" s="48"/>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A129" s="269"/>
-      <c r="B129" s="269"/>
+    <row r="129" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="284" t="s">
+        <v>181</v>
+      </c>
+      <c r="B129" s="284"/>
       <c r="D129" s="48"/>
       <c r="E129" s="48"/>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="284"/>
+      <c r="B130" s="284"/>
       <c r="D130" s="48"/>
       <c r="E130" s="48"/>
     </row>
-    <row r="131" spans="1:6" s="68" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A131"/>
-      <c r="B131" s="66"/>
-      <c r="C131" s="67"/>
-      <c r="D131" s="162"/>
-      <c r="E131" s="162"/>
-    </row>
-    <row r="132" spans="1:6" s="68" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="168" t="s">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A131" s="284"/>
+      <c r="B131" s="284"/>
+      <c r="D131" s="48"/>
+      <c r="E131" s="48"/>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D132" s="48"/>
+      <c r="E132" s="48"/>
+    </row>
+    <row r="133" spans="1:6" s="68" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A133"/>
+      <c r="B133" s="66"/>
+      <c r="C133" s="67"/>
+      <c r="D133" s="162"/>
+      <c r="E133" s="162"/>
+    </row>
+    <row r="134" spans="1:6" s="68" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A134" s="168" t="s">
         <v>189</v>
       </c>
-      <c r="B132" s="69">
+      <c r="B134" s="69">
         <v>1631378.049999997</v>
       </c>
-      <c r="C132" s="67"/>
-      <c r="D132" s="163"/>
-      <c r="E132" s="163"/>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A133" s="26" t="s">
+      <c r="C134" s="67"/>
+      <c r="D134" s="163"/>
+      <c r="E134" s="163"/>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A135" s="26" t="s">
         <v>144</v>
       </c>
-      <c r="B133" s="70">
-        <f>-B106-B107</f>
-        <v>-17671125.82</v>
-      </c>
-      <c r="D133" s="48"/>
-      <c r="E133" s="48"/>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A134" s="26" t="s">
-        <v>124</v>
-      </c>
-      <c r="B134" s="70">
-        <f>B147</f>
-        <v>728000</v>
-      </c>
-      <c r="D134" s="48"/>
-      <c r="E134" s="48"/>
-      <c r="F134" s="66"/>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135" s="26" t="s">
-        <v>2</v>
-      </c>
-      <c r="B135" s="71">
-        <f>PRORRATEO!F119</f>
-        <v>15926490.739999998</v>
+      <c r="B135" s="70">
+        <f>-B100-B101</f>
+        <v>-19150156.259999998</v>
       </c>
       <c r="D135" s="48"/>
       <c r="E135" s="48"/>
-      <c r="F135" s="66"/>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="26" t="s">
-        <v>276</v>
-      </c>
-      <c r="B136" s="335">
-        <v>-155000</v>
+        <v>124</v>
+      </c>
+      <c r="B136" s="70">
+        <f>B149</f>
+        <v>0</v>
       </c>
       <c r="D136" s="48"/>
       <c r="E136" s="48"/>
       <c r="F136" s="66"/>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="26" t="s">
-        <v>278</v>
-      </c>
-      <c r="B137" s="335">
-        <v>-24000</v>
+        <v>2</v>
+      </c>
+      <c r="B137" s="71">
+        <f>PRORRATEO!F119</f>
+        <v>18244513.000000004</v>
       </c>
       <c r="D137" s="48"/>
       <c r="E137" s="48"/>
       <c r="F137" s="66"/>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="26" t="s">
-        <v>249</v>
-      </c>
-      <c r="B138" s="146">
-        <v>-3942</v>
+        <v>250</v>
+      </c>
+      <c r="B138" s="265">
+        <v>-155000</v>
       </c>
       <c r="D138" s="48"/>
       <c r="E138" s="48"/>
       <c r="F138" s="66"/>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="26" t="s">
-        <v>248</v>
-      </c>
-      <c r="B139" s="146">
-        <v>-132000</v>
-      </c>
-      <c r="D139" s="48"/>
+        <v>276</v>
+      </c>
+      <c r="B139" s="265">
+        <v>-155000</v>
+      </c>
+      <c r="D139" s="48" t="s">
+        <v>277</v>
+      </c>
       <c r="E139" s="48"/>
       <c r="F139" s="66"/>
     </row>
-    <row r="140" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A140" s="72" t="s">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A140" s="26" t="s">
+        <v>223</v>
+      </c>
+      <c r="B140" s="146">
+        <v>0</v>
+      </c>
+      <c r="D140" s="48"/>
+      <c r="E140" s="48"/>
+      <c r="F140" s="66"/>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A141" s="26" t="s">
+        <v>222</v>
+      </c>
+      <c r="B141" s="146">
+        <v>0</v>
+      </c>
+      <c r="D141" s="48"/>
+      <c r="E141" s="48"/>
+      <c r="F141" s="66"/>
+    </row>
+    <row r="142" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A142" s="72" t="s">
         <v>160</v>
       </c>
-      <c r="B140" s="73">
-        <f>SUM(B132:C139)</f>
-        <v>299800.96999999508</v>
-      </c>
-      <c r="D140" s="66"/>
-      <c r="E140" s="50"/>
-      <c r="F140" s="50"/>
-    </row>
-    <row r="141" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A142" s="268" t="s">
+      <c r="B142" s="73">
+        <f>SUM(B134:C141)</f>
+        <v>415734.79000000283</v>
+      </c>
+      <c r="D142" s="66"/>
+      <c r="E142" s="50"/>
+      <c r="F142" s="50"/>
+    </row>
+    <row r="143" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A144" s="283" t="s">
         <v>125</v>
       </c>
-      <c r="B142" s="268"/>
-      <c r="C142" s="268"/>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A143" s="268"/>
-      <c r="B143" s="268"/>
-      <c r="C143" s="268"/>
-    </row>
-    <row r="144" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A144" s="74" t="s">
-        <v>243</v>
-      </c>
-      <c r="B144" s="115">
-        <v>200000</v>
-      </c>
-      <c r="C144" s="75"/>
-      <c r="D144" s="56"/>
-    </row>
-    <row r="145" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A145" s="74" t="s">
-        <v>246</v>
-      </c>
-      <c r="B145" s="115">
-        <v>320000</v>
-      </c>
-      <c r="C145" s="75"/>
-      <c r="D145" s="56"/>
-    </row>
-    <row r="146" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="74" t="s">
-        <v>247</v>
-      </c>
-      <c r="B146" s="115">
-        <v>208000</v>
-      </c>
+      <c r="B144" s="283"/>
+      <c r="C144" s="283"/>
+    </row>
+    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A145" s="283"/>
+      <c r="B145" s="283"/>
+      <c r="C145" s="283"/>
+    </row>
+    <row r="146" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A146" s="74"/>
+      <c r="B146" s="115"/>
       <c r="C146" s="75"/>
       <c r="D146" s="56"/>
     </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A147" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="B147" s="77">
-        <f>SUM(B144:B146)</f>
-        <v>728000</v>
-      </c>
-      <c r="C147" s="78"/>
-    </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M148" s="79"/>
+    <row r="147" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A147" s="74"/>
+      <c r="B147" s="115"/>
+      <c r="C147" s="75"/>
+      <c r="D147" s="56"/>
+    </row>
+    <row r="148" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="74"/>
+      <c r="B148" s="115"/>
+      <c r="C148" s="75"/>
+      <c r="D148" s="56"/>
+    </row>
+    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A149" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="B149" s="77">
+        <f>SUM(B146:B148)</f>
+        <v>0</v>
+      </c>
+      <c r="C149" s="78"/>
+    </row>
+    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M150" s="79"/>
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="A65:B65"/>
-    <mergeCell ref="A67:B67"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="D94:D95"/>
-    <mergeCell ref="E94:E95"/>
-    <mergeCell ref="A85:B85"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="A66:B66"/>
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="A94:B95"/>
-    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="A144:C145"/>
+    <mergeCell ref="A117:B119"/>
+    <mergeCell ref="A129:B131"/>
+    <mergeCell ref="A125:B127"/>
+    <mergeCell ref="A105:B107"/>
+    <mergeCell ref="A121:B123"/>
+    <mergeCell ref="A109:B111"/>
+    <mergeCell ref="A113:B115"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="A71:B71"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B8:C10"/>
     <mergeCell ref="A13:E16"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A52:B52"/>
     <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A58:B58"/>
     <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="A142:C143"/>
-    <mergeCell ref="A115:B117"/>
-    <mergeCell ref="A127:B129"/>
-    <mergeCell ref="A123:B125"/>
-    <mergeCell ref="A111:B113"/>
-    <mergeCell ref="A119:B121"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="D88:D89"/>
+    <mergeCell ref="E88:E89"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="A88:B89"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="A72:B72"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" scale="90" orientation="portrait" r:id="rId1"/>
@@ -4245,55 +4193,55 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{533DB7A7-09F4-49CF-B824-70F15C1FF525}">
   <dimension ref="A1:Q135"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.33203125" customWidth="1"/>
-    <col min="2" max="2" width="25.5546875" customWidth="1"/>
-    <col min="3" max="3" width="0.109375" customWidth="1"/>
-    <col min="4" max="4" width="8.44140625" customWidth="1"/>
-    <col min="5" max="5" width="14.109375" customWidth="1"/>
-    <col min="6" max="6" width="12.33203125" customWidth="1"/>
-    <col min="7" max="7" width="10.5546875" customWidth="1"/>
-    <col min="8" max="8" width="9.5546875" customWidth="1"/>
-    <col min="9" max="9" width="12.44140625" customWidth="1"/>
-    <col min="10" max="11" width="16.33203125" customWidth="1"/>
-    <col min="12" max="12" width="12.33203125" customWidth="1"/>
-    <col min="13" max="13" width="16.109375" customWidth="1"/>
-    <col min="14" max="14" width="14.6640625" customWidth="1"/>
-    <col min="15" max="15" width="14.33203125" customWidth="1"/>
-    <col min="16" max="16" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.28515625" customWidth="1"/>
+    <col min="2" max="2" width="25.5703125" customWidth="1"/>
+    <col min="3" max="3" width="0.140625" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.5703125" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" customWidth="1"/>
+    <col min="9" max="9" width="12.42578125" customWidth="1"/>
+    <col min="10" max="11" width="16.28515625" customWidth="1"/>
+    <col min="12" max="12" width="12.28515625" customWidth="1"/>
+    <col min="13" max="13" width="16.140625" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" customWidth="1"/>
+    <col min="16" max="16" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="12" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="93"/>
       <c r="B1" s="94"/>
       <c r="C1" s="94"/>
-      <c r="D1" s="302"/>
-      <c r="E1" s="302"/>
-      <c r="F1" s="302"/>
-      <c r="G1" s="302"/>
-      <c r="H1" s="302"/>
-      <c r="I1" s="302"/>
-      <c r="J1" s="302"/>
-      <c r="K1" s="302"/>
-      <c r="L1" s="302"/>
-      <c r="M1" s="302"/>
-      <c r="N1" s="302"/>
+      <c r="D1" s="286"/>
+      <c r="E1" s="286"/>
+      <c r="F1" s="286"/>
+      <c r="G1" s="286"/>
+      <c r="H1" s="286"/>
+      <c r="I1" s="286"/>
+      <c r="J1" s="286"/>
+      <c r="K1" s="286"/>
+      <c r="L1" s="286"/>
+      <c r="M1" s="286"/>
+      <c r="N1" s="286"/>
       <c r="O1" s="95"/>
     </row>
-    <row r="2" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="96"/>
       <c r="B2" s="97"/>
       <c r="C2" s="98"/>
       <c r="D2" s="98" t="s">
         <v>126</v>
       </c>
-      <c r="E2" s="324">
+      <c r="E2" s="310">
         <v>4500000</v>
       </c>
-      <c r="F2" s="324"/>
+      <c r="F2" s="310"/>
       <c r="G2" s="98"/>
       <c r="H2" s="98"/>
       <c r="I2" s="98" t="s">
@@ -4305,7 +4253,7 @@
       </c>
       <c r="K2" s="99"/>
       <c r="L2" s="99" t="s">
-        <v>254</v>
+        <v>228</v>
       </c>
       <c r="M2" s="99">
         <v>5946930.7699999996</v>
@@ -4317,7 +4265,7 @@
         <v>13312274.1</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="102"/>
       <c r="B3" s="103"/>
       <c r="C3" s="103"/>
@@ -4335,241 +4283,241 @@
       <c r="O3" s="106"/>
       <c r="P3" s="80"/>
     </row>
-    <row r="4" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="303" t="s">
+    <row r="4" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="287" t="s">
         <v>159</v>
       </c>
-      <c r="B4" s="304"/>
-      <c r="C4" s="304"/>
-      <c r="D4" s="304"/>
-      <c r="E4" s="304"/>
-      <c r="F4" s="304"/>
-      <c r="G4" s="304"/>
-      <c r="H4" s="304"/>
-      <c r="I4" s="304"/>
-      <c r="J4" s="304"/>
-      <c r="K4" s="304"/>
-      <c r="L4" s="304"/>
-      <c r="M4" s="304"/>
-      <c r="N4" s="304"/>
-      <c r="O4" s="305"/>
+      <c r="B4" s="288"/>
+      <c r="C4" s="288"/>
+      <c r="D4" s="288"/>
+      <c r="E4" s="288"/>
+      <c r="F4" s="288"/>
+      <c r="G4" s="288"/>
+      <c r="H4" s="288"/>
+      <c r="I4" s="288"/>
+      <c r="J4" s="288"/>
+      <c r="K4" s="288"/>
+      <c r="L4" s="288"/>
+      <c r="M4" s="288"/>
+      <c r="N4" s="288"/>
+      <c r="O4" s="289"/>
       <c r="P4" s="80"/>
     </row>
-    <row r="5" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="306"/>
-      <c r="B5" s="307"/>
-      <c r="C5" s="307"/>
-      <c r="D5" s="307"/>
-      <c r="E5" s="307"/>
-      <c r="F5" s="307"/>
-      <c r="G5" s="307"/>
-      <c r="H5" s="307"/>
-      <c r="I5" s="307"/>
-      <c r="J5" s="307"/>
-      <c r="K5" s="307"/>
-      <c r="L5" s="307"/>
-      <c r="M5" s="307"/>
-      <c r="N5" s="307"/>
-      <c r="O5" s="308"/>
+    <row r="5" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="290"/>
+      <c r="B5" s="291"/>
+      <c r="C5" s="291"/>
+      <c r="D5" s="291"/>
+      <c r="E5" s="291"/>
+      <c r="F5" s="291"/>
+      <c r="G5" s="291"/>
+      <c r="H5" s="291"/>
+      <c r="I5" s="291"/>
+      <c r="J5" s="291"/>
+      <c r="K5" s="291"/>
+      <c r="L5" s="291"/>
+      <c r="M5" s="291"/>
+      <c r="N5" s="291"/>
+      <c r="O5" s="292"/>
       <c r="P5" s="80"/>
     </row>
-    <row r="6" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="306"/>
-      <c r="B6" s="307"/>
-      <c r="C6" s="307"/>
-      <c r="D6" s="307"/>
-      <c r="E6" s="307"/>
-      <c r="F6" s="307"/>
-      <c r="G6" s="307"/>
-      <c r="H6" s="307"/>
-      <c r="I6" s="307"/>
-      <c r="J6" s="307"/>
-      <c r="K6" s="307"/>
-      <c r="L6" s="307"/>
-      <c r="M6" s="307"/>
-      <c r="N6" s="307"/>
-      <c r="O6" s="308"/>
+    <row r="6" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="290"/>
+      <c r="B6" s="291"/>
+      <c r="C6" s="291"/>
+      <c r="D6" s="291"/>
+      <c r="E6" s="291"/>
+      <c r="F6" s="291"/>
+      <c r="G6" s="291"/>
+      <c r="H6" s="291"/>
+      <c r="I6" s="291"/>
+      <c r="J6" s="291"/>
+      <c r="K6" s="291"/>
+      <c r="L6" s="291"/>
+      <c r="M6" s="291"/>
+      <c r="N6" s="291"/>
+      <c r="O6" s="292"/>
       <c r="P6" s="80"/>
     </row>
-    <row r="7" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="306"/>
-      <c r="B7" s="307"/>
-      <c r="C7" s="307"/>
-      <c r="D7" s="307"/>
-      <c r="E7" s="307"/>
-      <c r="F7" s="307"/>
-      <c r="G7" s="307"/>
-      <c r="H7" s="307"/>
-      <c r="I7" s="307"/>
-      <c r="J7" s="307"/>
-      <c r="K7" s="307"/>
-      <c r="L7" s="307"/>
-      <c r="M7" s="307"/>
-      <c r="N7" s="307"/>
-      <c r="O7" s="308"/>
+    <row r="7" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="290"/>
+      <c r="B7" s="291"/>
+      <c r="C7" s="291"/>
+      <c r="D7" s="291"/>
+      <c r="E7" s="291"/>
+      <c r="F7" s="291"/>
+      <c r="G7" s="291"/>
+      <c r="H7" s="291"/>
+      <c r="I7" s="291"/>
+      <c r="J7" s="291"/>
+      <c r="K7" s="291"/>
+      <c r="L7" s="291"/>
+      <c r="M7" s="291"/>
+      <c r="N7" s="291"/>
+      <c r="O7" s="292"/>
       <c r="P7" s="80"/>
     </row>
-    <row r="8" spans="1:17" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="309"/>
-      <c r="B8" s="310"/>
-      <c r="C8" s="310"/>
-      <c r="D8" s="310"/>
-      <c r="E8" s="310"/>
-      <c r="F8" s="310"/>
-      <c r="G8" s="310"/>
-      <c r="H8" s="310"/>
-      <c r="I8" s="310"/>
-      <c r="J8" s="310"/>
-      <c r="K8" s="310"/>
-      <c r="L8" s="310"/>
-      <c r="M8" s="310"/>
-      <c r="N8" s="310"/>
-      <c r="O8" s="311"/>
-    </row>
-    <row r="9" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="318" t="s">
+    <row r="8" spans="1:17" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="293"/>
+      <c r="B8" s="294"/>
+      <c r="C8" s="294"/>
+      <c r="D8" s="294"/>
+      <c r="E8" s="294"/>
+      <c r="F8" s="294"/>
+      <c r="G8" s="294"/>
+      <c r="H8" s="294"/>
+      <c r="I8" s="294"/>
+      <c r="J8" s="294"/>
+      <c r="K8" s="294"/>
+      <c r="L8" s="294"/>
+      <c r="M8" s="294"/>
+      <c r="N8" s="294"/>
+      <c r="O8" s="295"/>
+    </row>
+    <row r="9" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="304" t="s">
         <v>157</v>
       </c>
-      <c r="B9" s="319"/>
-      <c r="C9" s="319"/>
-      <c r="D9" s="319"/>
-      <c r="E9" s="319"/>
-      <c r="F9" s="319"/>
-      <c r="G9" s="319"/>
-      <c r="H9" s="319"/>
-      <c r="I9" s="319"/>
-      <c r="J9" s="319"/>
-      <c r="K9" s="319"/>
-      <c r="L9" s="319"/>
-      <c r="M9" s="319"/>
-      <c r="N9" s="319"/>
-      <c r="O9" s="320"/>
-    </row>
-    <row r="10" spans="1:17" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="291" t="s">
-        <v>216</v>
-      </c>
-      <c r="B10" s="292"/>
-      <c r="C10" s="292"/>
-      <c r="D10" s="292"/>
-      <c r="E10" s="292"/>
-      <c r="F10" s="292"/>
-      <c r="G10" s="292"/>
-      <c r="H10" s="292"/>
-      <c r="I10" s="292"/>
-      <c r="J10" s="292"/>
-      <c r="K10" s="292"/>
-      <c r="L10" s="292"/>
-      <c r="M10" s="292"/>
-      <c r="N10" s="292"/>
-      <c r="O10" s="293"/>
-    </row>
-    <row r="11" spans="1:17" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="294" t="s">
-        <v>217</v>
-      </c>
-      <c r="B11" s="295"/>
-      <c r="C11" s="295"/>
-      <c r="D11" s="295"/>
-      <c r="E11" s="295"/>
-      <c r="F11" s="295"/>
-      <c r="G11" s="295"/>
-      <c r="H11" s="295"/>
-      <c r="I11" s="295"/>
-      <c r="J11" s="295"/>
-      <c r="K11" s="295"/>
-      <c r="L11" s="295"/>
-      <c r="M11" s="295"/>
-      <c r="N11" s="295"/>
-      <c r="O11" s="296"/>
-    </row>
-    <row r="12" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="321" t="s">
+      <c r="B9" s="305"/>
+      <c r="C9" s="305"/>
+      <c r="D9" s="305"/>
+      <c r="E9" s="305"/>
+      <c r="F9" s="305"/>
+      <c r="G9" s="305"/>
+      <c r="H9" s="305"/>
+      <c r="I9" s="305"/>
+      <c r="J9" s="305"/>
+      <c r="K9" s="305"/>
+      <c r="L9" s="305"/>
+      <c r="M9" s="305"/>
+      <c r="N9" s="305"/>
+      <c r="O9" s="306"/>
+    </row>
+    <row r="10" spans="1:17" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="315" t="s">
+        <v>214</v>
+      </c>
+      <c r="B10" s="316"/>
+      <c r="C10" s="316"/>
+      <c r="D10" s="316"/>
+      <c r="E10" s="316"/>
+      <c r="F10" s="316"/>
+      <c r="G10" s="316"/>
+      <c r="H10" s="316"/>
+      <c r="I10" s="316"/>
+      <c r="J10" s="316"/>
+      <c r="K10" s="316"/>
+      <c r="L10" s="316"/>
+      <c r="M10" s="316"/>
+      <c r="N10" s="316"/>
+      <c r="O10" s="317"/>
+    </row>
+    <row r="11" spans="1:17" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="318" t="s">
+        <v>215</v>
+      </c>
+      <c r="B11" s="319"/>
+      <c r="C11" s="319"/>
+      <c r="D11" s="319"/>
+      <c r="E11" s="319"/>
+      <c r="F11" s="319"/>
+      <c r="G11" s="319"/>
+      <c r="H11" s="319"/>
+      <c r="I11" s="319"/>
+      <c r="J11" s="319"/>
+      <c r="K11" s="319"/>
+      <c r="L11" s="319"/>
+      <c r="M11" s="319"/>
+      <c r="N11" s="319"/>
+      <c r="O11" s="320"/>
+    </row>
+    <row r="12" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="307" t="s">
         <v>158</v>
       </c>
-      <c r="B12" s="322"/>
-      <c r="C12" s="322"/>
-      <c r="D12" s="322"/>
-      <c r="E12" s="322"/>
-      <c r="F12" s="322"/>
-      <c r="G12" s="322"/>
-      <c r="H12" s="322"/>
-      <c r="I12" s="322"/>
-      <c r="J12" s="322"/>
-      <c r="K12" s="322"/>
-      <c r="L12" s="322"/>
-      <c r="M12" s="322"/>
-      <c r="N12" s="322"/>
-      <c r="O12" s="323"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A13" s="312" t="s">
+      <c r="B12" s="308"/>
+      <c r="C12" s="308"/>
+      <c r="D12" s="308"/>
+      <c r="E12" s="308"/>
+      <c r="F12" s="308"/>
+      <c r="G12" s="308"/>
+      <c r="H12" s="308"/>
+      <c r="I12" s="308"/>
+      <c r="J12" s="308"/>
+      <c r="K12" s="308"/>
+      <c r="L12" s="308"/>
+      <c r="M12" s="308"/>
+      <c r="N12" s="308"/>
+      <c r="O12" s="309"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" s="296" t="s">
         <v>128</v>
       </c>
-      <c r="B13" s="314" t="s">
+      <c r="B13" s="298" t="s">
         <v>129</v>
       </c>
-      <c r="C13" s="314" t="s">
+      <c r="C13" s="298" t="s">
         <v>130</v>
       </c>
-      <c r="D13" s="314" t="s">
+      <c r="D13" s="298" t="s">
         <v>131</v>
       </c>
-      <c r="E13" s="289" t="s">
+      <c r="E13" s="300" t="s">
         <v>132</v>
       </c>
-      <c r="F13" s="314" t="s">
+      <c r="F13" s="298" t="s">
         <v>133</v>
       </c>
-      <c r="G13" s="316" t="s">
+      <c r="G13" s="302" t="s">
         <v>134</v>
       </c>
-      <c r="H13" s="289" t="s">
+      <c r="H13" s="300" t="s">
         <v>135</v>
       </c>
-      <c r="I13" s="289" t="s">
+      <c r="I13" s="300" t="s">
         <v>127</v>
       </c>
-      <c r="J13" s="289" t="s">
+      <c r="J13" s="300" t="s">
         <v>126</v>
       </c>
-      <c r="K13" s="299" t="s">
-        <v>253</v>
-      </c>
-      <c r="L13" s="325" t="s">
+      <c r="K13" s="323" t="s">
+        <v>227</v>
+      </c>
+      <c r="L13" s="311" t="s">
         <v>174</v>
       </c>
-      <c r="M13" s="287" t="s">
+      <c r="M13" s="313" t="s">
         <v>180</v>
       </c>
       <c r="N13" s="143" t="s">
-        <v>211</v>
-      </c>
-      <c r="O13" s="297" t="s">
+        <v>209</v>
+      </c>
+      <c r="O13" s="321" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="313"/>
-      <c r="B14" s="315"/>
-      <c r="C14" s="315"/>
-      <c r="D14" s="315"/>
-      <c r="E14" s="290"/>
-      <c r="F14" s="315"/>
-      <c r="G14" s="317"/>
-      <c r="H14" s="290"/>
-      <c r="I14" s="290"/>
-      <c r="J14" s="290"/>
-      <c r="K14" s="300"/>
-      <c r="L14" s="326"/>
-      <c r="M14" s="288"/>
+    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="297"/>
+      <c r="B14" s="299"/>
+      <c r="C14" s="299"/>
+      <c r="D14" s="299"/>
+      <c r="E14" s="301"/>
+      <c r="F14" s="299"/>
+      <c r="G14" s="303"/>
+      <c r="H14" s="301"/>
+      <c r="I14" s="301"/>
+      <c r="J14" s="301"/>
+      <c r="K14" s="324"/>
+      <c r="L14" s="312"/>
+      <c r="M14" s="314"/>
       <c r="N14" s="144" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 17/09</v>
       </c>
-      <c r="O14" s="298"/>
-    </row>
-    <row r="15" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O14" s="322"/>
+    </row>
+    <row r="15" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="129">
         <v>1</v>
       </c>
@@ -4581,11 +4529,11 @@
         <v>1.37</v>
       </c>
       <c r="E15" s="83">
-        <v>246600.01</v>
+        <v>287700.01</v>
       </c>
       <c r="F15" s="84">
         <f>E15</f>
-        <v>246600.01</v>
+        <v>287700.01</v>
       </c>
       <c r="G15" s="85">
         <f t="shared" ref="G15:G78" si="0">E15-F15</f>
@@ -4621,7 +4569,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="187">
         <v>2</v>
       </c>
@@ -4633,16 +4581,16 @@
         <v>1.18</v>
       </c>
       <c r="E16" s="210">
-        <v>3823811.02</v>
+        <v>4186325.02</v>
       </c>
       <c r="F16" s="210"/>
       <c r="G16" s="211">
         <f t="shared" si="0"/>
-        <v>3823811.02</v>
+        <v>4186325.02</v>
       </c>
       <c r="H16" s="211">
         <f t="shared" ref="H16:H79" si="3">IF(G16&gt;0,G16*3%,0)</f>
-        <v>114714.3306</v>
+        <v>125589.7506</v>
       </c>
       <c r="I16" s="212">
         <f t="shared" ref="I16:I46" si="4">J$2*D16/100</f>
@@ -4660,11 +4608,11 @@
       <c r="M16" s="213"/>
       <c r="N16" s="214">
         <f>ROUND(SUM(G16:M16),0) + P16</f>
-        <v>4186325.02</v>
+        <v>4559715.0199999996</v>
       </c>
       <c r="O16" s="215">
         <f t="shared" si="2"/>
-        <v>4311915.0199999996</v>
+        <v>4696506.0199999996</v>
       </c>
       <c r="P16" s="50">
         <f>P15+0.01</f>
@@ -4674,7 +4622,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="129">
         <v>3</v>
       </c>
@@ -4686,11 +4634,11 @@
         <v>0.74</v>
       </c>
       <c r="E17" s="83">
-        <v>133200.03</v>
+        <v>155400.03</v>
       </c>
       <c r="F17" s="84">
         <f>E17</f>
-        <v>133200.03</v>
+        <v>155400.03</v>
       </c>
       <c r="G17" s="85">
         <f t="shared" si="0"/>
@@ -4727,7 +4675,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="130">
         <v>4</v>
       </c>
@@ -4739,11 +4687,11 @@
         <v>1.47</v>
       </c>
       <c r="E18" s="84">
-        <v>264600.03999999998</v>
+        <v>308700.03999999998</v>
       </c>
       <c r="F18" s="84">
         <f>E18</f>
-        <v>264600.03999999998</v>
+        <v>308700.03999999998</v>
       </c>
       <c r="G18" s="111">
         <f t="shared" si="0"/>
@@ -4780,7 +4728,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="129">
         <v>5</v>
       </c>
@@ -4792,18 +4740,18 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E19" s="84">
-        <v>196060.05</v>
+        <v>229318.05</v>
       </c>
       <c r="F19" s="84">
         <v>201942.01</v>
       </c>
       <c r="G19" s="85">
         <f t="shared" si="0"/>
-        <v>-5881.960000000021</v>
+        <v>27376.039999999979</v>
       </c>
       <c r="H19" s="85">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>821.28119999999933</v>
       </c>
       <c r="I19" s="125">
         <f t="shared" si="4"/>
@@ -4821,18 +4769,18 @@
       <c r="M19" s="147"/>
       <c r="N19" s="86">
         <f t="shared" si="6"/>
-        <v>229318.05</v>
+        <v>263397.05</v>
       </c>
       <c r="O19" s="139">
         <f t="shared" si="2"/>
-        <v>236198.05</v>
+        <v>271299.05</v>
       </c>
       <c r="P19" s="50">
         <f t="shared" si="7"/>
         <v>0.05</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="129">
         <v>6</v>
       </c>
@@ -4844,14 +4792,14 @@
         <v>1.35</v>
       </c>
       <c r="E20" s="83">
-        <v>241582.06</v>
-      </c>
-      <c r="F20" s="84">
-        <v>242000.06</v>
+        <v>283082.06</v>
+      </c>
+      <c r="F20" s="338">
+        <v>284000.06</v>
       </c>
       <c r="G20" s="85">
         <f t="shared" si="0"/>
-        <v>-418</v>
+        <v>-918</v>
       </c>
       <c r="H20" s="85">
         <f t="shared" si="3"/>
@@ -4873,18 +4821,18 @@
       <c r="M20" s="147"/>
       <c r="N20" s="86">
         <f t="shared" si="6"/>
-        <v>283082.06</v>
+        <v>282582.06</v>
       </c>
       <c r="O20" s="139">
         <f t="shared" si="2"/>
-        <v>291574.06</v>
+        <v>291059.06</v>
       </c>
       <c r="P20" s="50">
         <f t="shared" si="7"/>
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="129">
         <v>7</v>
       </c>
@@ -4896,11 +4844,11 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E21" s="83">
-        <v>201600.07</v>
+        <v>235200.07</v>
       </c>
       <c r="F21" s="84">
         <f>E21</f>
-        <v>201600.07</v>
+        <v>235200.07</v>
       </c>
       <c r="G21" s="85">
         <f t="shared" si="0"/>
@@ -4937,7 +4885,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="129">
         <v>8</v>
       </c>
@@ -4949,11 +4897,11 @@
         <v>0.82</v>
       </c>
       <c r="E22" s="83">
-        <v>147600.07999999999</v>
+        <v>172200.08</v>
       </c>
       <c r="F22" s="84">
         <f>E22</f>
-        <v>147600.07999999999</v>
+        <v>172200.08</v>
       </c>
       <c r="G22" s="85">
         <f t="shared" si="0"/>
@@ -4990,7 +4938,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="129">
         <v>9</v>
       </c>
@@ -5002,18 +4950,18 @@
         <v>0.82</v>
       </c>
       <c r="E23" s="83">
-        <v>143660.09</v>
+        <v>167890.09</v>
       </c>
       <c r="F23" s="84">
         <v>147970.09</v>
       </c>
       <c r="G23" s="85">
         <f t="shared" si="0"/>
-        <v>-4310</v>
+        <v>19920</v>
       </c>
       <c r="H23" s="85">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>597.6</v>
       </c>
       <c r="I23" s="125">
         <f t="shared" si="4"/>
@@ -5031,18 +4979,18 @@
       <c r="M23" s="147"/>
       <c r="N23" s="86">
         <f t="shared" si="6"/>
-        <v>167890.09</v>
+        <v>192718.09</v>
       </c>
       <c r="O23" s="139">
         <f t="shared" si="2"/>
-        <v>172927.09</v>
+        <v>198500.09</v>
       </c>
       <c r="P23" s="50">
         <f t="shared" si="7"/>
         <v>0.09</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="129">
         <v>10</v>
       </c>
@@ -5054,18 +5002,18 @@
         <v>1.34</v>
       </c>
       <c r="E24" s="83">
-        <v>248436.1</v>
+        <v>288853.09999999998</v>
       </c>
       <c r="F24" s="84">
         <v>241200.1</v>
       </c>
       <c r="G24" s="85">
         <f t="shared" si="0"/>
-        <v>7236</v>
+        <v>47652.999999999971</v>
       </c>
       <c r="H24" s="85">
         <f t="shared" si="3"/>
-        <v>217.07999999999998</v>
+        <v>1429.589999999999</v>
       </c>
       <c r="I24" s="125">
         <f t="shared" si="4"/>
@@ -5083,18 +5031,18 @@
       <c r="M24" s="147"/>
       <c r="N24" s="86">
         <f t="shared" si="6"/>
-        <v>288853.09999999998</v>
+        <v>330483.09999999998</v>
       </c>
       <c r="O24" s="139">
         <f t="shared" si="2"/>
-        <v>297519.09999999998</v>
+        <v>340397.1</v>
       </c>
       <c r="P24" s="50">
         <f t="shared" si="7"/>
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="129">
         <v>11</v>
       </c>
@@ -5106,11 +5054,11 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E25" s="83">
-        <v>201600.11</v>
-      </c>
-      <c r="F25" s="84">
+        <v>235200.11</v>
+      </c>
+      <c r="F25" s="338">
         <f>E25</f>
-        <v>201600.11</v>
+        <v>235200.11</v>
       </c>
       <c r="G25" s="85">
         <f t="shared" si="0"/>
@@ -5147,7 +5095,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="187">
         <v>12</v>
       </c>
@@ -5159,18 +5107,18 @@
         <v>1.17</v>
       </c>
       <c r="E26" s="210">
-        <v>4819091.12</v>
+        <v>5209364.12</v>
       </c>
       <c r="F26" s="210">
         <v>0</v>
       </c>
       <c r="G26" s="211">
         <f t="shared" si="0"/>
-        <v>4819091.12</v>
+        <v>5209364.12</v>
       </c>
       <c r="H26" s="211">
         <f t="shared" si="3"/>
-        <v>144572.73360000001</v>
+        <v>156280.92360000001</v>
       </c>
       <c r="I26" s="212">
         <f t="shared" si="4"/>
@@ -5188,18 +5136,18 @@
       <c r="M26" s="213"/>
       <c r="N26" s="214">
         <f t="shared" si="6"/>
-        <v>5209364.12</v>
+        <v>5611345.1200000001</v>
       </c>
       <c r="O26" s="215">
         <f t="shared" si="2"/>
-        <v>5365645.12</v>
+        <v>5779685.1200000001</v>
       </c>
       <c r="P26" s="50">
         <f t="shared" si="7"/>
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="129">
         <v>13</v>
       </c>
@@ -5211,11 +5159,11 @@
         <v>1.35</v>
       </c>
       <c r="E27" s="83">
-        <v>243000.13</v>
+        <v>283500.13</v>
       </c>
       <c r="F27" s="84">
         <f>E27</f>
-        <v>243000.13</v>
+        <v>283500.13</v>
       </c>
       <c r="G27" s="85">
         <f t="shared" si="0"/>
@@ -5252,7 +5200,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="129">
         <v>14</v>
       </c>
@@ -5264,16 +5212,16 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E28" s="83">
-        <v>591280.14</v>
+        <v>844219.14</v>
       </c>
       <c r="F28" s="84"/>
       <c r="G28" s="85">
         <f t="shared" si="0"/>
-        <v>591280.14</v>
+        <v>844219.14</v>
       </c>
       <c r="H28" s="85">
         <f t="shared" si="3"/>
-        <v>17738.404200000001</v>
+        <v>25326.574199999999</v>
       </c>
       <c r="I28" s="125">
         <f t="shared" si="4"/>
@@ -5291,18 +5239,18 @@
       <c r="M28" s="147"/>
       <c r="N28" s="86">
         <f t="shared" si="6"/>
-        <v>844219.14</v>
+        <v>1104746.1399999999</v>
       </c>
       <c r="O28" s="139">
         <f t="shared" si="2"/>
-        <v>869546.14</v>
+        <v>1137888.1399999999</v>
       </c>
       <c r="P28" s="50">
         <f t="shared" si="7"/>
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="130">
         <v>15</v>
       </c>
@@ -5314,11 +5262,11 @@
         <v>0.82</v>
       </c>
       <c r="E29" s="84">
-        <v>152028.15</v>
+        <v>172200.15</v>
       </c>
       <c r="F29" s="84">
         <f>E29</f>
-        <v>152028.15</v>
+        <v>172200.15</v>
       </c>
       <c r="G29" s="85">
         <f t="shared" si="0"/>
@@ -5355,7 +5303,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="129">
         <v>16</v>
       </c>
@@ -5367,11 +5315,11 @@
         <v>0.82</v>
       </c>
       <c r="E30" s="83">
-        <v>147600.16</v>
+        <v>172200.16</v>
       </c>
       <c r="F30" s="84">
         <f>E30</f>
-        <v>147600.16</v>
+        <v>172200.16</v>
       </c>
       <c r="G30" s="85">
         <f t="shared" si="0"/>
@@ -5408,7 +5356,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="129">
         <v>17</v>
       </c>
@@ -5420,11 +5368,11 @@
         <v>1.34</v>
       </c>
       <c r="E31" s="83">
-        <v>313104.17</v>
+        <v>281400.17</v>
       </c>
       <c r="F31" s="84">
         <f>E31</f>
-        <v>313104.17</v>
+        <v>281400.17</v>
       </c>
       <c r="G31" s="85">
         <f t="shared" si="0"/>
@@ -5461,7 +5409,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="130">
         <v>18</v>
       </c>
@@ -5473,11 +5421,11 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E32" s="84">
-        <v>201600.18</v>
+        <v>235200.18</v>
       </c>
       <c r="F32" s="84">
         <f>E32</f>
-        <v>201600.18</v>
+        <v>235200.18</v>
       </c>
       <c r="G32" s="111">
         <f t="shared" si="0"/>
@@ -5514,11 +5462,11 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A33" s="239">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A33" s="235">
         <v>19</v>
       </c>
-      <c r="B33" s="240" t="s">
+      <c r="B33" s="236" t="s">
         <v>21</v>
       </c>
       <c r="C33" s="87"/>
@@ -5526,18 +5474,18 @@
         <v>1.17</v>
       </c>
       <c r="E33" s="83">
-        <v>176820.19</v>
+        <v>211920.19</v>
       </c>
       <c r="F33" s="84">
         <v>210600.19</v>
       </c>
       <c r="G33" s="85">
         <f t="shared" si="0"/>
-        <v>-33780</v>
+        <v>1320</v>
       </c>
       <c r="H33" s="85">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>39.6</v>
       </c>
       <c r="I33" s="125">
         <f t="shared" si="4"/>
@@ -5555,11 +5503,11 @@
       <c r="M33" s="147"/>
       <c r="N33" s="86">
         <f t="shared" si="6"/>
-        <v>211920.19</v>
+        <v>247060.19</v>
       </c>
       <c r="O33" s="139">
         <f t="shared" si="2"/>
-        <v>218278.19</v>
+        <v>254472.19</v>
       </c>
       <c r="P33" s="50">
         <f>P32+0.01</f>
@@ -5569,7 +5517,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="131">
         <v>20</v>
       </c>
@@ -5581,14 +5529,14 @@
         <v>1.35</v>
       </c>
       <c r="E34" s="122">
-        <v>1145438.2</v>
+        <v>1199638.2</v>
       </c>
       <c r="F34" s="122">
         <v>352600</v>
       </c>
       <c r="G34" s="123">
         <f t="shared" si="0"/>
-        <v>792838.2</v>
+        <v>847038.2</v>
       </c>
       <c r="H34" s="123"/>
       <c r="I34" s="128">
@@ -5609,21 +5557,21 @@
       </c>
       <c r="N34" s="124">
         <f t="shared" si="6"/>
-        <v>1199638.2</v>
+        <v>1253838.2</v>
       </c>
       <c r="O34" s="141">
         <f t="shared" si="2"/>
-        <v>1235627.2</v>
+        <v>1291453.2</v>
       </c>
       <c r="P34" s="50">
         <f t="shared" ref="P34:P97" si="8">P33+0.01</f>
         <v>0.20000000000000004</v>
       </c>
       <c r="Q34" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="130">
         <v>21</v>
       </c>
@@ -5635,11 +5583,11 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E35" s="84">
-        <v>201600.21</v>
+        <v>235200.21</v>
       </c>
       <c r="F35" s="84">
         <f>E35</f>
-        <v>201600.21</v>
+        <v>235200.21</v>
       </c>
       <c r="G35" s="111">
         <f t="shared" si="0"/>
@@ -5676,7 +5624,7 @@
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="130">
         <f>A35+1</f>
         <v>22</v>
@@ -5689,11 +5637,11 @@
         <v>0.82</v>
       </c>
       <c r="E36" s="83">
-        <v>147600.22</v>
+        <v>172200.22</v>
       </c>
       <c r="F36" s="84">
         <f>E36</f>
-        <v>147600.22</v>
+        <v>172200.22</v>
       </c>
       <c r="G36" s="85">
         <f t="shared" si="0"/>
@@ -5730,7 +5678,7 @@
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="129">
         <f t="shared" ref="A37:A100" si="10">A36+1</f>
         <v>23</v>
@@ -5743,11 +5691,11 @@
         <v>0.82</v>
       </c>
       <c r="E37" s="83">
-        <v>147600.23000000001</v>
+        <v>172200.23</v>
       </c>
       <c r="F37" s="84">
         <f>E37</f>
-        <v>147600.23000000001</v>
+        <v>172200.23</v>
       </c>
       <c r="G37" s="85">
         <f t="shared" si="0"/>
@@ -5784,7 +5732,7 @@
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="129">
         <f t="shared" si="10"/>
         <v>24</v>
@@ -5797,18 +5745,18 @@
         <v>1.34</v>
       </c>
       <c r="E38" s="83">
-        <v>475529.24</v>
+        <v>529836.24</v>
       </c>
       <c r="F38" s="84">
         <v>234329.34</v>
       </c>
       <c r="G38" s="85">
         <f t="shared" si="0"/>
-        <v>241199.9</v>
+        <v>295506.90000000002</v>
       </c>
       <c r="H38" s="85">
         <f t="shared" si="3"/>
-        <v>7235.9969999999994</v>
+        <v>8865.2070000000003</v>
       </c>
       <c r="I38" s="125">
         <f t="shared" si="4"/>
@@ -5826,18 +5774,18 @@
       <c r="M38" s="147"/>
       <c r="N38" s="86">
         <f t="shared" si="6"/>
-        <v>529836.24</v>
+        <v>585772.24</v>
       </c>
       <c r="O38" s="139">
         <f t="shared" si="9"/>
-        <v>545731.24</v>
+        <v>603345.24</v>
       </c>
       <c r="P38" s="50">
         <f t="shared" si="8"/>
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="129">
         <f t="shared" si="10"/>
         <v>25</v>
@@ -5850,18 +5798,18 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E39" s="83">
-        <v>201600.25</v>
+        <v>442848.25</v>
       </c>
       <c r="F39" s="84">
         <v>0</v>
       </c>
       <c r="G39" s="85">
         <f t="shared" si="0"/>
-        <v>201600.25</v>
+        <v>442848.25</v>
       </c>
       <c r="H39" s="85">
         <f t="shared" si="3"/>
-        <v>6048.0074999999997</v>
+        <v>13285.4475</v>
       </c>
       <c r="I39" s="125">
         <f t="shared" si="4"/>
@@ -5879,18 +5827,18 @@
       <c r="M39" s="147"/>
       <c r="N39" s="86">
         <f t="shared" si="6"/>
-        <v>442848.25</v>
+        <v>691334.25</v>
       </c>
       <c r="O39" s="139">
         <f t="shared" si="9"/>
-        <v>456133.25</v>
+        <v>712074.25</v>
       </c>
       <c r="P39" s="50">
         <f t="shared" si="8"/>
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="129">
         <f t="shared" si="10"/>
         <v>26</v>
@@ -5903,18 +5851,19 @@
         <v>1.17</v>
       </c>
       <c r="E40" s="83">
-        <v>210600.26</v>
-      </c>
-      <c r="F40" s="84">
-        <v>0</v>
+        <v>462618.26</v>
+      </c>
+      <c r="F40" s="338">
+        <f>216918.26</f>
+        <v>216918.26</v>
       </c>
       <c r="G40" s="85">
         <f t="shared" si="0"/>
-        <v>210600.26</v>
+        <v>245700</v>
       </c>
       <c r="H40" s="85">
         <f t="shared" si="3"/>
-        <v>6318.0078000000003</v>
+        <v>7371</v>
       </c>
       <c r="I40" s="125">
         <f t="shared" si="4"/>
@@ -5932,18 +5881,18 @@
       <c r="M40" s="147"/>
       <c r="N40" s="86">
         <f t="shared" si="6"/>
-        <v>462618.26</v>
+        <v>498771.26</v>
       </c>
       <c r="O40" s="139">
         <f t="shared" si="9"/>
-        <v>476497.26</v>
+        <v>513734.26</v>
       </c>
       <c r="P40" s="50">
         <f t="shared" si="8"/>
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="129">
         <f t="shared" si="10"/>
         <v>27</v>
@@ -5956,11 +5905,11 @@
         <v>1.35</v>
       </c>
       <c r="E41" s="83">
-        <v>243000.27</v>
+        <v>283500.27</v>
       </c>
       <c r="F41" s="84">
         <f t="shared" ref="F41" si="11">E41</f>
-        <v>243000.27</v>
+        <v>283500.27</v>
       </c>
       <c r="G41" s="85">
         <f t="shared" si="0"/>
@@ -5997,7 +5946,7 @@
         <v>0.27000000000000007</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="129">
         <f t="shared" si="10"/>
         <v>28</v>
@@ -6010,16 +5959,18 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E42" s="83">
-        <v>777788.28</v>
-      </c>
-      <c r="F42" s="84"/>
+        <v>1036322.28</v>
+      </c>
+      <c r="F42" s="338">
+        <v>507000</v>
+      </c>
       <c r="G42" s="85">
         <f t="shared" si="0"/>
-        <v>777788.28</v>
+        <v>529322.28</v>
       </c>
       <c r="H42" s="85">
         <f t="shared" si="3"/>
-        <v>23333.648399999998</v>
+        <v>15879.6684</v>
       </c>
       <c r="I42" s="125">
         <f t="shared" si="4"/>
@@ -6037,18 +5988,21 @@
       <c r="M42" s="147"/>
       <c r="N42" s="86">
         <f t="shared" si="6"/>
-        <v>1036322.28</v>
+        <v>780402.28</v>
       </c>
       <c r="O42" s="139">
         <f t="shared" si="9"/>
-        <v>1067412.28</v>
+        <v>803814.28</v>
       </c>
       <c r="P42" s="50">
         <f t="shared" si="8"/>
         <v>0.28000000000000008</v>
       </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q42" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="130">
         <f t="shared" si="10"/>
         <v>29</v>
@@ -6061,18 +6015,18 @@
         <v>0.82</v>
       </c>
       <c r="E43" s="84">
-        <v>143423.29</v>
+        <v>167897.29</v>
       </c>
       <c r="F43" s="84">
         <v>147726.29</v>
       </c>
       <c r="G43" s="111">
         <f t="shared" si="0"/>
-        <v>-4303</v>
+        <v>20171</v>
       </c>
       <c r="H43" s="111">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>605.13</v>
       </c>
       <c r="I43" s="126">
         <f t="shared" si="4"/>
@@ -6090,11 +6044,11 @@
       <c r="M43" s="148"/>
       <c r="N43" s="86">
         <f t="shared" si="6"/>
-        <v>167897.29</v>
+        <v>192976.29</v>
       </c>
       <c r="O43" s="140">
         <f t="shared" si="9"/>
-        <v>172934.29</v>
+        <v>198765.29</v>
       </c>
       <c r="P43" s="50">
         <f t="shared" si="8"/>
@@ -6104,7 +6058,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="130">
         <f t="shared" si="10"/>
         <v>30</v>
@@ -6117,11 +6071,11 @@
         <v>0.82</v>
       </c>
       <c r="E44" s="84">
-        <v>147600.29999999999</v>
+        <v>172200.3</v>
       </c>
       <c r="F44" s="84">
         <f>E44</f>
-        <v>147600.29999999999</v>
+        <v>172200.3</v>
       </c>
       <c r="G44" s="111">
         <f t="shared" si="0"/>
@@ -6158,7 +6112,7 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="129">
         <f t="shared" si="10"/>
         <v>31</v>
@@ -6171,11 +6125,11 @@
         <v>1.34</v>
       </c>
       <c r="E45" s="83">
-        <v>241200.31</v>
-      </c>
-      <c r="F45" s="84">
+        <v>281400.31</v>
+      </c>
+      <c r="F45" s="338">
         <f>E45</f>
-        <v>241200.31</v>
+        <v>281400.31</v>
       </c>
       <c r="G45" s="85">
         <f t="shared" si="0"/>
@@ -6212,7 +6166,7 @@
         <v>0.31000000000000011</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="129">
         <f t="shared" si="10"/>
         <v>32</v>
@@ -6225,7 +6179,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E46" s="83">
-        <v>562457.31999999995</v>
+        <v>361330.32</v>
       </c>
       <c r="F46" s="84">
         <f>300000.32+140000.32</f>
@@ -6233,11 +6187,11 @@
       </c>
       <c r="G46" s="85">
         <f t="shared" si="0"/>
-        <v>122456.67999999993</v>
+        <v>-78670.320000000007</v>
       </c>
       <c r="H46" s="85">
         <f t="shared" si="3"/>
-        <v>3673.7003999999979</v>
+        <v>0</v>
       </c>
       <c r="I46" s="125">
         <f t="shared" si="4"/>
@@ -6255,18 +6209,18 @@
       <c r="M46" s="147"/>
       <c r="N46" s="86">
         <f t="shared" si="6"/>
-        <v>361330.32</v>
+        <v>156530.32</v>
       </c>
       <c r="O46" s="139">
         <f t="shared" si="9"/>
-        <v>372170.32</v>
+        <v>161226.32</v>
       </c>
       <c r="P46" s="50">
         <f t="shared" si="8"/>
         <v>0.32000000000000012</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="131">
         <f t="shared" si="10"/>
         <v>33</v>
@@ -6279,11 +6233,11 @@
         <v>1.17</v>
       </c>
       <c r="E47" s="122">
-        <v>380600.33</v>
+        <v>415700.33</v>
       </c>
       <c r="F47" s="122">
         <f>E47</f>
-        <v>380600.33</v>
+        <v>415700.33</v>
       </c>
       <c r="G47" s="123">
         <f t="shared" si="0"/>
@@ -6319,10 +6273,10 @@
         <v>0.33000000000000013</v>
       </c>
       <c r="Q47" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="129">
         <f t="shared" si="10"/>
         <v>34</v>
@@ -6335,11 +6289,11 @@
         <v>1.35</v>
       </c>
       <c r="E48" s="83">
-        <v>243000.34</v>
+        <v>283500.34000000003</v>
       </c>
       <c r="F48" s="84">
         <f>E48</f>
-        <v>243000.34</v>
+        <v>283500.34000000003</v>
       </c>
       <c r="G48" s="85">
         <f t="shared" si="0"/>
@@ -6376,7 +6330,7 @@
         <v>0.34000000000000014</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="192">
         <f t="shared" si="10"/>
         <v>35</v>
@@ -6389,11 +6343,11 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E49" s="84">
-        <v>201600.35</v>
+        <v>235200.35</v>
       </c>
       <c r="F49" s="84">
         <f>E49</f>
-        <v>201600.35</v>
+        <v>235200.35</v>
       </c>
       <c r="G49" s="196">
         <f t="shared" si="0"/>
@@ -6433,7 +6387,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="129">
         <f t="shared" si="10"/>
         <v>36</v>
@@ -6446,11 +6400,11 @@
         <v>0.82</v>
       </c>
       <c r="E50" s="83">
-        <v>147600.35999999999</v>
-      </c>
-      <c r="F50" s="84">
+        <v>172200.36</v>
+      </c>
+      <c r="F50" s="338">
         <f>E50</f>
-        <v>147600.35999999999</v>
+        <v>172200.36</v>
       </c>
       <c r="G50" s="85">
         <f t="shared" si="0"/>
@@ -6490,7 +6444,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="129">
         <f t="shared" si="10"/>
         <v>37</v>
@@ -6503,7 +6457,7 @@
         <v>0.82</v>
       </c>
       <c r="E51" s="84">
-        <v>282942.37</v>
+        <v>171200.37</v>
       </c>
       <c r="F51" s="84">
         <f>132000+148000+3942</f>
@@ -6511,7 +6465,7 @@
       </c>
       <c r="G51" s="85">
         <f t="shared" si="0"/>
-        <v>-999.63000000000466</v>
+        <v>-112741.63</v>
       </c>
       <c r="H51" s="85">
         <f t="shared" si="3"/>
@@ -6533,11 +6487,11 @@
       <c r="M51" s="147"/>
       <c r="N51" s="86">
         <f t="shared" si="6"/>
-        <v>171200.37</v>
+        <v>59458.37</v>
       </c>
       <c r="O51" s="139">
         <f t="shared" si="9"/>
-        <v>176336.37</v>
+        <v>61242.37</v>
       </c>
       <c r="P51" s="50">
         <f t="shared" si="8"/>
@@ -6547,51 +6501,53 @@
         <v>202</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A52" s="129">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A52" s="131">
         <f t="shared" si="10"/>
         <v>38</v>
       </c>
-      <c r="B52" s="88" t="s">
+      <c r="B52" s="119" t="s">
         <v>39</v>
       </c>
-      <c r="C52" s="87"/>
-      <c r="D52" s="82">
+      <c r="C52" s="120"/>
+      <c r="D52" s="121">
         <v>1.34</v>
       </c>
-      <c r="E52" s="83">
-        <v>749172.38</v>
-      </c>
-      <c r="F52" s="84"/>
-      <c r="G52" s="85">
+      <c r="E52" s="122">
+        <v>1053048.3799999999</v>
+      </c>
+      <c r="F52" s="122"/>
+      <c r="G52" s="123">
         <f t="shared" si="0"/>
-        <v>749172.38</v>
-      </c>
-      <c r="H52" s="85">
+        <v>1053048.3799999999</v>
+      </c>
+      <c r="H52" s="123">
         <f t="shared" si="3"/>
-        <v>22475.171399999999</v>
-      </c>
-      <c r="I52" s="125">
+        <v>31591.451399999994</v>
+      </c>
+      <c r="I52" s="128">
         <f t="shared" si="12"/>
         <v>141411.12768200002</v>
       </c>
-      <c r="J52" s="125">
+      <c r="J52" s="128">
         <f t="shared" si="13"/>
         <v>60300</v>
       </c>
-      <c r="K52" s="125">
+      <c r="K52" s="128">
         <f t="shared" si="5"/>
         <v>79688.872318000009</v>
       </c>
-      <c r="L52" s="125"/>
-      <c r="M52" s="147"/>
-      <c r="N52" s="86">
+      <c r="L52" s="128"/>
+      <c r="M52" s="149">
+        <v>190000</v>
+      </c>
+      <c r="N52" s="124">
         <f t="shared" si="6"/>
-        <v>1053048.3799999999</v>
-      </c>
-      <c r="O52" s="139">
+        <v>1556040.38</v>
+      </c>
+      <c r="O52" s="141">
         <f t="shared" si="9"/>
-        <v>1084639.3799999999</v>
+        <v>1602721.38</v>
       </c>
       <c r="P52" s="50">
         <f t="shared" si="8"/>
@@ -6601,7 +6557,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="129">
         <f t="shared" si="10"/>
         <v>39</v>
@@ -6614,11 +6570,11 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E53" s="83">
-        <v>201600.39</v>
+        <v>235200.39</v>
       </c>
       <c r="F53" s="84">
         <f>E53</f>
-        <v>201600.39</v>
+        <v>235200.39</v>
       </c>
       <c r="G53" s="85">
         <f t="shared" si="0"/>
@@ -6655,7 +6611,7 @@
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" s="129">
         <f t="shared" si="10"/>
         <v>40</v>
@@ -6668,11 +6624,11 @@
         <v>1.17</v>
       </c>
       <c r="E54" s="83">
-        <v>216918.39999999999</v>
+        <v>245700.4</v>
       </c>
       <c r="F54" s="84">
         <f>E54</f>
-        <v>216918.39999999999</v>
+        <v>245700.4</v>
       </c>
       <c r="G54" s="85">
         <f t="shared" si="0"/>
@@ -6709,7 +6665,7 @@
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="129">
         <f t="shared" si="10"/>
         <v>41</v>
@@ -6722,18 +6678,18 @@
         <v>1.35</v>
       </c>
       <c r="E55" s="83">
-        <v>245768.41</v>
+        <v>276127.40999999997</v>
       </c>
       <c r="F55" s="84">
         <v>253141.41</v>
       </c>
       <c r="G55" s="85">
         <f t="shared" si="0"/>
-        <v>-7373</v>
+        <v>22985.999999999971</v>
       </c>
       <c r="H55" s="85">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>689.57999999999913</v>
       </c>
       <c r="I55" s="125">
         <f t="shared" si="12"/>
@@ -6751,18 +6707,18 @@
       <c r="M55" s="147"/>
       <c r="N55" s="86">
         <f t="shared" si="6"/>
-        <v>276127.40999999997</v>
+        <v>307176.40999999997</v>
       </c>
       <c r="O55" s="139">
         <f t="shared" si="9"/>
-        <v>284411.40999999997</v>
+        <v>316391.40999999997</v>
       </c>
       <c r="P55" s="50">
         <f t="shared" si="8"/>
         <v>0.4100000000000002</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" s="131">
         <f t="shared" si="10"/>
         <v>42</v>
@@ -6775,14 +6731,14 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E56" s="122">
-        <v>241638.42</v>
+        <v>275238.42</v>
       </c>
       <c r="F56" s="122">
         <v>234600.42</v>
       </c>
       <c r="G56" s="123">
         <f t="shared" si="0"/>
-        <v>7038</v>
+        <v>40637.999999999971</v>
       </c>
       <c r="H56" s="123"/>
       <c r="I56" s="128">
@@ -6803,21 +6759,21 @@
       </c>
       <c r="N56" s="124">
         <f t="shared" si="6"/>
-        <v>275238.42</v>
+        <v>308838.42</v>
       </c>
       <c r="O56" s="141">
         <f t="shared" si="9"/>
-        <v>283495.42</v>
+        <v>318103.42</v>
       </c>
       <c r="P56" s="50">
         <f t="shared" si="8"/>
         <v>0.42000000000000021</v>
       </c>
       <c r="Q56" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="131">
         <f t="shared" si="10"/>
         <v>43</v>
@@ -6830,18 +6786,18 @@
         <v>0.82</v>
       </c>
       <c r="E57" s="164">
-        <v>756600.43</v>
+        <v>790470.43</v>
       </c>
       <c r="F57" s="122">
         <v>447600.43</v>
       </c>
       <c r="G57" s="123">
         <f t="shared" si="0"/>
-        <v>309000.00000000006</v>
+        <v>342870.00000000006</v>
       </c>
       <c r="H57" s="123">
         <f t="shared" si="3"/>
-        <v>9270.0000000000018</v>
+        <v>10286.100000000002</v>
       </c>
       <c r="I57" s="128">
         <f t="shared" si="12"/>
@@ -6861,21 +6817,21 @@
       </c>
       <c r="N57" s="124">
         <f>ROUND(SUM(G57:M57),0) + P57</f>
-        <v>790470.43</v>
+        <v>825356.43</v>
       </c>
       <c r="O57" s="141">
         <f t="shared" si="9"/>
-        <v>814184.43</v>
+        <v>850117.43</v>
       </c>
       <c r="P57" s="50">
         <f t="shared" si="8"/>
         <v>0.43000000000000022</v>
       </c>
       <c r="Q57" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="130">
         <f t="shared" si="10"/>
         <v>44</v>
@@ -6888,7 +6844,7 @@
         <v>0.82</v>
       </c>
       <c r="E58" s="83">
-        <v>105859.44</v>
+        <v>129113.44</v>
       </c>
       <c r="F58" s="84">
         <f>39911.44+109035.44</f>
@@ -6896,7 +6852,7 @@
       </c>
       <c r="G58" s="85">
         <f t="shared" si="0"/>
-        <v>-43087.44</v>
+        <v>-19833.440000000002</v>
       </c>
       <c r="H58" s="85">
         <f t="shared" si="3"/>
@@ -6918,21 +6874,21 @@
       <c r="M58" s="147"/>
       <c r="N58" s="86">
         <f t="shared" si="6"/>
-        <v>129113.44</v>
+        <v>152367.44</v>
       </c>
       <c r="O58" s="139">
         <f t="shared" si="9"/>
-        <v>132986.44</v>
+        <v>156938.44</v>
       </c>
       <c r="P58" s="50">
         <f t="shared" si="8"/>
         <v>0.44000000000000022</v>
       </c>
       <c r="Q58" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" s="130">
         <f t="shared" si="10"/>
         <v>45</v>
@@ -6945,11 +6901,11 @@
         <v>1.34</v>
       </c>
       <c r="E59" s="83">
-        <v>241200.45</v>
+        <v>281400.45</v>
       </c>
       <c r="F59" s="84">
         <f>E59</f>
-        <v>241200.45</v>
+        <v>281400.45</v>
       </c>
       <c r="G59" s="85">
         <f t="shared" si="0"/>
@@ -6986,12 +6942,12 @@
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A60" s="262">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A60" s="258">
         <f t="shared" si="10"/>
         <v>46</v>
       </c>
-      <c r="B60" s="263" t="s">
+      <c r="B60" s="259" t="s">
         <v>45</v>
       </c>
       <c r="C60" s="113"/>
@@ -6999,18 +6955,18 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E60" s="83">
-        <v>227951.46</v>
+        <v>243390.46</v>
       </c>
       <c r="F60" s="84">
         <v>220000</v>
       </c>
       <c r="G60" s="85">
         <f t="shared" si="0"/>
-        <v>7951.4599999999919</v>
+        <v>23390.459999999992</v>
       </c>
       <c r="H60" s="85">
         <f t="shared" si="3"/>
-        <v>238.54379999999975</v>
+        <v>701.71379999999976</v>
       </c>
       <c r="I60" s="125">
         <f t="shared" si="12"/>
@@ -7028,11 +6984,11 @@
       <c r="M60" s="147"/>
       <c r="N60" s="86">
         <f t="shared" si="6"/>
-        <v>243390.46</v>
+        <v>259292.46</v>
       </c>
       <c r="O60" s="139">
         <f t="shared" si="9"/>
-        <v>250692.46</v>
+        <v>267071.45999999996</v>
       </c>
       <c r="P60" s="50">
         <f t="shared" si="8"/>
@@ -7042,7 +6998,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="131">
         <f t="shared" si="10"/>
         <v>47</v>
@@ -7055,14 +7011,14 @@
         <v>1.17</v>
       </c>
       <c r="E61" s="122">
-        <v>735095.47</v>
+        <v>1115795.47</v>
       </c>
       <c r="F61" s="122">
         <v>0</v>
       </c>
       <c r="G61" s="123">
         <f t="shared" si="0"/>
-        <v>735095.47</v>
+        <v>1115795.47</v>
       </c>
       <c r="H61" s="123"/>
       <c r="I61" s="128">
@@ -7083,21 +7039,21 @@
       </c>
       <c r="N61" s="124">
         <f t="shared" si="6"/>
-        <v>1115795.47</v>
+        <v>1496495.47</v>
       </c>
       <c r="O61" s="141">
         <f t="shared" si="9"/>
-        <v>1149269.47</v>
+        <v>1541390.47</v>
       </c>
       <c r="P61" s="50">
         <f t="shared" si="8"/>
         <v>0.47000000000000025</v>
       </c>
       <c r="Q61" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="219">
         <f t="shared" si="10"/>
         <v>48</v>
@@ -7110,11 +7066,11 @@
         <v>1.35</v>
       </c>
       <c r="E62" s="223">
-        <v>250290.48</v>
+        <v>283500.48</v>
       </c>
       <c r="F62" s="223">
         <f t="shared" ref="F62:F67" si="14">E62</f>
-        <v>250290.48</v>
+        <v>283500.48</v>
       </c>
       <c r="G62" s="224">
         <f t="shared" si="0"/>
@@ -7154,7 +7110,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" s="130">
         <f t="shared" si="10"/>
         <v>49</v>
@@ -7167,11 +7123,11 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E63" s="83">
-        <v>201600.49</v>
+        <v>235200.49</v>
       </c>
       <c r="F63" s="84">
         <f>E63</f>
-        <v>201600.49</v>
+        <v>235200.49</v>
       </c>
       <c r="G63" s="85">
         <f t="shared" si="0"/>
@@ -7208,7 +7164,7 @@
         <v>0.49000000000000027</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" s="130">
         <f t="shared" si="10"/>
         <v>50</v>
@@ -7221,18 +7177,18 @@
         <v>0.82</v>
       </c>
       <c r="E64" s="83">
-        <v>147600.5</v>
+        <v>324229.5</v>
       </c>
       <c r="F64" s="84">
         <v>0</v>
       </c>
       <c r="G64" s="85">
         <f t="shared" si="0"/>
-        <v>147600.5</v>
+        <v>324229.5</v>
       </c>
       <c r="H64" s="85">
         <f t="shared" si="3"/>
-        <v>4428.0149999999994</v>
+        <v>9726.8850000000002</v>
       </c>
       <c r="I64" s="125">
         <f t="shared" si="12"/>
@@ -7250,18 +7206,18 @@
       <c r="M64" s="147"/>
       <c r="N64" s="86">
         <f t="shared" si="6"/>
-        <v>324229.5</v>
+        <v>506156.5</v>
       </c>
       <c r="O64" s="139">
         <f t="shared" si="9"/>
-        <v>333956.5</v>
+        <v>521341.5</v>
       </c>
       <c r="P64" s="50">
         <f t="shared" si="8"/>
         <v>0.50000000000000022</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" s="130">
         <f t="shared" si="10"/>
         <v>51</v>
@@ -7274,11 +7230,11 @@
         <v>0.82</v>
       </c>
       <c r="E65" s="83">
-        <v>147600.51</v>
+        <v>172200.51</v>
       </c>
       <c r="F65" s="84">
         <f t="shared" si="14"/>
-        <v>147600.51</v>
+        <v>172200.51</v>
       </c>
       <c r="G65" s="85">
         <f t="shared" si="0"/>
@@ -7315,7 +7271,7 @@
         <v>0.51000000000000023</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" s="130">
         <f t="shared" si="10"/>
         <v>52</v>
@@ -7328,11 +7284,11 @@
         <v>1.34</v>
       </c>
       <c r="E66" s="83">
-        <v>241200.52</v>
+        <v>281400.52</v>
       </c>
       <c r="F66" s="84">
         <f t="shared" si="14"/>
-        <v>241200.52</v>
+        <v>281400.52</v>
       </c>
       <c r="G66" s="85">
         <f t="shared" si="0"/>
@@ -7369,7 +7325,7 @@
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" s="130">
         <f t="shared" si="10"/>
         <v>53</v>
@@ -7382,11 +7338,11 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E67" s="84">
-        <v>207648.53</v>
+        <v>235200.53</v>
       </c>
       <c r="F67" s="84">
         <f t="shared" si="14"/>
-        <v>207648.53</v>
+        <v>235200.53</v>
       </c>
       <c r="G67" s="85">
         <f t="shared" si="0"/>
@@ -7423,7 +7379,7 @@
         <v>0.53000000000000025</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" s="130">
         <f t="shared" si="10"/>
         <v>54</v>
@@ -7436,14 +7392,15 @@
         <v>1.17</v>
       </c>
       <c r="E68" s="83">
-        <v>204641.54</v>
-      </c>
-      <c r="F68" s="84">
-        <v>210780.54</v>
+        <v>239561.54</v>
+      </c>
+      <c r="F68" s="338">
+        <f>E68</f>
+        <v>239561.54</v>
       </c>
       <c r="G68" s="85">
         <f t="shared" si="0"/>
-        <v>-6139</v>
+        <v>0</v>
       </c>
       <c r="H68" s="85">
         <f t="shared" si="3"/>
@@ -7465,18 +7422,18 @@
       <c r="M68" s="147"/>
       <c r="N68" s="86">
         <f t="shared" si="6"/>
-        <v>239561.54</v>
+        <v>245700.54</v>
       </c>
       <c r="O68" s="139">
         <f t="shared" si="9"/>
-        <v>246748.54</v>
+        <v>253071.54</v>
       </c>
       <c r="P68" s="50">
         <f t="shared" si="8"/>
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" s="130">
         <f t="shared" si="10"/>
         <v>55</v>
@@ -7489,11 +7446,11 @@
         <v>1.35</v>
       </c>
       <c r="E69" s="83">
-        <v>236124.55</v>
+        <v>283500.55</v>
       </c>
       <c r="F69" s="84">
         <f>E69</f>
-        <v>236124.55</v>
+        <v>283500.55</v>
       </c>
       <c r="G69" s="85">
         <f t="shared" si="0"/>
@@ -7530,7 +7487,7 @@
         <v>0.55000000000000027</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" s="130">
         <f t="shared" si="10"/>
         <v>56</v>
@@ -7543,18 +7500,18 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E70" s="83">
-        <v>519542.56</v>
+        <v>770329.56</v>
       </c>
       <c r="F70" s="84">
         <v>0</v>
       </c>
       <c r="G70" s="85">
         <f t="shared" si="0"/>
-        <v>519542.56</v>
+        <v>770329.56</v>
       </c>
       <c r="H70" s="85">
         <f t="shared" si="3"/>
-        <v>15586.2768</v>
+        <v>23109.8868</v>
       </c>
       <c r="I70" s="125">
         <f t="shared" si="12"/>
@@ -7572,18 +7529,18 @@
       <c r="M70" s="147"/>
       <c r="N70" s="86">
         <f t="shared" si="6"/>
-        <v>770329.56</v>
+        <v>1028639.56</v>
       </c>
       <c r="O70" s="139">
         <f t="shared" si="9"/>
-        <v>793439.56</v>
+        <v>1059498.56</v>
       </c>
       <c r="P70" s="50">
         <f t="shared" si="8"/>
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" s="130">
         <f t="shared" si="10"/>
         <v>57</v>
@@ -7596,11 +7553,11 @@
         <v>0.82</v>
       </c>
       <c r="E71" s="83">
-        <v>147600.57</v>
+        <v>172200.57</v>
       </c>
       <c r="F71" s="84">
         <f>E71</f>
-        <v>147600.57</v>
+        <v>172200.57</v>
       </c>
       <c r="G71" s="85">
         <f t="shared" si="0"/>
@@ -7637,10 +7594,10 @@
         <v>0.57000000000000028</v>
       </c>
       <c r="Q71" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="130">
         <f t="shared" si="10"/>
         <v>58</v>
@@ -7653,11 +7610,11 @@
         <v>0.82</v>
       </c>
       <c r="E72" s="83">
-        <v>147600.57999999999</v>
+        <v>172200.58</v>
       </c>
       <c r="F72" s="84">
         <f t="shared" ref="F72" si="15">E72</f>
-        <v>147600.57999999999</v>
+        <v>172200.58</v>
       </c>
       <c r="G72" s="85">
         <f t="shared" si="0"/>
@@ -7697,7 +7654,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" s="130">
         <f t="shared" si="10"/>
         <v>59</v>
@@ -7710,18 +7667,18 @@
         <v>1.34</v>
       </c>
       <c r="E73" s="84">
-        <v>234375.59</v>
+        <v>274369.59000000003</v>
       </c>
       <c r="F73" s="84">
         <v>241406.59</v>
       </c>
       <c r="G73" s="111">
         <f t="shared" si="0"/>
-        <v>-7031</v>
+        <v>32963.000000000029</v>
       </c>
       <c r="H73" s="111">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>988.89000000000078</v>
       </c>
       <c r="I73" s="126">
         <f t="shared" si="12"/>
@@ -7739,18 +7696,18 @@
       <c r="M73" s="148"/>
       <c r="N73" s="86">
         <f t="shared" si="6"/>
-        <v>274369.59000000003</v>
+        <v>315352.59000000003</v>
       </c>
       <c r="O73" s="140">
         <f t="shared" si="9"/>
-        <v>282600.59000000003</v>
+        <v>324813.59000000003</v>
       </c>
       <c r="P73" s="50">
         <f t="shared" si="8"/>
         <v>0.5900000000000003</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" s="130">
         <f t="shared" si="10"/>
         <v>60</v>
@@ -7763,18 +7720,18 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E74" s="83">
-        <v>196055.6</v>
+        <v>229318.6</v>
       </c>
       <c r="F74" s="84">
         <v>201937.6</v>
       </c>
       <c r="G74" s="85">
         <f t="shared" si="0"/>
-        <v>-5882</v>
+        <v>27381</v>
       </c>
       <c r="H74" s="85">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>821.43</v>
       </c>
       <c r="I74" s="125">
         <f t="shared" si="12"/>
@@ -7792,18 +7749,18 @@
       <c r="M74" s="147"/>
       <c r="N74" s="86">
         <f t="shared" si="6"/>
-        <v>229318.6</v>
+        <v>263402.59999999998</v>
       </c>
       <c r="O74" s="139">
         <f t="shared" si="9"/>
-        <v>236198.6</v>
+        <v>271304.59999999998</v>
       </c>
       <c r="P74" s="50">
         <f t="shared" si="8"/>
         <v>0.60000000000000031</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" s="130">
         <f t="shared" si="10"/>
         <v>61</v>
@@ -7816,11 +7773,11 @@
         <v>1.17</v>
       </c>
       <c r="E75" s="83">
-        <v>210600.61</v>
+        <v>245700.61</v>
       </c>
       <c r="F75" s="84">
         <f>E75</f>
-        <v>210600.61</v>
+        <v>245700.61</v>
       </c>
       <c r="G75" s="85">
         <f t="shared" si="0"/>
@@ -7857,7 +7814,7 @@
         <v>0.61000000000000032</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" s="130">
         <f t="shared" si="10"/>
         <v>62</v>
@@ -7870,11 +7827,11 @@
         <v>1.35</v>
       </c>
       <c r="E76" s="83">
-        <v>236124.62</v>
+        <v>283500.62</v>
       </c>
       <c r="F76" s="84">
         <f>E76</f>
-        <v>236124.62</v>
+        <v>283500.62</v>
       </c>
       <c r="G76" s="85">
         <f t="shared" si="0"/>
@@ -7911,7 +7868,7 @@
         <v>0.62000000000000033</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" s="130">
         <f t="shared" si="10"/>
         <v>63</v>
@@ -7924,11 +7881,11 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E77" s="83">
-        <v>201600.63</v>
+        <v>235200.63</v>
       </c>
       <c r="F77" s="84">
         <f>E77</f>
-        <v>201600.63</v>
+        <v>235200.63</v>
       </c>
       <c r="G77" s="85">
         <f t="shared" si="0"/>
@@ -7968,7 +7925,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" s="130">
         <f t="shared" si="10"/>
         <v>64</v>
@@ -7981,18 +7938,18 @@
         <v>0.82</v>
       </c>
       <c r="E78" s="83">
-        <v>143450.64000000001</v>
+        <v>167896.64</v>
       </c>
       <c r="F78" s="84">
         <v>147754.64000000001</v>
       </c>
       <c r="G78" s="85">
         <f t="shared" si="0"/>
-        <v>-4304</v>
+        <v>20142</v>
       </c>
       <c r="H78" s="85">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>604.26</v>
       </c>
       <c r="I78" s="125">
         <f t="shared" si="12"/>
@@ -8010,23 +7967,23 @@
       <c r="M78" s="147"/>
       <c r="N78" s="86">
         <f t="shared" si="6"/>
-        <v>167896.64</v>
+        <v>192946.64</v>
       </c>
       <c r="O78" s="139">
         <f t="shared" si="9"/>
-        <v>172933.64</v>
+        <v>198734.64</v>
       </c>
       <c r="P78" s="50">
         <f t="shared" si="8"/>
         <v>0.64000000000000035</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A79" s="256">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A79" s="252">
         <f t="shared" si="10"/>
         <v>65</v>
       </c>
-      <c r="B79" s="257" t="s">
+      <c r="B79" s="253" t="s">
         <v>64</v>
       </c>
       <c r="C79" s="113"/>
@@ -8034,18 +7991,18 @@
         <v>0.82</v>
       </c>
       <c r="E79" s="84">
-        <v>546922.65</v>
+        <v>735530.65</v>
       </c>
       <c r="F79" s="176">
         <v>0</v>
       </c>
       <c r="G79" s="111">
         <f t="shared" ref="G79:G117" si="16">E79-F79</f>
-        <v>546922.65</v>
+        <v>735530.65</v>
       </c>
       <c r="H79" s="111">
         <f t="shared" si="3"/>
-        <v>16407.679499999998</v>
+        <v>22065.9195</v>
       </c>
       <c r="I79" s="126">
         <f t="shared" ref="I79:I110" si="17">J$2*D79/100</f>
@@ -8063,11 +8020,11 @@
       <c r="M79" s="148"/>
       <c r="N79" s="86">
         <f t="shared" si="6"/>
-        <v>735530.65</v>
+        <v>929797.65</v>
       </c>
       <c r="O79" s="140">
         <f t="shared" si="9"/>
-        <v>757596.65</v>
+        <v>957691.65</v>
       </c>
       <c r="P79" s="50">
         <f t="shared" si="8"/>
@@ -8077,7 +8034,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="130">
         <f t="shared" si="10"/>
         <v>66</v>
@@ -8090,18 +8047,18 @@
         <v>1.34</v>
       </c>
       <c r="E80" s="84">
-        <v>588494.66</v>
+        <v>887549.66</v>
       </c>
       <c r="F80" s="84">
         <v>0</v>
       </c>
       <c r="G80" s="111">
         <f t="shared" si="16"/>
-        <v>588494.66</v>
+        <v>887549.66</v>
       </c>
       <c r="H80" s="111">
         <f t="shared" ref="H80:H117" si="19">IF(G80&gt;0,G80*3%,0)</f>
-        <v>17654.839800000002</v>
+        <v>26626.489799999999</v>
       </c>
       <c r="I80" s="126">
         <f t="shared" si="17"/>
@@ -8119,18 +8076,18 @@
       <c r="M80" s="148"/>
       <c r="N80" s="112">
         <f t="shared" si="6"/>
-        <v>887549.66</v>
+        <v>1195576.6599999999</v>
       </c>
       <c r="O80" s="140">
         <f t="shared" si="9"/>
-        <v>914175.66</v>
+        <v>1231443.6599999999</v>
       </c>
       <c r="P80" s="50">
         <f t="shared" si="8"/>
         <v>0.66000000000000036</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="130">
         <f t="shared" si="10"/>
         <v>67</v>
@@ -8143,18 +8100,18 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E81" s="83">
-        <v>195895.67</v>
+        <v>436973.67</v>
       </c>
       <c r="F81" s="84">
         <v>0</v>
       </c>
       <c r="G81" s="85">
         <f t="shared" si="16"/>
-        <v>195895.67</v>
+        <v>436973.67</v>
       </c>
       <c r="H81" s="85">
         <f t="shared" si="19"/>
-        <v>5876.8701000000001</v>
+        <v>13109.210099999998</v>
       </c>
       <c r="I81" s="125">
         <f t="shared" si="17"/>
@@ -8172,18 +8129,18 @@
       <c r="M81" s="147"/>
       <c r="N81" s="86">
         <f t="shared" ref="N81:N117" si="21">ROUND(SUM(G81:M81),0) + P81</f>
-        <v>436973.67</v>
+        <v>685283.67</v>
       </c>
       <c r="O81" s="139">
         <f t="shared" si="9"/>
-        <v>450082.67</v>
+        <v>705842.67</v>
       </c>
       <c r="P81" s="50">
         <f t="shared" si="8"/>
         <v>0.67000000000000037</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" s="187">
         <f t="shared" si="10"/>
         <v>68</v>
@@ -8196,18 +8153,18 @@
         <v>1.17</v>
       </c>
       <c r="E82" s="210">
-        <v>7338190.6799999997</v>
+        <v>7899036.6799999997</v>
       </c>
       <c r="F82" s="210">
         <v>0</v>
       </c>
       <c r="G82" s="211">
         <f t="shared" si="16"/>
-        <v>7338190.6799999997</v>
+        <v>7899036.6799999997</v>
       </c>
       <c r="H82" s="211">
         <f t="shared" si="19"/>
-        <v>220145.72039999999</v>
+        <v>236971.1004</v>
       </c>
       <c r="I82" s="212">
         <f t="shared" si="17"/>
@@ -8227,23 +8184,23 @@
       <c r="M82" s="213"/>
       <c r="N82" s="214">
         <f t="shared" si="21"/>
-        <v>7899036.6799999997</v>
+        <v>8476708.6799999997</v>
       </c>
       <c r="O82" s="215">
         <f t="shared" si="9"/>
-        <v>8136007.6799999997</v>
+        <v>8731009.6799999997</v>
       </c>
       <c r="P82" s="50">
         <f t="shared" si="8"/>
         <v>0.68000000000000038</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A83" s="233">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A83" s="229">
         <f t="shared" si="10"/>
         <v>69</v>
       </c>
-      <c r="B83" s="234" t="s">
+      <c r="B83" s="230" t="s">
         <v>68</v>
       </c>
       <c r="C83" s="87"/>
@@ -8251,18 +8208,18 @@
         <v>1.35</v>
       </c>
       <c r="E83" s="83">
-        <v>242119.69</v>
+        <v>283420.69</v>
       </c>
       <c r="F83" s="84">
         <v>242200</v>
       </c>
       <c r="G83" s="85">
         <f t="shared" si="16"/>
-        <v>-80.309999999997672</v>
+        <v>41220.69</v>
       </c>
       <c r="H83" s="85">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>1236.6206999999999</v>
       </c>
       <c r="I83" s="125">
         <f t="shared" si="17"/>
@@ -8282,23 +8239,23 @@
       <c r="M83" s="147"/>
       <c r="N83" s="86">
         <f t="shared" si="21"/>
-        <v>283420.69</v>
+        <v>325957.69</v>
       </c>
       <c r="O83" s="139">
         <f t="shared" si="9"/>
-        <v>291923.69</v>
+        <v>335736.69</v>
       </c>
       <c r="P83" s="50">
         <f t="shared" si="8"/>
         <v>0.69000000000000039</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A84" s="245">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A84" s="241">
         <f t="shared" si="10"/>
         <v>70</v>
       </c>
-      <c r="B84" s="246" t="s">
+      <c r="B84" s="242" t="s">
         <v>69</v>
       </c>
       <c r="C84" s="113"/>
@@ -8306,18 +8263,18 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E84" s="84">
-        <v>201600.7</v>
+        <v>442849.7</v>
       </c>
       <c r="F84" s="84">
         <v>0</v>
       </c>
       <c r="G84" s="111">
         <f t="shared" si="16"/>
-        <v>201600.7</v>
+        <v>442849.7</v>
       </c>
       <c r="H84" s="111">
         <f t="shared" si="19"/>
-        <v>6048.0209999999997</v>
+        <v>13285.491</v>
       </c>
       <c r="I84" s="126">
         <f t="shared" si="17"/>
@@ -8335,11 +8292,11 @@
       <c r="M84" s="148"/>
       <c r="N84" s="86">
         <f t="shared" si="21"/>
-        <v>442849.7</v>
+        <v>691335.7</v>
       </c>
       <c r="O84" s="140">
         <f t="shared" si="9"/>
-        <v>456134.7</v>
+        <v>712075.7</v>
       </c>
       <c r="P84" s="50">
         <f t="shared" si="8"/>
@@ -8349,7 +8306,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" s="130">
         <f t="shared" si="10"/>
         <v>71</v>
@@ -8362,11 +8319,11 @@
         <v>0.82</v>
       </c>
       <c r="E85" s="83">
-        <v>147600.71</v>
+        <v>172200.71</v>
       </c>
       <c r="F85" s="84">
         <f>E85</f>
-        <v>147600.71</v>
+        <v>172200.71</v>
       </c>
       <c r="G85" s="85">
         <f t="shared" si="16"/>
@@ -8403,7 +8360,7 @@
         <v>0.71000000000000041</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" s="130">
         <f t="shared" si="10"/>
         <v>72</v>
@@ -8416,11 +8373,11 @@
         <v>0.82</v>
       </c>
       <c r="E86" s="83">
-        <v>147600.72</v>
-      </c>
-      <c r="F86" s="84">
+        <v>172200.72</v>
+      </c>
+      <c r="F86" s="338">
         <f>E86</f>
-        <v>147600.72</v>
+        <v>172200.72</v>
       </c>
       <c r="G86" s="85">
         <f t="shared" si="16"/>
@@ -8457,7 +8414,7 @@
         <v>0.72000000000000042</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" s="130">
         <f t="shared" si="10"/>
         <v>73</v>
@@ -8470,11 +8427,11 @@
         <v>1.34</v>
       </c>
       <c r="E87" s="83">
-        <v>248434.73</v>
+        <v>281400.73</v>
       </c>
       <c r="F87" s="84">
         <f>E87</f>
-        <v>248434.73</v>
+        <v>281400.73</v>
       </c>
       <c r="G87" s="85">
         <f t="shared" si="16"/>
@@ -8511,63 +8468,63 @@
         <v>0.73000000000000043</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A88" s="239">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A88" s="235">
         <f t="shared" si="10"/>
         <v>74</v>
       </c>
-      <c r="B88" s="251" t="s">
+      <c r="B88" s="247" t="s">
         <v>73</v>
       </c>
       <c r="C88" s="87"/>
-      <c r="D88" s="82">
+      <c r="D88" s="121">
         <v>1.1200000000000001</v>
       </c>
-      <c r="E88" s="83">
-        <v>1129429.74</v>
-      </c>
-      <c r="F88" s="84"/>
-      <c r="G88" s="85">
+      <c r="E88" s="122">
+        <v>1528513.74</v>
+      </c>
+      <c r="F88" s="122"/>
+      <c r="G88" s="123">
         <f t="shared" si="16"/>
-        <v>1129429.74</v>
-      </c>
-      <c r="H88" s="85">
+        <v>1528513.74</v>
+      </c>
+      <c r="H88" s="123">
         <f t="shared" si="19"/>
-        <v>33882.892200000002</v>
-      </c>
-      <c r="I88" s="125">
+        <v>45855.412199999999</v>
+      </c>
+      <c r="I88" s="128">
         <f t="shared" si="17"/>
         <v>118194.37537600001</v>
       </c>
-      <c r="J88" s="125">
+      <c r="J88" s="128">
         <f t="shared" si="18"/>
         <v>50400.000000000007</v>
       </c>
-      <c r="K88" s="125">
+      <c r="K88" s="128">
         <f t="shared" si="20"/>
         <v>66605.624624000004</v>
       </c>
-      <c r="L88" s="125"/>
-      <c r="M88" s="147">
+      <c r="L88" s="128"/>
+      <c r="M88" s="149">
         <v>130000</v>
       </c>
-      <c r="N88" s="86">
+      <c r="N88" s="124">
         <f t="shared" si="21"/>
-        <v>1528513.74</v>
-      </c>
-      <c r="O88" s="139">
+        <v>1939569.74</v>
+      </c>
+      <c r="O88" s="141">
         <f t="shared" si="9"/>
-        <v>1574368.74</v>
+        <v>1997756.74</v>
       </c>
       <c r="P88" s="50">
         <f t="shared" si="8"/>
         <v>0.74000000000000044</v>
       </c>
       <c r="Q88" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" s="129">
         <f t="shared" si="10"/>
         <v>75</v>
@@ -8580,18 +8537,18 @@
         <v>1.17</v>
       </c>
       <c r="E89" s="83">
-        <v>210600.75</v>
+        <v>239382.75</v>
       </c>
       <c r="F89" s="84">
         <v>216918.75</v>
       </c>
       <c r="G89" s="85">
         <f t="shared" si="16"/>
-        <v>-6318</v>
+        <v>22464</v>
       </c>
       <c r="H89" s="85">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>673.92</v>
       </c>
       <c r="I89" s="125">
         <f t="shared" si="17"/>
@@ -8609,18 +8566,18 @@
       <c r="M89" s="147"/>
       <c r="N89" s="86">
         <f t="shared" si="21"/>
-        <v>239382.75</v>
+        <v>268838.75</v>
       </c>
       <c r="O89" s="139">
         <f t="shared" si="9"/>
-        <v>246563.75</v>
+        <v>276903.75</v>
       </c>
       <c r="P89" s="50">
         <f t="shared" si="8"/>
         <v>0.75000000000000044</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" s="189">
         <f t="shared" si="10"/>
         <v>76</v>
@@ -8633,18 +8590,18 @@
         <v>1.35</v>
       </c>
       <c r="E90" s="201">
-        <v>250290.76</v>
+        <v>291009.76</v>
       </c>
       <c r="F90" s="201">
         <v>243000.76</v>
       </c>
       <c r="G90" s="202">
         <f t="shared" si="16"/>
-        <v>7290</v>
+        <v>48009</v>
       </c>
       <c r="H90" s="202">
         <f t="shared" si="19"/>
-        <v>218.7</v>
+        <v>1440.27</v>
       </c>
       <c r="I90" s="203">
         <f t="shared" si="17"/>
@@ -8662,18 +8619,18 @@
       <c r="M90" s="204"/>
       <c r="N90" s="205">
         <f t="shared" si="21"/>
-        <v>291009.76</v>
+        <v>332949.76000000001</v>
       </c>
       <c r="O90" s="206">
         <f t="shared" si="9"/>
-        <v>299739.76</v>
+        <v>342937.76</v>
       </c>
       <c r="P90" s="50">
         <f t="shared" si="8"/>
         <v>0.76000000000000045</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" s="129">
         <f t="shared" si="10"/>
         <v>77</v>
@@ -8686,11 +8643,11 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E91" s="83">
-        <v>201600.77</v>
+        <v>235200.77</v>
       </c>
       <c r="F91" s="84">
         <f>E91</f>
-        <v>201600.77</v>
+        <v>235200.77</v>
       </c>
       <c r="G91" s="85">
         <f t="shared" si="16"/>
@@ -8727,7 +8684,7 @@
         <v>0.77000000000000046</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" s="131">
         <f t="shared" si="10"/>
         <v>78</v>
@@ -8740,11 +8697,11 @@
         <v>0.82</v>
       </c>
       <c r="E92" s="122">
-        <v>321978.78000000003</v>
+        <v>337200.78</v>
       </c>
       <c r="F92" s="122">
         <f>E92</f>
-        <v>321978.78000000003</v>
+        <v>337200.78</v>
       </c>
       <c r="G92" s="123">
         <f t="shared" si="16"/>
@@ -8780,10 +8737,10 @@
         <v>0.78000000000000047</v>
       </c>
       <c r="Q92" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" s="129">
         <f t="shared" si="10"/>
         <v>79</v>
@@ -8796,11 +8753,11 @@
         <v>0.82</v>
       </c>
       <c r="E93" s="83">
-        <v>147600.79</v>
+        <v>172200.79</v>
       </c>
       <c r="F93" s="84">
         <f>E93</f>
-        <v>147600.79</v>
+        <v>172200.79</v>
       </c>
       <c r="G93" s="85">
         <f t="shared" si="16"/>
@@ -8840,7 +8797,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" s="130">
         <f t="shared" si="10"/>
         <v>80</v>
@@ -8853,18 +8810,18 @@
         <v>1.34</v>
       </c>
       <c r="E94" s="84">
-        <v>241200.8</v>
+        <v>274162.8</v>
       </c>
       <c r="F94" s="84">
         <v>248438.8</v>
       </c>
       <c r="G94" s="85">
         <f>E94-F94</f>
-        <v>-7238</v>
+        <v>25724</v>
       </c>
       <c r="H94" s="85">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>771.72</v>
       </c>
       <c r="I94" s="125">
         <f t="shared" si="17"/>
@@ -8882,18 +8839,18 @@
       <c r="M94" s="147"/>
       <c r="N94" s="86">
         <f t="shared" si="21"/>
-        <v>274162.8</v>
+        <v>307896.8</v>
       </c>
       <c r="O94" s="139">
         <f t="shared" si="9"/>
-        <v>282387.8</v>
+        <v>317133.8</v>
       </c>
       <c r="P94" s="50">
         <f t="shared" si="8"/>
         <v>0.80000000000000049</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" s="130">
         <f t="shared" si="10"/>
         <v>81</v>
@@ -8906,11 +8863,11 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E95" s="84">
-        <v>201600.81</v>
+        <v>235200.81</v>
       </c>
       <c r="F95" s="84">
         <f>E95</f>
-        <v>201600.81</v>
+        <v>235200.81</v>
       </c>
       <c r="G95" s="111">
         <f t="shared" si="16"/>
@@ -8950,7 +8907,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" s="130">
         <f t="shared" si="10"/>
         <v>82</v>
@@ -8963,11 +8920,11 @@
         <v>1.17</v>
       </c>
       <c r="E96" s="83">
-        <v>195738.82</v>
+        <v>245700.82</v>
       </c>
       <c r="F96" s="84">
         <f>E96</f>
-        <v>195738.82</v>
+        <v>245700.82</v>
       </c>
       <c r="G96" s="85">
         <f t="shared" si="16"/>
@@ -9004,7 +8961,7 @@
         <v>0.82000000000000051</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" s="130">
         <f t="shared" si="10"/>
         <v>83</v>
@@ -9017,11 +8974,11 @@
         <v>1.35</v>
       </c>
       <c r="E97" s="84">
-        <v>243000.83</v>
+        <v>283500.83</v>
       </c>
       <c r="F97" s="84">
         <f>E97</f>
-        <v>243000.83</v>
+        <v>283500.83</v>
       </c>
       <c r="G97" s="85">
         <f t="shared" si="16"/>
@@ -9058,7 +9015,7 @@
         <v>0.83000000000000052</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" s="130">
         <f t="shared" si="10"/>
         <v>84</v>
@@ -9071,16 +9028,16 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E98" s="84">
-        <v>-61935.16</v>
+        <v>173265.84</v>
       </c>
       <c r="F98" s="84"/>
       <c r="G98" s="85">
         <f t="shared" si="16"/>
-        <v>-61935.16</v>
+        <v>173265.84</v>
       </c>
       <c r="H98" s="85">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>5197.9751999999999</v>
       </c>
       <c r="I98" s="125">
         <f t="shared" si="17"/>
@@ -9098,18 +9055,18 @@
       <c r="M98" s="147"/>
       <c r="N98" s="86">
         <f t="shared" si="21"/>
-        <v>173265.84</v>
+        <v>413664.84</v>
       </c>
       <c r="O98" s="139">
         <f t="shared" si="9"/>
-        <v>178463.84</v>
+        <v>426074.84</v>
       </c>
       <c r="P98" s="50">
         <f t="shared" ref="P98:P117" si="22">P97+0.01</f>
         <v>0.84000000000000052</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" s="129">
         <f t="shared" si="10"/>
         <v>85</v>
@@ -9122,11 +9079,11 @@
         <v>0.82</v>
       </c>
       <c r="E99" s="83">
-        <v>147600.85</v>
-      </c>
-      <c r="F99" s="84">
-        <f>62600.85+85000</f>
-        <v>147600.85</v>
+        <v>172200.85</v>
+      </c>
+      <c r="F99" s="338">
+        <f>E99</f>
+        <v>172200.85</v>
       </c>
       <c r="G99" s="85">
         <f t="shared" si="16"/>
@@ -9163,7 +9120,7 @@
         <v>0.85000000000000053</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" s="130">
         <f t="shared" si="10"/>
         <v>86</v>
@@ -9176,18 +9133,18 @@
         <v>0.82</v>
       </c>
       <c r="E100" s="84">
-        <v>147600.85999999999</v>
+        <v>167772.86</v>
       </c>
       <c r="F100" s="84">
         <v>152028.85999999999</v>
       </c>
       <c r="G100" s="111">
         <f t="shared" si="16"/>
-        <v>-4428</v>
+        <v>15744</v>
       </c>
       <c r="H100" s="111">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>472.32</v>
       </c>
       <c r="I100" s="126">
         <f t="shared" si="17"/>
@@ -9205,18 +9162,18 @@
       <c r="M100" s="148"/>
       <c r="N100" s="112">
         <f t="shared" si="21"/>
-        <v>167772.86</v>
+        <v>188416.86</v>
       </c>
       <c r="O100" s="140">
         <f t="shared" ref="O100:O117" si="23">ROUND(N100*3%,0) + N100</f>
-        <v>172805.86</v>
+        <v>194069.86</v>
       </c>
       <c r="P100" s="50">
         <f t="shared" si="22"/>
         <v>0.86000000000000054</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" s="129">
         <f t="shared" ref="A101:A117" si="24">A100+1</f>
         <v>87</v>
@@ -9229,11 +9186,11 @@
         <v>1.34</v>
       </c>
       <c r="E101" s="83">
-        <v>241200.87</v>
+        <v>281400.87</v>
       </c>
       <c r="F101" s="84">
         <f t="shared" ref="F101:F104" si="25">E101</f>
-        <v>241200.87</v>
+        <v>281400.87</v>
       </c>
       <c r="G101" s="85">
         <f t="shared" si="16"/>
@@ -9270,7 +9227,7 @@
         <v>0.87000000000000055</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" s="129">
         <f t="shared" si="24"/>
         <v>88</v>
@@ -9283,11 +9240,11 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E102" s="83">
-        <v>201600.88</v>
+        <v>235200.88</v>
       </c>
       <c r="F102" s="84">
         <f>E102</f>
-        <v>201600.88</v>
+        <v>235200.88</v>
       </c>
       <c r="G102" s="85">
         <f t="shared" si="16"/>
@@ -9324,7 +9281,7 @@
         <v>0.88000000000000056</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" s="129">
         <f t="shared" si="24"/>
         <v>89</v>
@@ -9337,11 +9294,11 @@
         <v>1.17</v>
       </c>
       <c r="E103" s="83">
-        <v>210600.89</v>
+        <v>245700.89</v>
       </c>
       <c r="F103" s="84">
         <f>E103</f>
-        <v>210600.89</v>
+        <v>245700.89</v>
       </c>
       <c r="G103" s="85">
         <f t="shared" si="16"/>
@@ -9378,7 +9335,7 @@
         <v>0.89000000000000057</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" s="129">
         <f t="shared" si="24"/>
         <v>90</v>
@@ -9391,11 +9348,11 @@
         <v>0.1</v>
       </c>
       <c r="E104" s="83">
-        <v>18000.900000000001</v>
+        <v>21000.9</v>
       </c>
       <c r="F104" s="84">
         <f t="shared" si="25"/>
-        <v>18000.900000000001</v>
+        <v>21000.9</v>
       </c>
       <c r="G104" s="85">
         <f t="shared" si="16"/>
@@ -9432,7 +9389,7 @@
         <v>0.90000000000000058</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105" s="129">
         <f t="shared" si="24"/>
         <v>91</v>
@@ -9445,18 +9402,18 @@
         <v>0.1</v>
       </c>
       <c r="E105" s="83">
-        <v>34985.910000000003</v>
+        <v>21510.91</v>
       </c>
       <c r="F105" s="84">
         <v>34490.910000000003</v>
       </c>
       <c r="G105" s="85">
         <f t="shared" si="16"/>
-        <v>495</v>
+        <v>-12980.000000000004</v>
       </c>
       <c r="H105" s="85">
         <f t="shared" si="19"/>
-        <v>14.85</v>
+        <v>0</v>
       </c>
       <c r="I105" s="125">
         <f t="shared" si="17"/>
@@ -9474,18 +9431,18 @@
       <c r="M105" s="147"/>
       <c r="N105" s="86">
         <f t="shared" si="21"/>
-        <v>21510.91</v>
+        <v>8020.91</v>
       </c>
       <c r="O105" s="139">
         <f t="shared" si="23"/>
-        <v>22155.91</v>
+        <v>8261.91</v>
       </c>
       <c r="P105" s="50">
         <f t="shared" si="22"/>
         <v>0.91000000000000059</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106" s="129">
         <f t="shared" si="24"/>
         <v>92</v>
@@ -9498,18 +9455,18 @@
         <v>0.1</v>
       </c>
       <c r="E106" s="83">
-        <v>17505.919999999998</v>
+        <v>20475.919999999998</v>
       </c>
       <c r="F106" s="84">
         <v>18030.919999999998</v>
       </c>
       <c r="G106" s="85">
         <f t="shared" si="16"/>
-        <v>-525</v>
+        <v>2445</v>
       </c>
       <c r="H106" s="85">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>73.349999999999994</v>
       </c>
       <c r="I106" s="125">
         <f t="shared" si="17"/>
@@ -9527,18 +9484,18 @@
       <c r="M106" s="147"/>
       <c r="N106" s="86">
         <f t="shared" si="21"/>
-        <v>20475.919999999998</v>
+        <v>23518.92</v>
       </c>
       <c r="O106" s="139">
         <f t="shared" si="23"/>
-        <v>21089.919999999998</v>
+        <v>24224.92</v>
       </c>
       <c r="P106" s="50">
         <f t="shared" si="22"/>
         <v>0.9200000000000006</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107" s="130">
         <f t="shared" si="24"/>
         <v>93</v>
@@ -9551,18 +9508,18 @@
         <v>0.1</v>
       </c>
       <c r="E107" s="84">
-        <v>17491.93</v>
+        <v>20475.93</v>
       </c>
       <c r="F107" s="84">
         <v>18016.93</v>
       </c>
       <c r="G107" s="111">
         <f t="shared" si="16"/>
-        <v>-525</v>
+        <v>2459</v>
       </c>
       <c r="H107" s="111">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>73.77</v>
       </c>
       <c r="I107" s="126">
         <f t="shared" si="17"/>
@@ -9580,18 +9537,18 @@
       <c r="M107" s="148"/>
       <c r="N107" s="86">
         <f t="shared" si="21"/>
-        <v>20475.93</v>
+        <v>23533.93</v>
       </c>
       <c r="O107" s="140">
         <f t="shared" si="23"/>
-        <v>21089.93</v>
+        <v>24239.93</v>
       </c>
       <c r="P107" s="50">
         <f t="shared" si="22"/>
         <v>0.9300000000000006</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108" s="130">
         <f t="shared" si="24"/>
         <v>94</v>
@@ -9604,11 +9561,11 @@
         <v>0.1</v>
       </c>
       <c r="E108" s="84">
-        <v>18000.939999999999</v>
+        <v>21000.94</v>
       </c>
       <c r="F108" s="84">
         <f t="shared" ref="F108:F113" si="26">E108</f>
-        <v>18000.939999999999</v>
+        <v>21000.94</v>
       </c>
       <c r="G108" s="111">
         <f t="shared" si="16"/>
@@ -9645,7 +9602,7 @@
         <v>0.94000000000000061</v>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="130">
         <f t="shared" si="24"/>
         <v>95</v>
@@ -9658,11 +9615,11 @@
         <v>0.1</v>
       </c>
       <c r="E109" s="84">
-        <v>18000.95</v>
-      </c>
-      <c r="F109" s="84">
+        <v>21000.95</v>
+      </c>
+      <c r="F109" s="338">
         <f t="shared" si="26"/>
-        <v>18000.95</v>
+        <v>21000.95</v>
       </c>
       <c r="G109" s="111">
         <f t="shared" si="16"/>
@@ -9699,7 +9656,7 @@
         <v>0.95000000000000062</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110" s="130">
         <f t="shared" si="24"/>
         <v>96</v>
@@ -9712,11 +9669,11 @@
         <v>0.1</v>
       </c>
       <c r="E110" s="84">
-        <v>17491.96</v>
-      </c>
-      <c r="F110" s="84">
-        <f t="shared" si="26"/>
-        <v>17491.96</v>
+        <v>21000.959999999999</v>
+      </c>
+      <c r="F110" s="338">
+        <f>E110</f>
+        <v>21000.959999999999</v>
       </c>
       <c r="G110" s="111">
         <f t="shared" si="16"/>
@@ -9756,7 +9713,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A111" s="130">
         <f t="shared" si="24"/>
         <v>97</v>
@@ -9769,11 +9726,11 @@
         <v>0.1</v>
       </c>
       <c r="E111" s="84">
-        <v>18000.97</v>
+        <v>21000.97</v>
       </c>
       <c r="F111" s="84">
         <f t="shared" si="26"/>
-        <v>18000.97</v>
+        <v>21000.97</v>
       </c>
       <c r="G111" s="111">
         <f t="shared" si="16"/>
@@ -9810,7 +9767,7 @@
         <v>0.97000000000000064</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A112" s="130">
         <f t="shared" si="24"/>
         <v>98</v>
@@ -9823,11 +9780,11 @@
         <v>0.1</v>
       </c>
       <c r="E112" s="84">
-        <v>18000.98</v>
+        <v>21000.98</v>
       </c>
       <c r="F112" s="84">
         <f t="shared" si="26"/>
-        <v>18000.98</v>
+        <v>21000.98</v>
       </c>
       <c r="G112" s="111">
         <f t="shared" si="16"/>
@@ -9864,7 +9821,7 @@
         <v>0.98000000000000065</v>
       </c>
     </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A113" s="130">
         <f t="shared" si="24"/>
         <v>99</v>
@@ -9877,11 +9834,11 @@
         <v>0.1</v>
       </c>
       <c r="E113" s="84">
-        <v>18000.990000000002</v>
+        <v>21000.99</v>
       </c>
       <c r="F113" s="84">
         <f t="shared" si="26"/>
-        <v>18000.990000000002</v>
+        <v>21000.99</v>
       </c>
       <c r="G113" s="111">
         <f t="shared" si="16"/>
@@ -9918,7 +9875,7 @@
         <v>0.99000000000000066</v>
       </c>
     </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A114" s="130">
         <f t="shared" si="24"/>
         <v>100</v>
@@ -9931,7 +9888,7 @@
         <v>0.1</v>
       </c>
       <c r="E114" s="84">
-        <v>52795</v>
+        <v>6236</v>
       </c>
       <c r="F114" s="84">
         <f>33780*2</f>
@@ -9939,7 +9896,7 @@
       </c>
       <c r="G114" s="111">
         <f t="shared" si="16"/>
-        <v>-14765</v>
+        <v>-61324</v>
       </c>
       <c r="H114" s="111">
         <f t="shared" si="19"/>
@@ -9961,18 +9918,18 @@
       <c r="M114" s="148"/>
       <c r="N114" s="86">
         <f t="shared" si="21"/>
-        <v>6236</v>
+        <v>-40323</v>
       </c>
       <c r="O114" s="140">
         <f t="shared" si="23"/>
-        <v>6423</v>
+        <v>-41533</v>
       </c>
       <c r="P114" s="50">
         <f t="shared" si="22"/>
         <v>1.0000000000000007</v>
       </c>
     </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A115" s="130">
         <f t="shared" si="24"/>
         <v>101</v>
@@ -9985,18 +9942,18 @@
         <v>0.1</v>
       </c>
       <c r="E115" s="84">
-        <v>17493.009999999998</v>
+        <v>20476.009999999998</v>
       </c>
       <c r="F115" s="84">
         <v>18018.009999999998</v>
       </c>
       <c r="G115" s="111">
         <f t="shared" si="16"/>
-        <v>-525</v>
+        <v>2458</v>
       </c>
       <c r="H115" s="111">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>73.739999999999995</v>
       </c>
       <c r="I115" s="126">
         <f t="shared" si="27"/>
@@ -10014,18 +9971,18 @@
       <c r="M115" s="148"/>
       <c r="N115" s="86">
         <f t="shared" si="21"/>
-        <v>20476.009999999998</v>
+        <v>23533.01</v>
       </c>
       <c r="O115" s="140">
         <f t="shared" si="23"/>
-        <v>21090.01</v>
+        <v>24239.01</v>
       </c>
       <c r="P115" s="50">
         <f t="shared" si="22"/>
         <v>1.0100000000000007</v>
       </c>
     </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A116" s="130">
         <f t="shared" si="24"/>
         <v>102</v>
@@ -10038,11 +9995,11 @@
         <v>0.1</v>
       </c>
       <c r="E116" s="84">
-        <v>18001.02</v>
+        <v>21001.02</v>
       </c>
       <c r="F116" s="84">
         <f>E116</f>
-        <v>18001.02</v>
+        <v>21001.02</v>
       </c>
       <c r="G116" s="111">
         <f t="shared" si="16"/>
@@ -10079,7 +10036,7 @@
         <v>1.0200000000000007</v>
       </c>
     </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A117" s="130">
         <f t="shared" si="24"/>
         <v>103</v>
@@ -10092,11 +10049,11 @@
         <v>0.1</v>
       </c>
       <c r="E117" s="84">
-        <v>18001.03</v>
+        <v>21001.03</v>
       </c>
       <c r="F117" s="84">
         <f>E117</f>
-        <v>18001.03</v>
+        <v>21001.03</v>
       </c>
       <c r="G117" s="111">
         <f t="shared" si="16"/>
@@ -10133,7 +10090,7 @@
         <v>1.0300000000000007</v>
       </c>
     </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A118" s="130"/>
       <c r="B118" s="108"/>
       <c r="C118" s="113"/>
@@ -10151,7 +10108,7 @@
       <c r="O118" s="140"/>
       <c r="P118" s="50"/>
     </row>
-    <row r="119" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="132"/>
       <c r="B119" s="133"/>
       <c r="C119" s="133"/>
@@ -10161,19 +10118,19 @@
       </c>
       <c r="E119" s="135">
         <f t="shared" si="29"/>
-        <v>39778263.560000002</v>
+        <v>46712826.56000001</v>
       </c>
       <c r="F119" s="136">
         <f>SUM(F15:F118)</f>
-        <v>15926490.739999998</v>
+        <v>18244513.000000004</v>
       </c>
       <c r="G119" s="136">
         <f t="shared" si="29"/>
-        <v>23851772.82</v>
+        <v>28468313.560000002</v>
       </c>
       <c r="H119" s="136">
         <f t="shared" si="29"/>
-        <v>676099.48949999991</v>
+        <v>802539.27840000007</v>
       </c>
       <c r="I119" s="137">
         <f t="shared" si="29"/>
@@ -10188,126 +10145,126 @@
       <c r="M119" s="150"/>
       <c r="N119" s="145">
         <f t="shared" si="29"/>
-        <v>46712826.56000001</v>
+        <v>51645806.560000002</v>
       </c>
       <c r="O119" s="142">
         <f t="shared" si="29"/>
-        <v>48114209.560000002</v>
-      </c>
-    </row>
-    <row r="120" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>53195178.559999995</v>
+      </c>
+    </row>
+    <row r="120" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B120" s="89"/>
       <c r="C120" s="89"/>
     </row>
-    <row r="121" spans="1:16" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="122" spans="1:16" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B122" s="301" t="s">
+    <row r="121" spans="1:16" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="122" spans="1:16" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B122" s="285" t="s">
         <v>103</v>
       </c>
-      <c r="C122" s="301"/>
-      <c r="D122" s="301"/>
-      <c r="E122" s="301"/>
-      <c r="F122" s="301"/>
-      <c r="G122" s="301"/>
-      <c r="H122" s="301"/>
-      <c r="I122" s="301"/>
-      <c r="J122" s="301"/>
-      <c r="K122" s="301"/>
-      <c r="L122" s="301"/>
-      <c r="M122" s="301"/>
-      <c r="N122" s="301"/>
-    </row>
-    <row r="123" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B123" s="301"/>
-      <c r="C123" s="301"/>
-      <c r="D123" s="301"/>
-      <c r="E123" s="301"/>
-      <c r="F123" s="301"/>
-      <c r="G123" s="301"/>
-      <c r="H123" s="301"/>
-      <c r="I123" s="301"/>
-      <c r="J123" s="301"/>
-      <c r="K123" s="301"/>
-      <c r="L123" s="301"/>
-      <c r="M123" s="301"/>
-      <c r="N123" s="301"/>
-    </row>
-    <row r="124" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B124" s="301"/>
-      <c r="C124" s="301"/>
-      <c r="D124" s="301"/>
-      <c r="E124" s="301"/>
-      <c r="F124" s="301"/>
-      <c r="G124" s="301"/>
-      <c r="H124" s="301"/>
-      <c r="I124" s="301"/>
-      <c r="J124" s="301"/>
-      <c r="K124" s="301"/>
-      <c r="L124" s="301"/>
-      <c r="M124" s="301"/>
-      <c r="N124" s="301"/>
-    </row>
-    <row r="125" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B125" s="301"/>
-      <c r="C125" s="301"/>
-      <c r="D125" s="301"/>
-      <c r="E125" s="301"/>
-      <c r="F125" s="301"/>
-      <c r="G125" s="301"/>
-      <c r="H125" s="301"/>
-      <c r="I125" s="301"/>
-      <c r="J125" s="301"/>
-      <c r="K125" s="301"/>
-      <c r="L125" s="301"/>
-      <c r="M125" s="301"/>
-      <c r="N125" s="301"/>
-    </row>
-    <row r="126" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B126" s="301"/>
-      <c r="C126" s="301"/>
-      <c r="D126" s="301"/>
-      <c r="E126" s="301"/>
-      <c r="F126" s="301"/>
-      <c r="G126" s="301"/>
-      <c r="H126" s="301"/>
-      <c r="I126" s="301"/>
-      <c r="J126" s="301"/>
-      <c r="K126" s="301"/>
-      <c r="L126" s="301"/>
-      <c r="M126" s="301"/>
-      <c r="N126" s="301"/>
-    </row>
-    <row r="127" spans="1:16" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B127" s="301"/>
-      <c r="C127" s="301"/>
-      <c r="D127" s="301"/>
-      <c r="E127" s="301"/>
-      <c r="F127" s="301"/>
-      <c r="G127" s="301"/>
-      <c r="H127" s="301"/>
-      <c r="I127" s="301"/>
-      <c r="J127" s="301"/>
-      <c r="K127" s="301"/>
-      <c r="L127" s="301"/>
-      <c r="M127" s="301"/>
-      <c r="N127" s="301"/>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C122" s="285"/>
+      <c r="D122" s="285"/>
+      <c r="E122" s="285"/>
+      <c r="F122" s="285"/>
+      <c r="G122" s="285"/>
+      <c r="H122" s="285"/>
+      <c r="I122" s="285"/>
+      <c r="J122" s="285"/>
+      <c r="K122" s="285"/>
+      <c r="L122" s="285"/>
+      <c r="M122" s="285"/>
+      <c r="N122" s="285"/>
+    </row>
+    <row r="123" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B123" s="285"/>
+      <c r="C123" s="285"/>
+      <c r="D123" s="285"/>
+      <c r="E123" s="285"/>
+      <c r="F123" s="285"/>
+      <c r="G123" s="285"/>
+      <c r="H123" s="285"/>
+      <c r="I123" s="285"/>
+      <c r="J123" s="285"/>
+      <c r="K123" s="285"/>
+      <c r="L123" s="285"/>
+      <c r="M123" s="285"/>
+      <c r="N123" s="285"/>
+    </row>
+    <row r="124" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B124" s="285"/>
+      <c r="C124" s="285"/>
+      <c r="D124" s="285"/>
+      <c r="E124" s="285"/>
+      <c r="F124" s="285"/>
+      <c r="G124" s="285"/>
+      <c r="H124" s="285"/>
+      <c r="I124" s="285"/>
+      <c r="J124" s="285"/>
+      <c r="K124" s="285"/>
+      <c r="L124" s="285"/>
+      <c r="M124" s="285"/>
+      <c r="N124" s="285"/>
+    </row>
+    <row r="125" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B125" s="285"/>
+      <c r="C125" s="285"/>
+      <c r="D125" s="285"/>
+      <c r="E125" s="285"/>
+      <c r="F125" s="285"/>
+      <c r="G125" s="285"/>
+      <c r="H125" s="285"/>
+      <c r="I125" s="285"/>
+      <c r="J125" s="285"/>
+      <c r="K125" s="285"/>
+      <c r="L125" s="285"/>
+      <c r="M125" s="285"/>
+      <c r="N125" s="285"/>
+    </row>
+    <row r="126" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B126" s="285"/>
+      <c r="C126" s="285"/>
+      <c r="D126" s="285"/>
+      <c r="E126" s="285"/>
+      <c r="F126" s="285"/>
+      <c r="G126" s="285"/>
+      <c r="H126" s="285"/>
+      <c r="I126" s="285"/>
+      <c r="J126" s="285"/>
+      <c r="K126" s="285"/>
+      <c r="L126" s="285"/>
+      <c r="M126" s="285"/>
+      <c r="N126" s="285"/>
+    </row>
+    <row r="127" spans="1:16" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B127" s="285"/>
+      <c r="C127" s="285"/>
+      <c r="D127" s="285"/>
+      <c r="E127" s="285"/>
+      <c r="F127" s="285"/>
+      <c r="G127" s="285"/>
+      <c r="H127" s="285"/>
+      <c r="I127" s="285"/>
+      <c r="J127" s="285"/>
+      <c r="K127" s="285"/>
+      <c r="L127" s="285"/>
+      <c r="M127" s="285"/>
+      <c r="N127" s="285"/>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B130">
         <v>1631378.049999997</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>249</v>
+        <v>223</v>
       </c>
       <c r="B134" s="216">
         <v>-3942</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>248</v>
+        <v>222</v>
       </c>
       <c r="B135">
         <v>-132000</v>
@@ -10315,6 +10272,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="A10:O10"/>
+    <mergeCell ref="A11:O11"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="K13:K14"/>
     <mergeCell ref="B122:N127"/>
     <mergeCell ref="D1:N1"/>
     <mergeCell ref="A4:O8"/>
@@ -10331,12 +10294,6 @@
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="I13:I14"/>
     <mergeCell ref="L13:L14"/>
-    <mergeCell ref="M13:M14"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="A10:O10"/>
-    <mergeCell ref="A11:O11"/>
-    <mergeCell ref="O13:O14"/>
-    <mergeCell ref="K13:K14"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="70" orientation="landscape" r:id="rId1"/>
@@ -10346,16 +10303,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56D35F41-74CB-4294-A7A2-EC3C67574818}">
   <dimension ref="C3:N65"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C3" s="19"/>
     </row>
-    <row r="4" spans="3:14" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:14" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C4" s="172" t="s">
         <v>190</v>
       </c>
@@ -10371,7 +10328,7 @@
       <c r="K4" s="19"/>
       <c r="L4" s="19"/>
     </row>
-    <row r="5" spans="3:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:14" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C5" s="174" t="s">
         <v>191</v>
       </c>
@@ -10388,7 +10345,7 @@
       <c r="M5" s="19"/>
       <c r="N5" s="19"/>
     </row>
-    <row r="6" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C6" s="174" t="s">
         <v>194</v>
       </c>
@@ -10402,7 +10359,7 @@
         <v>128</v>
       </c>
       <c r="H6" t="s">
-        <v>255</v>
+        <v>229</v>
       </c>
       <c r="J6" s="171"/>
       <c r="K6" s="19"/>
@@ -10410,7 +10367,7 @@
       <c r="M6" s="19"/>
       <c r="N6" s="19"/>
     </row>
-    <row r="7" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C7" s="47" t="s">
         <v>197</v>
       </c>
@@ -10420,42 +10377,42 @@
       <c r="M7" s="19"/>
       <c r="N7" s="19"/>
     </row>
-    <row r="8" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="C8" s="327" t="s">
-        <v>256</v>
-      </c>
-      <c r="D8" s="328"/>
-      <c r="E8" s="328"/>
-      <c r="F8" s="328"/>
-      <c r="G8" s="328"/>
-      <c r="H8" s="328"/>
-      <c r="I8" s="328"/>
-      <c r="J8" s="329"/>
+    <row r="8" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="C8" s="325" t="s">
+        <v>230</v>
+      </c>
+      <c r="D8" s="326"/>
+      <c r="E8" s="326"/>
+      <c r="F8" s="326"/>
+      <c r="G8" s="326"/>
+      <c r="H8" s="326"/>
+      <c r="I8" s="326"/>
+      <c r="J8" s="327"/>
       <c r="K8" s="19"/>
       <c r="L8" s="19"/>
       <c r="M8" s="19"/>
       <c r="N8" s="19"/>
     </row>
-    <row r="9" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C9" s="330"/>
-      <c r="D9" s="331"/>
-      <c r="E9" s="331"/>
-      <c r="F9" s="331"/>
-      <c r="G9" s="331"/>
-      <c r="H9" s="331"/>
-      <c r="I9" s="331"/>
-      <c r="J9" s="332"/>
+    <row r="9" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C9" s="328"/>
+      <c r="D9" s="329"/>
+      <c r="E9" s="329"/>
+      <c r="F9" s="329"/>
+      <c r="G9" s="329"/>
+      <c r="H9" s="329"/>
+      <c r="I9" s="329"/>
+      <c r="J9" s="330"/>
       <c r="K9" s="19"/>
       <c r="L9" s="19"/>
       <c r="M9" s="19"/>
       <c r="N9" s="19"/>
     </row>
-    <row r="11" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="12" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="C12" s="236" t="s">
+    <row r="11" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="C12" s="232" t="s">
         <v>190</v>
       </c>
-      <c r="D12" s="237">
+      <c r="D12" s="233">
         <v>1</v>
       </c>
       <c r="E12" s="169"/>
@@ -10465,8 +10422,8 @@
       <c r="I12" s="169"/>
       <c r="J12" s="170"/>
     </row>
-    <row r="13" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="C13" s="238" t="s">
+    <row r="13" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="C13" s="234" t="s">
         <v>191</v>
       </c>
       <c r="D13" s="19"/>
@@ -10477,10 +10434,10 @@
         <v>193</v>
       </c>
       <c r="J13" s="171"/>
-      <c r="L13" s="235"/>
-    </row>
-    <row r="14" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="C14" s="238" t="s">
+      <c r="L13" s="231"/>
+    </row>
+    <row r="14" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="C14" s="234" t="s">
         <v>194</v>
       </c>
       <c r="D14" s="19" t="s">
@@ -10494,40 +10451,40 @@
       </c>
       <c r="J14" s="171"/>
     </row>
-    <row r="15" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C15" s="47" t="s">
         <v>197</v>
       </c>
       <c r="J15" s="171"/>
     </row>
-    <row r="16" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="C16" s="333" t="s">
-        <v>257</v>
-      </c>
-      <c r="D16" s="328"/>
-      <c r="E16" s="328"/>
-      <c r="F16" s="328"/>
-      <c r="G16" s="328"/>
-      <c r="H16" s="328"/>
-      <c r="I16" s="328"/>
-      <c r="J16" s="329"/>
-    </row>
-    <row r="17" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C17" s="330"/>
-      <c r="D17" s="331"/>
-      <c r="E17" s="331"/>
-      <c r="F17" s="331"/>
-      <c r="G17" s="331"/>
-      <c r="H17" s="331"/>
-      <c r="I17" s="331"/>
-      <c r="J17" s="332"/>
-    </row>
-    <row r="19" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C20" s="241" t="s">
+    <row r="16" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="C16" s="331" t="s">
+        <v>231</v>
+      </c>
+      <c r="D16" s="326"/>
+      <c r="E16" s="326"/>
+      <c r="F16" s="326"/>
+      <c r="G16" s="326"/>
+      <c r="H16" s="326"/>
+      <c r="I16" s="326"/>
+      <c r="J16" s="327"/>
+    </row>
+    <row r="17" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C17" s="328"/>
+      <c r="D17" s="329"/>
+      <c r="E17" s="329"/>
+      <c r="F17" s="329"/>
+      <c r="G17" s="329"/>
+      <c r="H17" s="329"/>
+      <c r="I17" s="329"/>
+      <c r="J17" s="330"/>
+    </row>
+    <row r="19" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C20" s="237" t="s">
         <v>190</v>
       </c>
-      <c r="D20" s="242">
+      <c r="D20" s="238">
         <v>1</v>
       </c>
       <c r="E20" s="169"/>
@@ -10537,11 +10494,11 @@
       <c r="I20" s="169"/>
       <c r="J20" s="170"/>
     </row>
-    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C21" s="243" t="s">
+    <row r="21" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C21" s="239" t="s">
         <v>191</v>
       </c>
-      <c r="D21" s="244"/>
+      <c r="D21" s="240"/>
       <c r="E21" t="s">
         <v>192</v>
       </c>
@@ -10550,11 +10507,11 @@
       </c>
       <c r="J21" s="171"/>
     </row>
-    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C22" s="243" t="s">
+    <row r="22" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C22" s="239" t="s">
         <v>194</v>
       </c>
-      <c r="D22" s="244" t="s">
+      <c r="D22" s="240" t="s">
         <v>195</v>
       </c>
       <c r="E22" t="s">
@@ -10564,45 +10521,45 @@
         <v>128</v>
       </c>
       <c r="H22" t="s">
-        <v>258</v>
+        <v>232</v>
       </c>
       <c r="J22" s="171"/>
     </row>
-    <row r="23" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C23" s="243" t="s">
+    <row r="23" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C23" s="239" t="s">
         <v>197</v>
       </c>
-      <c r="D23" s="244"/>
+      <c r="D23" s="240"/>
       <c r="J23" s="171"/>
     </row>
-    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C24" s="327" t="s">
-        <v>263</v>
-      </c>
-      <c r="D24" s="328"/>
-      <c r="E24" s="328"/>
-      <c r="F24" s="328"/>
-      <c r="G24" s="328"/>
-      <c r="H24" s="328"/>
-      <c r="I24" s="328"/>
-      <c r="J24" s="329"/>
-    </row>
-    <row r="25" spans="3:10" ht="57.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C25" s="330"/>
-      <c r="D25" s="331"/>
-      <c r="E25" s="331"/>
-      <c r="F25" s="331"/>
-      <c r="G25" s="331"/>
-      <c r="H25" s="331"/>
-      <c r="I25" s="331"/>
-      <c r="J25" s="332"/>
-    </row>
-    <row r="27" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="28" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C28" s="247" t="s">
+    <row r="24" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C24" s="325" t="s">
+        <v>237</v>
+      </c>
+      <c r="D24" s="326"/>
+      <c r="E24" s="326"/>
+      <c r="F24" s="326"/>
+      <c r="G24" s="326"/>
+      <c r="H24" s="326"/>
+      <c r="I24" s="326"/>
+      <c r="J24" s="327"/>
+    </row>
+    <row r="25" spans="3:10" ht="57.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C25" s="328"/>
+      <c r="D25" s="329"/>
+      <c r="E25" s="329"/>
+      <c r="F25" s="329"/>
+      <c r="G25" s="329"/>
+      <c r="H25" s="329"/>
+      <c r="I25" s="329"/>
+      <c r="J25" s="330"/>
+    </row>
+    <row r="27" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C28" s="243" t="s">
         <v>190</v>
       </c>
-      <c r="D28" s="248">
+      <c r="D28" s="244">
         <v>1</v>
       </c>
       <c r="E28" s="169"/>
@@ -10612,11 +10569,11 @@
       <c r="I28" s="169"/>
       <c r="J28" s="170"/>
     </row>
-    <row r="29" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C29" s="249" t="s">
+    <row r="29" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C29" s="245" t="s">
         <v>191</v>
       </c>
-      <c r="D29" s="250"/>
+      <c r="D29" s="246"/>
       <c r="E29" t="s">
         <v>192</v>
       </c>
@@ -10625,11 +10582,11 @@
       </c>
       <c r="J29" s="171"/>
     </row>
-    <row r="30" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C30" s="249" t="s">
+    <row r="30" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C30" s="245" t="s">
         <v>194</v>
       </c>
-      <c r="D30" s="250" t="s">
+      <c r="D30" s="246" t="s">
         <v>195</v>
       </c>
       <c r="E30" t="s">
@@ -10639,45 +10596,45 @@
         <v>128</v>
       </c>
       <c r="H30" t="s">
-        <v>259</v>
+        <v>233</v>
       </c>
       <c r="J30" s="171"/>
     </row>
-    <row r="31" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C31" s="249" t="s">
+    <row r="31" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C31" s="245" t="s">
         <v>197</v>
       </c>
-      <c r="D31" s="250"/>
+      <c r="D31" s="246"/>
       <c r="J31" s="171"/>
     </row>
-    <row r="32" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C32" s="327" t="s">
-        <v>260</v>
-      </c>
-      <c r="D32" s="328"/>
-      <c r="E32" s="328"/>
-      <c r="F32" s="328"/>
-      <c r="G32" s="328"/>
-      <c r="H32" s="328"/>
-      <c r="I32" s="328"/>
-      <c r="J32" s="329"/>
-    </row>
-    <row r="33" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C33" s="330"/>
-      <c r="D33" s="331"/>
-      <c r="E33" s="331"/>
-      <c r="F33" s="331"/>
-      <c r="G33" s="331"/>
-      <c r="H33" s="331"/>
-      <c r="I33" s="331"/>
-      <c r="J33" s="332"/>
-    </row>
-    <row r="35" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="36" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C36" s="241" t="s">
+    <row r="32" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C32" s="325" t="s">
+        <v>234</v>
+      </c>
+      <c r="D32" s="326"/>
+      <c r="E32" s="326"/>
+      <c r="F32" s="326"/>
+      <c r="G32" s="326"/>
+      <c r="H32" s="326"/>
+      <c r="I32" s="326"/>
+      <c r="J32" s="327"/>
+    </row>
+    <row r="33" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C33" s="328"/>
+      <c r="D33" s="329"/>
+      <c r="E33" s="329"/>
+      <c r="F33" s="329"/>
+      <c r="G33" s="329"/>
+      <c r="H33" s="329"/>
+      <c r="I33" s="329"/>
+      <c r="J33" s="330"/>
+    </row>
+    <row r="35" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="36" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C36" s="237" t="s">
         <v>190</v>
       </c>
-      <c r="D36" s="242">
+      <c r="D36" s="238">
         <v>1</v>
       </c>
       <c r="E36" s="169"/>
@@ -10687,11 +10644,11 @@
       <c r="I36" s="169"/>
       <c r="J36" s="170"/>
     </row>
-    <row r="37" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C37" s="243" t="s">
+    <row r="37" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C37" s="239" t="s">
         <v>191</v>
       </c>
-      <c r="D37" s="244"/>
+      <c r="D37" s="240"/>
       <c r="E37" t="s">
         <v>192</v>
       </c>
@@ -10700,11 +10657,11 @@
       </c>
       <c r="J37" s="171"/>
     </row>
-    <row r="38" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C38" s="243" t="s">
+    <row r="38" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C38" s="239" t="s">
         <v>194</v>
       </c>
-      <c r="D38" s="244" t="s">
+      <c r="D38" s="240" t="s">
         <v>195</v>
       </c>
       <c r="E38" t="s">
@@ -10718,41 +10675,41 @@
       </c>
       <c r="J38" s="171"/>
     </row>
-    <row r="39" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C39" s="243" t="s">
+    <row r="39" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C39" s="239" t="s">
         <v>197</v>
       </c>
-      <c r="D39" s="244"/>
+      <c r="D39" s="240"/>
       <c r="J39" s="171"/>
     </row>
-    <row r="40" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C40" s="327" t="s">
-        <v>262</v>
-      </c>
-      <c r="D40" s="328"/>
-      <c r="E40" s="328"/>
-      <c r="F40" s="328"/>
-      <c r="G40" s="328"/>
-      <c r="H40" s="328"/>
-      <c r="I40" s="328"/>
-      <c r="J40" s="329"/>
-    </row>
-    <row r="41" spans="3:10" ht="24.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C41" s="330"/>
-      <c r="D41" s="331"/>
-      <c r="E41" s="331"/>
-      <c r="F41" s="331"/>
-      <c r="G41" s="331"/>
-      <c r="H41" s="331"/>
-      <c r="I41" s="331"/>
-      <c r="J41" s="332"/>
-    </row>
-    <row r="43" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="44" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C44" s="252" t="s">
+    <row r="40" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C40" s="325" t="s">
+        <v>236</v>
+      </c>
+      <c r="D40" s="326"/>
+      <c r="E40" s="326"/>
+      <c r="F40" s="326"/>
+      <c r="G40" s="326"/>
+      <c r="H40" s="326"/>
+      <c r="I40" s="326"/>
+      <c r="J40" s="327"/>
+    </row>
+    <row r="41" spans="3:10" ht="24.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C41" s="328"/>
+      <c r="D41" s="329"/>
+      <c r="E41" s="329"/>
+      <c r="F41" s="329"/>
+      <c r="G41" s="329"/>
+      <c r="H41" s="329"/>
+      <c r="I41" s="329"/>
+      <c r="J41" s="330"/>
+    </row>
+    <row r="43" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="44" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C44" s="248" t="s">
         <v>190</v>
       </c>
-      <c r="D44" s="253">
+      <c r="D44" s="249">
         <v>1</v>
       </c>
       <c r="E44" s="169"/>
@@ -10762,11 +10719,11 @@
       <c r="I44" s="169"/>
       <c r="J44" s="170"/>
     </row>
-    <row r="45" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C45" s="254" t="s">
+    <row r="45" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C45" s="250" t="s">
         <v>191</v>
       </c>
-      <c r="D45" s="255"/>
+      <c r="D45" s="251"/>
       <c r="E45" t="s">
         <v>192</v>
       </c>
@@ -10775,11 +10732,11 @@
       </c>
       <c r="J45" s="171"/>
     </row>
-    <row r="46" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C46" s="254" t="s">
+    <row r="46" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C46" s="250" t="s">
         <v>194</v>
       </c>
-      <c r="D46" s="255" t="s">
+      <c r="D46" s="251" t="s">
         <v>195</v>
       </c>
       <c r="E46" t="s">
@@ -10789,45 +10746,45 @@
         <v>128</v>
       </c>
       <c r="H46" t="s">
-        <v>264</v>
+        <v>238</v>
       </c>
       <c r="J46" s="171"/>
     </row>
-    <row r="47" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C47" s="254" t="s">
+    <row r="47" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C47" s="250" t="s">
         <v>197</v>
       </c>
-      <c r="D47" s="255"/>
+      <c r="D47" s="251"/>
       <c r="J47" s="171"/>
     </row>
-    <row r="48" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C48" s="327" t="s">
-        <v>265</v>
-      </c>
-      <c r="D48" s="328"/>
-      <c r="E48" s="328"/>
-      <c r="F48" s="328"/>
-      <c r="G48" s="328"/>
-      <c r="H48" s="328"/>
-      <c r="I48" s="328"/>
-      <c r="J48" s="329"/>
-    </row>
-    <row r="49" spans="3:10" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C49" s="330"/>
-      <c r="D49" s="331"/>
-      <c r="E49" s="331"/>
-      <c r="F49" s="331"/>
-      <c r="G49" s="331"/>
-      <c r="H49" s="331"/>
-      <c r="I49" s="331"/>
-      <c r="J49" s="332"/>
-    </row>
-    <row r="51" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="52" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C52" s="258" t="s">
+    <row r="48" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C48" s="325" t="s">
+        <v>239</v>
+      </c>
+      <c r="D48" s="326"/>
+      <c r="E48" s="326"/>
+      <c r="F48" s="326"/>
+      <c r="G48" s="326"/>
+      <c r="H48" s="326"/>
+      <c r="I48" s="326"/>
+      <c r="J48" s="327"/>
+    </row>
+    <row r="49" spans="3:10" ht="29.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C49" s="328"/>
+      <c r="D49" s="329"/>
+      <c r="E49" s="329"/>
+      <c r="F49" s="329"/>
+      <c r="G49" s="329"/>
+      <c r="H49" s="329"/>
+      <c r="I49" s="329"/>
+      <c r="J49" s="330"/>
+    </row>
+    <row r="51" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="52" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C52" s="254" t="s">
         <v>190</v>
       </c>
-      <c r="D52" s="259">
+      <c r="D52" s="255">
         <v>1</v>
       </c>
       <c r="E52" s="169"/>
@@ -10837,11 +10794,11 @@
       <c r="I52" s="169"/>
       <c r="J52" s="170"/>
     </row>
-    <row r="53" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C53" s="260" t="s">
+    <row r="53" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C53" s="256" t="s">
         <v>191</v>
       </c>
-      <c r="D53" s="261"/>
+      <c r="D53" s="257"/>
       <c r="E53" t="s">
         <v>192</v>
       </c>
@@ -10850,11 +10807,11 @@
       </c>
       <c r="J53" s="171"/>
     </row>
-    <row r="54" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C54" s="260" t="s">
+    <row r="54" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C54" s="256" t="s">
         <v>194</v>
       </c>
-      <c r="D54" s="261" t="s">
+      <c r="D54" s="257" t="s">
         <v>195</v>
       </c>
       <c r="E54" t="s">
@@ -10864,45 +10821,45 @@
         <v>128</v>
       </c>
       <c r="H54" t="s">
-        <v>266</v>
+        <v>240</v>
       </c>
       <c r="J54" s="171"/>
     </row>
-    <row r="55" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C55" s="260" t="s">
+    <row r="55" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C55" s="256" t="s">
         <v>197</v>
       </c>
-      <c r="D55" s="261"/>
+      <c r="D55" s="257"/>
       <c r="J55" s="171"/>
     </row>
-    <row r="56" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C56" s="327" t="s">
-        <v>267</v>
-      </c>
-      <c r="D56" s="328"/>
-      <c r="E56" s="328"/>
-      <c r="F56" s="328"/>
-      <c r="G56" s="328"/>
-      <c r="H56" s="328"/>
-      <c r="I56" s="328"/>
-      <c r="J56" s="329"/>
-    </row>
-    <row r="57" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C57" s="330"/>
-      <c r="D57" s="331"/>
-      <c r="E57" s="331"/>
-      <c r="F57" s="331"/>
-      <c r="G57" s="331"/>
-      <c r="H57" s="331"/>
-      <c r="I57" s="331"/>
-      <c r="J57" s="332"/>
-    </row>
-    <row r="59" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="60" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C60" s="264" t="s">
+    <row r="56" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C56" s="325" t="s">
+        <v>241</v>
+      </c>
+      <c r="D56" s="326"/>
+      <c r="E56" s="326"/>
+      <c r="F56" s="326"/>
+      <c r="G56" s="326"/>
+      <c r="H56" s="326"/>
+      <c r="I56" s="326"/>
+      <c r="J56" s="327"/>
+    </row>
+    <row r="57" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C57" s="328"/>
+      <c r="D57" s="329"/>
+      <c r="E57" s="329"/>
+      <c r="F57" s="329"/>
+      <c r="G57" s="329"/>
+      <c r="H57" s="329"/>
+      <c r="I57" s="329"/>
+      <c r="J57" s="330"/>
+    </row>
+    <row r="59" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C60" s="260" t="s">
         <v>190</v>
       </c>
-      <c r="D60" s="265">
+      <c r="D60" s="261">
         <v>1</v>
       </c>
       <c r="E60" s="169"/>
@@ -10912,11 +10869,11 @@
       <c r="I60" s="169"/>
       <c r="J60" s="170"/>
     </row>
-    <row r="61" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C61" s="266" t="s">
+    <row r="61" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C61" s="262" t="s">
         <v>191</v>
       </c>
-      <c r="D61" s="267"/>
+      <c r="D61" s="263"/>
       <c r="E61" t="s">
         <v>192</v>
       </c>
@@ -10925,11 +10882,11 @@
       </c>
       <c r="J61" s="171"/>
     </row>
-    <row r="62" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C62" s="266" t="s">
+    <row r="62" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C62" s="262" t="s">
         <v>194</v>
       </c>
-      <c r="D62" s="267" t="s">
+      <c r="D62" s="263" t="s">
         <v>195</v>
       </c>
       <c r="E62" t="s">
@@ -10939,38 +10896,38 @@
         <v>128</v>
       </c>
       <c r="H62" t="s">
-        <v>269</v>
+        <v>243</v>
       </c>
       <c r="J62" s="171"/>
     </row>
-    <row r="63" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C63" s="266" t="s">
+    <row r="63" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C63" s="262" t="s">
         <v>197</v>
       </c>
-      <c r="D63" s="267"/>
+      <c r="D63" s="263"/>
       <c r="J63" s="171"/>
     </row>
-    <row r="64" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C64" s="327" t="s">
-        <v>268</v>
-      </c>
-      <c r="D64" s="328"/>
-      <c r="E64" s="328"/>
-      <c r="F64" s="328"/>
-      <c r="G64" s="328"/>
-      <c r="H64" s="328"/>
-      <c r="I64" s="328"/>
-      <c r="J64" s="329"/>
-    </row>
-    <row r="65" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C65" s="330"/>
-      <c r="D65" s="331"/>
-      <c r="E65" s="331"/>
-      <c r="F65" s="331"/>
-      <c r="G65" s="331"/>
-      <c r="H65" s="331"/>
-      <c r="I65" s="331"/>
-      <c r="J65" s="332"/>
+    <row r="64" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C64" s="325" t="s">
+        <v>242</v>
+      </c>
+      <c r="D64" s="326"/>
+      <c r="E64" s="326"/>
+      <c r="F64" s="326"/>
+      <c r="G64" s="326"/>
+      <c r="H64" s="326"/>
+      <c r="I64" s="326"/>
+      <c r="J64" s="327"/>
+    </row>
+    <row r="65" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C65" s="328"/>
+      <c r="D65" s="329"/>
+      <c r="E65" s="329"/>
+      <c r="F65" s="329"/>
+      <c r="G65" s="329"/>
+      <c r="H65" s="329"/>
+      <c r="I65" s="329"/>
+      <c r="J65" s="330"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/2026/ITALIA/Agosto/Agosto ITALIA.xlsx
+++ b/2026/ITALIA/Agosto/Agosto ITALIA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\ITALIA\Agosto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\ITALIA\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88FD79D5-21A0-4CF8-928A-6D33C8C68AA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{637EF035-5676-43EE-A87F-3E2C6796C587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="4" r:id="rId1"/>
@@ -22,16 +22,11 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$159</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="281">
   <si>
     <t>TOTAL</t>
   </si>
@@ -707,46 +702,6 @@
   </si>
   <si>
     <t>10A</t>
-  </si>
-  <si>
-    <t>10 A deposito $285.000 06/08 o 07/08</t>
-  </si>
-  <si>
-    <t>adabeleo19@gmail.com agregar a la cadena de mail</t>
-  </si>
-  <si>
-    <t>19 y Cochera con 00 centavos</t>
-  </si>
-  <si>
-    <t>10B</t>
-  </si>
-  <si>
-    <t>Transfirio $50.400 el 12/08 para sus extraordinarias</t>
-  </si>
-  <si>
-    <t>Inicia un plan de pagos en donde abona $140.000 en el mes de julio - Y ademas consta de 9 cuotas de $130.000 - Mes de agosto arranca debiendo abonar: $365.200,74</t>
-  </si>
-  <si>
-    <t>En la UF 19 viene figurando que tiene "dinero a favor pagando de mas" - Ese dinero a favor es en teoria para la cochera 100 - En Junio pago $33.780 de mas y en Julio pago $33.780 de mas tambien - De cochera debe abonar $6.236 y de UF (19) debe abonar $280.493,19 - 12043 de punitorios = $268.450,19 - Abonan el 14/08 creo un poco menos de lo que debian abonar : lo informan x mail</t>
-  </si>
-  <si>
-    <t>9d</t>
-  </si>
-  <si>
-    <t>Lucas Calviño 9D: Dice que tiene un deposito en el mes pasado por $320.000 sin identificar y este mes transfirió $172.200,65 - Queda con un saldo restante a abonar de 244.922</t>
-  </si>
-  <si>
-    <t>6f</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Angelica 6F: Transfirió $220.000 el 21/08
-</t>
-  </si>
-  <si>
-    <t>Mama me dijo que hay que revisar a un tal Rajmilevich</t>
-  </si>
-  <si>
-    <t>?</t>
   </si>
   <si>
     <t>VTO 17/09</t>
@@ -921,6 +876,35 @@
   <si>
     <t>FCI - SALDO INICIAL</t>
   </si>
+  <si>
+    <t xml:space="preserve">10A deposito $300.000 el 08/09
+</t>
+  </si>
+  <si>
+    <t>4A pago $297.000,02 el 09/08 LE ERRO A LOS CENTAVOS</t>
+  </si>
+  <si>
+    <t>Agregar a panchomorena27@gmail.com a la cadena de mail</t>
+  </si>
+  <si>
+    <t>03 - PB C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deposito $162.000 14/09 y se transfirió saldo $800,03.
+</t>
+  </si>
+  <si>
+    <t>Ricardo Vega transfirio $307.000 el 04/09</t>
+  </si>
+  <si>
+    <t>1A</t>
+  </si>
+  <si>
+    <t>6F - UF 46</t>
+  </si>
+  <si>
+    <t>Deposito 17/09 $250.000</t>
+  </si>
 </sst>
 </file>
 
@@ -936,7 +920,7 @@
     <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="168" formatCode="0.000"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1105,16 +1089,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="19">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1213,13 +1189,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
+        <fgColor theme="3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF74FA84"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1789,13 +1771,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="316">
+  <cellXfs count="320">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2101,89 +2082,234 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="44" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="3"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="43" fontId="17" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="10" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="9" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="42" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="10" fillId="2" borderId="42" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="10" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="10" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="8" fontId="10" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="8" fontId="10" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="44" fontId="10" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="17" fillId="7" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="44" fontId="10" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="10" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="10" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="10" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2191,12 +2317,6 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2227,84 +2347,6 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2323,70 +2365,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="18" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="17" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="10" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="6" fillId="9" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="42" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="10" fillId="2" borderId="42" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="10" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="10" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="8" fontId="10" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="8" fontId="10" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="44" fontId="10" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="17" fillId="7" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="4">
-    <cellStyle name="Hipervínculo" xfId="3" builtinId="8"/>
+  <cellStyles count="3">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2395,8 +2383,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF74FA84"/>
       <color rgb="FF00FF00"/>
-      <color rgb="FF74FA84"/>
       <color rgb="FFCCCCFF"/>
     </mruColors>
   </colors>
@@ -2470,9 +2458,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2510,9 +2498,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2545,26 +2533,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2597,26 +2568,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2791,31 +2745,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E413A25D-5161-4141-BE0B-6E37A2A76CA5}">
   <dimension ref="A1:M160"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" customWidth="1"/>
+    <col min="6" max="6" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.28515625" customWidth="1"/>
+    <col min="10" max="10" width="16.33203125" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
-      <c r="B1" s="228" t="s">
+      <c r="B1" s="258" t="s">
         <v>146</v>
       </c>
-      <c r="C1" s="228"/>
-      <c r="D1" s="228"/>
-      <c r="E1" s="229"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C1" s="258"/>
+      <c r="D1" s="258"/>
+      <c r="E1" s="259"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="9" t="s">
         <v>148</v>
@@ -2824,16 +2778,16 @@
       <c r="D2" s="3"/>
       <c r="E2" s="4"/>
     </row>
-    <row r="3" spans="1:5" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2"/>
-      <c r="B3" s="234" t="s">
+      <c r="B3" s="262" t="s">
         <v>187</v>
       </c>
-      <c r="C3" s="234"/>
-      <c r="D3" s="234"/>
-      <c r="E3" s="235"/>
-    </row>
-    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C3" s="262"/>
+      <c r="D3" s="262"/>
+      <c r="E3" s="263"/>
+    </row>
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>100</v>
       </c>
@@ -2844,12 +2798,12 @@
       <c r="D4" s="7"/>
       <c r="E4" s="8"/>
     </row>
-    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>147</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="3" t="s">
@@ -2857,7 +2811,7 @@
       </c>
       <c r="E5" s="10"/>
     </row>
-    <row r="6" spans="1:5" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="85" t="s">
         <v>137</v>
       </c>
@@ -2868,95 +2822,95 @@
       </c>
       <c r="E6" s="8"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="48"/>
-      <c r="B8" s="236" t="s">
-        <v>235</v>
-      </c>
-      <c r="C8" s="236"/>
+      <c r="B8" s="264" t="s">
+        <v>222</v>
+      </c>
+      <c r="C8" s="264"/>
       <c r="D8" s="48"/>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="48"/>
-      <c r="B9" s="236"/>
-      <c r="C9" s="236"/>
+      <c r="B9" s="264"/>
+      <c r="C9" s="264"/>
       <c r="D9" s="48"/>
       <c r="E9" s="48"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="48"/>
-      <c r="B10" s="236"/>
-      <c r="C10" s="236"/>
+      <c r="B10" s="264"/>
+      <c r="C10" s="264"/>
       <c r="D10" s="48"/>
       <c r="E10" s="48"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="48"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
       <c r="E11" s="48"/>
     </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="48"/>
       <c r="B12" s="48"/>
       <c r="C12" s="48"/>
       <c r="D12" s="48"/>
       <c r="E12" s="48"/>
     </row>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="237" t="s">
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="265" t="s">
         <v>103</v>
       </c>
-      <c r="B13" s="237"/>
-      <c r="C13" s="237"/>
-      <c r="D13" s="237"/>
-      <c r="E13" s="237"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="237"/>
-      <c r="B14" s="237"/>
-      <c r="C14" s="237"/>
-      <c r="D14" s="237"/>
-      <c r="E14" s="237"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="237"/>
-      <c r="B15" s="237"/>
-      <c r="C15" s="237"/>
-      <c r="D15" s="237"/>
-      <c r="E15" s="237"/>
-    </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="237"/>
-      <c r="B16" s="237"/>
-      <c r="C16" s="237"/>
-      <c r="D16" s="237"/>
-      <c r="E16" s="237"/>
-    </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="265"/>
+      <c r="C13" s="265"/>
+      <c r="D13" s="265"/>
+      <c r="E13" s="265"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="265"/>
+      <c r="B14" s="265"/>
+      <c r="C14" s="265"/>
+      <c r="D14" s="265"/>
+      <c r="E14" s="265"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="265"/>
+      <c r="B15" s="265"/>
+      <c r="C15" s="265"/>
+      <c r="D15" s="265"/>
+      <c r="E15" s="265"/>
+    </row>
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="265"/>
+      <c r="B16" s="265"/>
+      <c r="C16" s="265"/>
+      <c r="D16" s="265"/>
+      <c r="E16" s="265"/>
+    </row>
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="48"/>
       <c r="B17" s="48"/>
       <c r="C17" s="48"/>
       <c r="D17" s="48"/>
       <c r="E17" s="48"/>
     </row>
-    <row r="18" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="169"/>
       <c r="B18" s="48"/>
       <c r="C18" s="48"/>
       <c r="D18" s="48"/>
       <c r="E18" s="48"/>
     </row>
-    <row r="19" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="48"/>
       <c r="B19" s="48"/>
       <c r="C19" s="48"/>
       <c r="D19" s="48"/>
       <c r="E19" s="48"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="170" t="s">
         <v>104</v>
       </c>
@@ -2965,7 +2919,7 @@
       <c r="D20" s="58"/>
       <c r="E20" s="59"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="36" t="s">
         <v>138</v>
       </c>
@@ -2974,11 +2928,11 @@
       <c r="D21" s="112"/>
       <c r="E21" s="145"/>
     </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="230" t="s">
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="260" t="s">
         <v>161</v>
       </c>
-      <c r="B22" s="231"/>
+      <c r="B22" s="261"/>
       <c r="C22" s="173"/>
       <c r="D22" s="174">
         <v>2415207.52</v>
@@ -2986,11 +2940,11 @@
       <c r="E22" s="146"/>
       <c r="H22" s="19"/>
     </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="230" t="s">
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="260" t="s">
         <v>162</v>
       </c>
-      <c r="B23" s="231"/>
+      <c r="B23" s="261"/>
       <c r="C23" s="173"/>
       <c r="D23" s="174">
         <v>-525307.52</v>
@@ -2998,11 +2952,11 @@
       <c r="E23" s="20"/>
       <c r="H23" s="19"/>
     </row>
-    <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="230" t="s">
+    <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="260" t="s">
         <v>1</v>
       </c>
-      <c r="B24" s="231"/>
+      <c r="B24" s="261"/>
       <c r="C24" s="173"/>
       <c r="D24" s="175">
         <v>0</v>
@@ -3011,7 +2965,7 @@
       <c r="F24" s="199"/>
       <c r="H24" s="19"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="176" t="s">
         <v>105</v>
       </c>
@@ -3023,7 +2977,7 @@
         <v>1889900</v>
       </c>
     </row>
-    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="176" t="s">
         <v>176</v>
       </c>
@@ -3032,49 +2986,49 @@
       <c r="D26" s="22"/>
       <c r="E26" s="148"/>
     </row>
-    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="173"/>
       <c r="B27" s="173"/>
       <c r="C27" s="173"/>
       <c r="D27" s="35"/>
       <c r="E27" s="160"/>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="173"/>
       <c r="B28" s="173"/>
       <c r="C28" s="173"/>
       <c r="D28" s="35"/>
       <c r="E28" s="160"/>
     </row>
-    <row r="29" spans="1:8" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="173"/>
       <c r="B29" s="173"/>
       <c r="C29" s="173"/>
       <c r="D29" s="35"/>
       <c r="E29" s="160"/>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="173"/>
       <c r="B30" s="173"/>
       <c r="C30" s="173"/>
       <c r="D30" s="35"/>
       <c r="E30" s="149"/>
     </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="173"/>
       <c r="B31" s="173"/>
       <c r="C31" s="173"/>
       <c r="D31" s="35"/>
       <c r="E31" s="149"/>
     </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="173"/>
       <c r="B32" s="173"/>
       <c r="C32" s="173"/>
       <c r="D32" s="35"/>
       <c r="E32" s="149"/>
     </row>
-    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="176" t="s">
         <v>105</v>
       </c>
@@ -3086,7 +3040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="36" t="s">
         <v>139</v>
       </c>
@@ -3095,9 +3049,9 @@
       <c r="D34" s="22"/>
       <c r="E34" s="148"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="173" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="B35" s="178"/>
       <c r="C35" s="178"/>
@@ -3110,9 +3064,9 @@
       </c>
       <c r="G35" s="66"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="173" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="B36" s="178"/>
       <c r="C36" s="178"/>
@@ -3120,13 +3074,13 @@
         <v>1488022.91</v>
       </c>
       <c r="E36" s="149" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="G36" s="66"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="173" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="B37" s="178"/>
       <c r="C37" s="178"/>
@@ -3134,11 +3088,11 @@
         <v>1027794.88</v>
       </c>
       <c r="E37" s="149" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="G37" s="66"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="173" t="s">
         <v>141</v>
       </c>
@@ -3148,11 +3102,11 @@
         <v>201343.09</v>
       </c>
       <c r="E38" s="149" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="G38" s="66"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="173" t="s">
         <v>143</v>
       </c>
@@ -3167,7 +3121,7 @@
       </c>
       <c r="G39" s="50"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="173" t="s">
         <v>142</v>
       </c>
@@ -3181,7 +3135,7 @@
         <v>Debito 12/08</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="173" t="s">
         <v>149</v>
       </c>
@@ -3190,7 +3144,7 @@
       <c r="D41" s="35"/>
       <c r="E41" s="149"/>
     </row>
-    <row r="42" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="176" t="s">
         <v>140</v>
       </c>
@@ -3202,7 +3156,7 @@
         <v>2845932.32</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
         <v>106</v>
       </c>
@@ -3211,33 +3165,33 @@
       <c r="D43" s="23"/>
       <c r="E43" s="150"/>
     </row>
-    <row r="44" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="238" t="s">
+    <row r="44" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="255" t="s">
         <v>183</v>
       </c>
-      <c r="B44" s="239"/>
+      <c r="B44" s="256"/>
       <c r="C44" s="26"/>
-      <c r="D44" s="309">
+      <c r="D44" s="222">
         <v>7805</v>
       </c>
       <c r="E44" s="20" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="238" t="s">
+    <row r="45" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="255" t="s">
         <v>185</v>
       </c>
-      <c r="B45" s="239"/>
+      <c r="B45" s="256"/>
       <c r="C45" s="26"/>
-      <c r="D45" s="309">
+      <c r="D45" s="222">
         <v>213891</v>
       </c>
       <c r="E45" s="20" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="21" t="s">
         <v>107</v>
       </c>
@@ -3249,7 +3203,7 @@
         <v>221696</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="14" t="s">
         <v>108</v>
       </c>
@@ -3258,7 +3212,7 @@
       <c r="D47" s="28"/>
       <c r="E47" s="151"/>
     </row>
-    <row r="48" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="29" t="s">
         <v>109</v>
       </c>
@@ -3270,10 +3224,10 @@
         <v>568601.14</v>
       </c>
       <c r="E48" s="113" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="29" t="s">
         <v>109</v>
       </c>
@@ -3286,7 +3240,7 @@
       </c>
       <c r="E49" s="181"/>
     </row>
-    <row r="50" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="29" t="s">
         <v>177</v>
       </c>
@@ -3299,7 +3253,7 @@
       </c>
       <c r="E50" s="20"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="29" t="s">
         <v>178</v>
       </c>
@@ -3310,20 +3264,20 @@
       </c>
       <c r="E51" s="20"/>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="238" t="s">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" s="255" t="s">
         <v>110</v>
       </c>
-      <c r="B52" s="239"/>
+      <c r="B52" s="256"/>
       <c r="C52" s="29"/>
       <c r="D52" s="30">
         <v>5805252.4400000004</v>
       </c>
       <c r="E52" s="113" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="32" t="s">
         <v>111</v>
       </c>
@@ -3332,7 +3286,7 @@
       <c r="D53" s="30"/>
       <c r="E53" s="20"/>
     </row>
-    <row r="54" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="21" t="s">
         <v>112</v>
       </c>
@@ -3344,54 +3298,54 @@
         <v>6373853.5800000001</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="14"/>
       <c r="B55" s="21"/>
       <c r="C55" s="21"/>
       <c r="D55" s="22"/>
       <c r="E55" s="153"/>
     </row>
-    <row r="56" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="232" t="s">
+    <row r="56" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="249" t="s">
         <v>164</v>
       </c>
-      <c r="B56" s="233"/>
+      <c r="B56" s="250"/>
       <c r="C56" s="29"/>
       <c r="D56" s="30">
         <v>285000</v>
       </c>
       <c r="E56" s="159" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="232" t="s">
-        <v>256</v>
-      </c>
-      <c r="B57" s="233"/>
+        <v>232</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="249" t="s">
+        <v>243</v>
+      </c>
+      <c r="B57" s="250"/>
       <c r="C57" s="29"/>
       <c r="D57" s="30">
         <v>200000</v>
       </c>
       <c r="E57" s="159" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" ht="186.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="232" t="s">
-        <v>255</v>
-      </c>
-      <c r="B58" s="233"/>
+        <v>244</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="186.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="249" t="s">
+        <v>242</v>
+      </c>
+      <c r="B58" s="250"/>
       <c r="C58" s="29"/>
       <c r="D58" s="30">
         <v>3300000</v>
       </c>
       <c r="E58" s="159" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="F58" s="50"/>
     </row>
-    <row r="59" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="16" t="s">
         <v>210</v>
       </c>
@@ -3403,9 +3357,9 @@
       <c r="E59" s="34"/>
       <c r="F59" s="200"/>
     </row>
-    <row r="60" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="87" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="B60" s="17"/>
       <c r="C60" s="29"/>
@@ -3413,55 +3367,55 @@
         <v>638000</v>
       </c>
       <c r="E60" s="34" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="F60" s="50"/>
     </row>
-    <row r="61" spans="1:6" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="232" t="s">
-        <v>244</v>
-      </c>
-      <c r="B61" s="233"/>
+    <row r="61" spans="1:6" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="249" t="s">
+        <v>231</v>
+      </c>
+      <c r="B61" s="250"/>
       <c r="C61" s="29"/>
       <c r="D61" s="30">
         <v>31400</v>
       </c>
       <c r="E61" s="34" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="F61" s="50"/>
     </row>
-    <row r="62" spans="1:6" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="232" t="s">
-        <v>243</v>
-      </c>
-      <c r="B62" s="233"/>
+    <row r="62" spans="1:6" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="249" t="s">
+        <v>230</v>
+      </c>
+      <c r="B62" s="250"/>
       <c r="C62" s="29"/>
       <c r="D62" s="30">
         <v>31400</v>
       </c>
       <c r="E62" s="34" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="F62" s="50"/>
     </row>
-    <row r="63" spans="1:6" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="232" t="s">
-        <v>247</v>
-      </c>
-      <c r="B63" s="233"/>
+    <row r="63" spans="1:6" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="249" t="s">
+        <v>234</v>
+      </c>
+      <c r="B63" s="250"/>
       <c r="C63" s="29"/>
       <c r="D63" s="30">
         <v>90000</v>
       </c>
       <c r="E63" s="159" t="s">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="F63" s="50"/>
     </row>
-    <row r="64" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="87" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="B64" s="17"/>
       <c r="C64" s="29"/>
@@ -3469,39 +3423,39 @@
         <v>155300</v>
       </c>
       <c r="E64" s="159" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="F64" s="50"/>
     </row>
-    <row r="65" spans="1:7" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="232" t="s">
-        <v>251</v>
-      </c>
-      <c r="B65" s="233"/>
+    <row r="65" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="249" t="s">
+        <v>238</v>
+      </c>
+      <c r="B65" s="250"/>
       <c r="C65" s="29"/>
       <c r="D65" s="30">
         <v>500000</v>
       </c>
       <c r="E65" s="159" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="F65" s="50"/>
     </row>
-    <row r="66" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="232" t="s">
-        <v>240</v>
-      </c>
-      <c r="B66" s="233"/>
+    <row r="66" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="249" t="s">
+        <v>227</v>
+      </c>
+      <c r="B66" s="250"/>
       <c r="C66" s="29"/>
       <c r="D66" s="30">
         <v>27660.41</v>
       </c>
       <c r="E66" s="159" t="s">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="F66" s="50"/>
     </row>
-    <row r="67" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="87" t="s">
         <v>199</v>
       </c>
@@ -3511,25 +3465,25 @@
         <v>379800</v>
       </c>
       <c r="E67" s="159" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="F67" s="50"/>
     </row>
-    <row r="68" spans="1:7" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="232" t="s">
-        <v>237</v>
-      </c>
-      <c r="B68" s="233"/>
+    <row r="68" spans="1:7" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="249" t="s">
+        <v>224</v>
+      </c>
+      <c r="B68" s="250"/>
       <c r="C68" s="29"/>
       <c r="D68" s="30">
         <v>124611.12</v>
       </c>
       <c r="E68" s="159" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="F68" s="50"/>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" s="21" t="s">
         <v>0</v>
       </c>
@@ -3541,7 +3495,7 @@
         <v>5770161.5300000003</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" s="14" t="s">
         <v>113</v>
       </c>
@@ -3550,76 +3504,76 @@
       <c r="D70" s="15"/>
       <c r="E70" s="145"/>
     </row>
-    <row r="71" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="232" t="s">
-        <v>238</v>
-      </c>
-      <c r="B71" s="233"/>
+    <row r="71" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="249" t="s">
+        <v>225</v>
+      </c>
+      <c r="B71" s="250"/>
       <c r="C71" s="18"/>
-      <c r="D71" s="310">
+      <c r="D71" s="223">
         <v>781000</v>
       </c>
       <c r="E71" s="159" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="G71" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="232" t="s">
-        <v>262</v>
-      </c>
-      <c r="B72" s="233"/>
+    <row r="72" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="249" t="s">
+        <v>249</v>
+      </c>
+      <c r="B72" s="250"/>
       <c r="C72" s="18"/>
-      <c r="D72" s="311">
+      <c r="D72" s="224">
         <f>24000+72000</f>
         <v>96000</v>
       </c>
       <c r="E72" s="159" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="87" t="s">
-        <v>263</v>
-      </c>
-      <c r="B73" s="225"/>
+        <v>250</v>
+      </c>
+      <c r="B73" s="17"/>
       <c r="C73" s="18"/>
-      <c r="D73" s="311">
+      <c r="D73" s="224">
         <v>220000</v>
       </c>
       <c r="E73" s="159" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="16" t="s">
         <v>163</v>
       </c>
       <c r="B74" s="17"/>
       <c r="C74" s="18"/>
-      <c r="D74" s="311">
+      <c r="D74" s="224">
         <v>250000</v>
       </c>
       <c r="E74" s="159" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="87" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="B75" s="17"/>
       <c r="C75" s="18"/>
-      <c r="D75" s="311">
+      <c r="D75" s="224">
         <v>50000</v>
       </c>
       <c r="E75" s="159" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" s="21" t="s">
         <v>105</v>
       </c>
@@ -3631,7 +3585,7 @@
         <v>1397000</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" s="14" t="s">
         <v>114</v>
       </c>
@@ -3640,30 +3594,30 @@
       <c r="D77" s="38"/>
       <c r="E77" s="41"/>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="29" t="s">
         <v>215</v>
       </c>
       <c r="B78" s="86"/>
       <c r="C78" s="86"/>
-      <c r="D78" s="312">
+      <c r="D78" s="225">
         <f>65000+29590.38</f>
         <v>94590.38</v>
       </c>
       <c r="E78" s="154"/>
     </row>
-    <row r="79" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="238" t="s">
+    <row r="79" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="255" t="s">
         <v>214</v>
       </c>
-      <c r="B79" s="239"/>
+      <c r="B79" s="256"/>
       <c r="C79" s="86"/>
-      <c r="D79" s="312">
+      <c r="D79" s="225">
         <v>269207.65999999997</v>
       </c>
       <c r="E79" s="154"/>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" s="39" t="s">
         <v>105</v>
       </c>
@@ -3675,14 +3629,14 @@
         <v>363798.04</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="29"/>
       <c r="B81" s="29"/>
       <c r="C81" s="29"/>
       <c r="D81" s="42"/>
       <c r="E81" s="43"/>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="44" t="s">
         <v>115</v>
       </c>
@@ -3693,13 +3647,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="47"/>
       <c r="D83" s="48"/>
       <c r="E83" s="49"/>
       <c r="F83" s="50"/>
     </row>
-    <row r="84" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="51" t="s">
         <v>116</v>
       </c>
@@ -3713,16 +3667,16 @@
       <c r="F84" s="56"/>
       <c r="G84" s="50"/>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="D85" s="48"/>
       <c r="E85" s="48"/>
     </row>
-    <row r="86" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D86" s="48"/>
       <c r="E86" s="48"/>
       <c r="H86" s="57"/>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="11" t="s">
         <v>117</v>
       </c>
@@ -3731,34 +3685,34 @@
       <c r="D87" s="58"/>
       <c r="E87" s="59"/>
     </row>
-    <row r="88" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="244"/>
-      <c r="B88" s="244"/>
+    <row r="88" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="257"/>
+      <c r="B88" s="257"/>
       <c r="C88" s="31"/>
-      <c r="D88" s="240"/>
-      <c r="E88" s="242"/>
-    </row>
-    <row r="89" spans="1:8" ht="1.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="244"/>
-      <c r="B89" s="244"/>
+      <c r="D88" s="251"/>
+      <c r="E88" s="253"/>
+    </row>
+    <row r="89" spans="1:8" ht="1.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="257"/>
+      <c r="B89" s="257"/>
       <c r="C89" s="31"/>
-      <c r="D89" s="241"/>
-      <c r="E89" s="243"/>
-    </row>
-    <row r="90" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D89" s="252"/>
+      <c r="E89" s="254"/>
+    </row>
+    <row r="90" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="29"/>
       <c r="B90" s="29"/>
       <c r="D90" s="42"/>
       <c r="E90" s="42"/>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" s="24"/>
       <c r="B91" s="61"/>
       <c r="C91" s="29"/>
       <c r="D91" s="35"/>
       <c r="E91" s="60"/>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="62" t="s">
         <v>145</v>
       </c>
@@ -3770,15 +3724,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D93" s="48"/>
       <c r="E93" s="48"/>
     </row>
-    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="D94" s="48"/>
       <c r="E94" s="48"/>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="44" t="s">
         <v>118</v>
       </c>
@@ -3789,11 +3743,11 @@
         <v>4500000</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D96" s="48"/>
       <c r="E96" s="48"/>
     </row>
-    <row r="97" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A97" s="51" t="s">
         <v>119</v>
       </c>
@@ -3805,11 +3759,11 @@
         <v>4500000</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D98" s="48"/>
       <c r="E98" s="48"/>
     </row>
-    <row r="99" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A99" s="64" t="s">
         <v>120</v>
       </c>
@@ -3820,7 +3774,7 @@
       <c r="D99" s="48"/>
       <c r="E99" s="48"/>
     </row>
-    <row r="100" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A100" s="64" t="s">
         <v>121</v>
       </c>
@@ -3831,7 +3785,7 @@
       <c r="D100" s="48"/>
       <c r="E100" s="48"/>
     </row>
-    <row r="101" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A101" s="64" t="s">
         <v>122</v>
       </c>
@@ -3842,7 +3796,7 @@
       <c r="D101" s="48"/>
       <c r="E101" s="48"/>
     </row>
-    <row r="102" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A102" s="64" t="s">
         <v>123</v>
       </c>
@@ -3853,217 +3807,217 @@
       <c r="D102" s="48"/>
       <c r="E102" s="48"/>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D103" s="48"/>
       <c r="E103" s="48"/>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D104" s="48"/>
       <c r="E104" s="48"/>
     </row>
-    <row r="105" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="227" t="s">
+    <row r="105" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="267" t="s">
         <v>172</v>
       </c>
-      <c r="B105" s="227"/>
+      <c r="B105" s="267"/>
       <c r="D105" s="48"/>
       <c r="E105" s="48"/>
     </row>
-    <row r="106" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="227"/>
-      <c r="B106" s="227"/>
+    <row r="106" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="267"/>
+      <c r="B106" s="267"/>
       <c r="D106" s="48"/>
       <c r="E106" s="48"/>
     </row>
-    <row r="107" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="227"/>
-      <c r="B107" s="227"/>
+    <row r="107" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="267"/>
+      <c r="B107" s="267"/>
       <c r="D107" s="48"/>
       <c r="E107" s="48"/>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D108" s="48"/>
       <c r="E108" s="48"/>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A109" s="227" t="s">
-        <v>265</v>
-      </c>
-      <c r="B109" s="227"/>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A109" s="267" t="s">
+        <v>252</v>
+      </c>
+      <c r="B109" s="267"/>
       <c r="D109" s="48"/>
       <c r="E109" s="48"/>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A110" s="227"/>
-      <c r="B110" s="227"/>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A110" s="267"/>
+      <c r="B110" s="267"/>
       <c r="D110" s="48"/>
       <c r="E110" s="48"/>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A111" s="227"/>
-      <c r="B111" s="227"/>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A111" s="267"/>
+      <c r="B111" s="267"/>
       <c r="D111" s="48"/>
       <c r="E111" s="48"/>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D112" s="48"/>
       <c r="E112" s="48"/>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A113" s="227" t="s">
-        <v>266</v>
-      </c>
-      <c r="B113" s="227"/>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A113" s="267" t="s">
+        <v>253</v>
+      </c>
+      <c r="B113" s="267"/>
       <c r="D113" s="48"/>
       <c r="E113" s="48"/>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A114" s="227"/>
-      <c r="B114" s="227"/>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A114" s="267"/>
+      <c r="B114" s="267"/>
       <c r="D114" s="48"/>
       <c r="E114" s="48"/>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A115" s="227"/>
-      <c r="B115" s="227"/>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A115" s="267"/>
+      <c r="B115" s="267"/>
       <c r="D115" s="48"/>
       <c r="E115" s="48"/>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D116" s="48"/>
       <c r="E116" s="48"/>
     </row>
-    <row r="117" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="227" t="s">
+    <row r="117" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="267" t="s">
         <v>198</v>
       </c>
-      <c r="B117" s="227"/>
+      <c r="B117" s="267"/>
       <c r="D117" s="48"/>
       <c r="E117" s="48"/>
     </row>
-    <row r="118" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="227"/>
-      <c r="B118" s="227"/>
+    <row r="118" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="267"/>
+      <c r="B118" s="267"/>
       <c r="D118" s="48"/>
       <c r="E118" s="48"/>
     </row>
-    <row r="119" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="227"/>
-      <c r="B119" s="227"/>
+    <row r="119" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="267"/>
+      <c r="B119" s="267"/>
       <c r="D119" s="48"/>
       <c r="E119" s="48"/>
     </row>
-    <row r="120" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D120" s="48"/>
       <c r="E120" s="48"/>
       <c r="F120" s="199"/>
     </row>
-    <row r="121" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="227" t="s">
+    <row r="121" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="267" t="s">
         <v>179</v>
       </c>
-      <c r="B121" s="227"/>
+      <c r="B121" s="267"/>
       <c r="D121" s="48"/>
       <c r="E121" s="48"/>
     </row>
-    <row r="122" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="227"/>
-      <c r="B122" s="227"/>
+    <row r="122" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="267"/>
+      <c r="B122" s="267"/>
       <c r="D122" s="48"/>
       <c r="E122" s="48"/>
     </row>
-    <row r="123" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="227"/>
-      <c r="B123" s="227"/>
+    <row r="123" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A123" s="267"/>
+      <c r="B123" s="267"/>
       <c r="D123" s="48"/>
       <c r="E123" s="48"/>
     </row>
-    <row r="124" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D124" s="48"/>
       <c r="E124" s="48"/>
     </row>
-    <row r="125" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="227" t="s">
+    <row r="125" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A125" s="267" t="s">
         <v>182</v>
       </c>
-      <c r="B125" s="227"/>
+      <c r="B125" s="267"/>
       <c r="D125" s="48"/>
       <c r="E125" s="48"/>
     </row>
-    <row r="126" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="227"/>
-      <c r="B126" s="227"/>
+    <row r="126" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A126" s="267"/>
+      <c r="B126" s="267"/>
       <c r="D126" s="48"/>
       <c r="E126" s="48"/>
     </row>
-    <row r="127" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="227"/>
-      <c r="B127" s="227"/>
+    <row r="127" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A127" s="267"/>
+      <c r="B127" s="267"/>
       <c r="D127" s="48"/>
       <c r="E127" s="48"/>
     </row>
-    <row r="128" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D128" s="48"/>
       <c r="E128" s="48"/>
     </row>
-    <row r="129" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="227" t="s">
+    <row r="129" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A129" s="267" t="s">
         <v>181</v>
       </c>
-      <c r="B129" s="227"/>
+      <c r="B129" s="267"/>
       <c r="D129" s="48"/>
       <c r="E129" s="48"/>
     </row>
-    <row r="130" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="227"/>
-      <c r="B130" s="227"/>
+    <row r="130" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A130" s="267"/>
+      <c r="B130" s="267"/>
       <c r="D130" s="48"/>
       <c r="E130" s="48"/>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A131" s="227"/>
-      <c r="B131" s="227"/>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A131" s="267"/>
+      <c r="B131" s="267"/>
       <c r="D131" s="48"/>
       <c r="E131" s="48"/>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D132" s="48"/>
       <c r="E132" s="48"/>
     </row>
-    <row r="133" spans="1:6" s="68" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:6" s="68" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A133"/>
       <c r="B133" s="66"/>
       <c r="C133" s="67"/>
       <c r="D133" s="156"/>
       <c r="E133" s="156"/>
     </row>
-    <row r="134" spans="1:6" s="68" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="295" t="s">
+    <row r="134" spans="1:6" s="68" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A134" s="208" t="s">
         <v>188</v>
       </c>
-      <c r="B134" s="296">
+      <c r="B134" s="209">
         <v>1157299.74</v>
       </c>
       <c r="C134" s="67"/>
       <c r="D134" s="157"/>
       <c r="E134" s="157"/>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A135" s="297" t="s">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A135" s="210" t="s">
         <v>144</v>
       </c>
-      <c r="B135" s="298">
+      <c r="B135" s="211">
         <f>-B100-B101</f>
         <v>-18862341.469999999</v>
       </c>
       <c r="D135" s="48"/>
       <c r="E135" s="48"/>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A136" s="297" t="s">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A136" s="210" t="s">
         <v>124</v>
       </c>
-      <c r="B136" s="299">
+      <c r="B136" s="212">
         <f>B159</f>
         <v>0</v>
       </c>
@@ -4071,11 +4025,11 @@
       <c r="E136" s="48"/>
       <c r="F136" s="66"/>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A137" s="297" t="s">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A137" s="210" t="s">
         <v>2</v>
       </c>
-      <c r="B137" s="300">
+      <c r="B137" s="213">
         <f>PRORRATEO!F119</f>
         <v>21426698.540000003</v>
       </c>
@@ -4083,66 +4037,66 @@
       <c r="E137" s="48"/>
       <c r="F137" s="66"/>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A138" s="297" t="s">
-        <v>241</v>
-      </c>
-      <c r="B138" s="301">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A138" s="210" t="s">
+        <v>228</v>
+      </c>
+      <c r="B138" s="214">
         <v>-155000</v>
       </c>
       <c r="D138" s="48"/>
       <c r="E138" s="48"/>
       <c r="F138" s="66"/>
     </row>
-    <row r="139" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="297" t="s">
-        <v>267</v>
-      </c>
-      <c r="B139" s="301">
+    <row r="139" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A139" s="210" t="s">
+        <v>254</v>
+      </c>
+      <c r="B139" s="214">
         <v>-155000</v>
       </c>
       <c r="D139" s="48"/>
       <c r="E139" s="48"/>
       <c r="F139" s="66"/>
     </row>
-    <row r="140" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="297" t="s">
-        <v>271</v>
-      </c>
-      <c r="B140" s="302">
+    <row r="140" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A140" s="210" t="s">
+        <v>258</v>
+      </c>
+      <c r="B140" s="215">
         <v>145000</v>
       </c>
       <c r="D140" s="48"/>
       <c r="E140" s="48"/>
       <c r="F140" s="66"/>
     </row>
-    <row r="141" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="297" t="s">
-        <v>278</v>
-      </c>
-      <c r="B141" s="302">
+    <row r="141" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A141" s="210" t="s">
+        <v>265</v>
+      </c>
+      <c r="B141" s="215">
         <v>145000</v>
       </c>
       <c r="D141" s="48"/>
       <c r="E141" s="48"/>
       <c r="F141" s="66"/>
     </row>
-    <row r="142" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="297" t="s">
-        <v>280</v>
-      </c>
-      <c r="B142" s="301">
+    <row r="142" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A142" s="210" t="s">
+        <v>267</v>
+      </c>
+      <c r="B142" s="214">
         <v>-1500000</v>
       </c>
       <c r="D142" s="48"/>
       <c r="E142" s="48"/>
       <c r="F142" s="66"/>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A143" s="297" t="s">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A143" s="210" t="s">
         <v>218</v>
       </c>
-      <c r="B143" s="303">
+      <c r="B143" s="216">
         <f>-12043-6808-18270</f>
         <v>-37121</v>
       </c>
@@ -4150,120 +4104,120 @@
       <c r="E143" s="48"/>
       <c r="F143" s="66"/>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A144" s="297" t="s">
-        <v>275</v>
-      </c>
-      <c r="B144" s="303">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A144" s="210" t="s">
+        <v>262</v>
+      </c>
+      <c r="B144" s="216">
         <v>-300000</v>
       </c>
       <c r="D144" s="48"/>
       <c r="E144" s="48"/>
       <c r="F144" s="66"/>
     </row>
-    <row r="145" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A145" s="304" t="s">
+    <row r="145" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A145" s="217" t="s">
         <v>217</v>
       </c>
-      <c r="B145" s="305">
+      <c r="B145" s="218">
         <v>-320000</v>
       </c>
       <c r="D145" s="48"/>
       <c r="E145" s="48"/>
       <c r="F145" s="66"/>
     </row>
-    <row r="146" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="293" t="s">
+    <row r="146" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A146" s="206" t="s">
         <v>160</v>
       </c>
-      <c r="B146" s="294">
+      <c r="B146" s="207">
         <f>SUM(B134:C145)</f>
         <v>1544535.8100000024</v>
       </c>
-      <c r="D146" s="313"/>
+      <c r="D146" s="226"/>
       <c r="E146" s="50"/>
       <c r="F146" s="50"/>
     </row>
-    <row r="147" spans="1:13" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:13" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D147" s="48"/>
     </row>
-    <row r="148" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="295" t="s">
-        <v>284</v>
-      </c>
-      <c r="B148" s="296">
+    <row r="148" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A148" s="208" t="s">
+        <v>271</v>
+      </c>
+      <c r="B148" s="209">
         <v>0</v>
       </c>
       <c r="D148" s="48"/>
     </row>
-    <row r="149" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="297" t="s">
-        <v>281</v>
-      </c>
-      <c r="B149" s="306">
+    <row r="149" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A149" s="210" t="s">
+        <v>268</v>
+      </c>
+      <c r="B149" s="219">
         <v>1500000</v>
       </c>
       <c r="D149" s="48"/>
     </row>
-    <row r="150" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="307" t="s">
-        <v>282</v>
-      </c>
-      <c r="B150" s="308">
+    <row r="150" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A150" s="220" t="s">
+        <v>269</v>
+      </c>
+      <c r="B150" s="221">
         <f>1506421.54-B149</f>
         <v>6421.5400000000373</v>
       </c>
       <c r="D150" s="48"/>
     </row>
-    <row r="151" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A151" s="293" t="s">
-        <v>283</v>
-      </c>
-      <c r="B151" s="294">
+    <row r="151" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A151" s="206" t="s">
+        <v>270</v>
+      </c>
+      <c r="B151" s="207">
         <f>SUM(B148:B150)</f>
         <v>1506421.54</v>
       </c>
       <c r="D151" s="48"/>
     </row>
-    <row r="152" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D152" s="48"/>
     </row>
-    <row r="153" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D153" s="48"/>
     </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A154" s="226" t="s">
+    <row r="154" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A154" s="266" t="s">
         <v>125</v>
       </c>
-      <c r="B154" s="226"/>
-      <c r="C154" s="226"/>
+      <c r="B154" s="266"/>
+      <c r="C154" s="266"/>
       <c r="D154" s="48"/>
     </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A155" s="226"/>
-      <c r="B155" s="226"/>
-      <c r="C155" s="226"/>
+    <row r="155" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A155" s="266"/>
+      <c r="B155" s="266"/>
+      <c r="C155" s="266"/>
       <c r="D155" s="48"/>
     </row>
-    <row r="156" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="69"/>
       <c r="B156" s="110"/>
       <c r="C156" s="70"/>
-      <c r="D156" s="314"/>
-    </row>
-    <row r="157" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D156" s="227"/>
+    </row>
+    <row r="157" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="69"/>
       <c r="B157" s="110"/>
       <c r="C157" s="70"/>
-      <c r="D157" s="314"/>
-    </row>
-    <row r="158" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D157" s="227"/>
+    </row>
+    <row r="158" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="69"/>
       <c r="B158" s="110"/>
       <c r="C158" s="70"/>
       <c r="D158" s="56"/>
     </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A159" s="71" t="s">
         <v>0</v>
       </c>
@@ -4273,20 +4227,19 @@
       </c>
       <c r="C159" s="73"/>
     </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:13" x14ac:dyDescent="0.3">
       <c r="M160" s="74"/>
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="A65:B65"/>
-    <mergeCell ref="D88:D89"/>
-    <mergeCell ref="E88:E89"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="A68:B68"/>
-    <mergeCell ref="A88:B89"/>
-    <mergeCell ref="A66:B66"/>
-    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="A154:C155"/>
+    <mergeCell ref="A117:B119"/>
+    <mergeCell ref="A129:B131"/>
+    <mergeCell ref="A125:B127"/>
+    <mergeCell ref="A105:B107"/>
+    <mergeCell ref="A121:B123"/>
+    <mergeCell ref="A109:B111"/>
+    <mergeCell ref="A113:B115"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A71:B71"/>
@@ -4303,14 +4256,15 @@
     <mergeCell ref="A57:B57"/>
     <mergeCell ref="A61:B61"/>
     <mergeCell ref="A63:B63"/>
-    <mergeCell ref="A154:C155"/>
-    <mergeCell ref="A117:B119"/>
-    <mergeCell ref="A129:B131"/>
-    <mergeCell ref="A125:B127"/>
-    <mergeCell ref="A105:B107"/>
-    <mergeCell ref="A121:B123"/>
-    <mergeCell ref="A109:B111"/>
-    <mergeCell ref="A113:B115"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="D88:D89"/>
+    <mergeCell ref="E88:E89"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="A88:B89"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="A72:B72"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" scale="90" orientation="portrait" r:id="rId1"/>
@@ -4321,55 +4275,55 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{533DB7A7-09F4-49CF-B824-70F15C1FF525}">
   <dimension ref="A1:Q135"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" customWidth="1"/>
-    <col min="2" max="2" width="25.5703125" customWidth="1"/>
-    <col min="3" max="3" width="0.140625" customWidth="1"/>
-    <col min="4" max="4" width="8.42578125" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.5703125" customWidth="1"/>
-    <col min="8" max="8" width="9.5703125" customWidth="1"/>
-    <col min="9" max="9" width="12.42578125" customWidth="1"/>
-    <col min="10" max="11" width="16.28515625" customWidth="1"/>
-    <col min="12" max="12" width="12.28515625" customWidth="1"/>
-    <col min="13" max="13" width="16.140625" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" customWidth="1"/>
-    <col min="16" max="16" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" customWidth="1"/>
+    <col min="2" max="2" width="25.5546875" customWidth="1"/>
+    <col min="3" max="3" width="0.109375" customWidth="1"/>
+    <col min="4" max="4" width="8.44140625" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" customWidth="1"/>
+    <col min="7" max="7" width="10.5546875" customWidth="1"/>
+    <col min="8" max="8" width="9.5546875" customWidth="1"/>
+    <col min="9" max="9" width="12.44140625" customWidth="1"/>
+    <col min="10" max="11" width="16.33203125" customWidth="1"/>
+    <col min="12" max="12" width="12.33203125" customWidth="1"/>
+    <col min="13" max="13" width="16.109375" customWidth="1"/>
+    <col min="14" max="14" width="14.6640625" customWidth="1"/>
+    <col min="15" max="15" width="14.33203125" customWidth="1"/>
+    <col min="16" max="16" width="7.33203125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="12" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="88"/>
       <c r="B1" s="89"/>
       <c r="C1" s="89"/>
-      <c r="D1" s="260"/>
-      <c r="E1" s="260"/>
-      <c r="F1" s="260"/>
-      <c r="G1" s="260"/>
-      <c r="H1" s="260"/>
-      <c r="I1" s="260"/>
-      <c r="J1" s="260"/>
-      <c r="K1" s="260"/>
-      <c r="L1" s="260"/>
-      <c r="M1" s="260"/>
-      <c r="N1" s="260"/>
+      <c r="D1" s="269"/>
+      <c r="E1" s="269"/>
+      <c r="F1" s="269"/>
+      <c r="G1" s="269"/>
+      <c r="H1" s="269"/>
+      <c r="I1" s="269"/>
+      <c r="J1" s="269"/>
+      <c r="K1" s="269"/>
+      <c r="L1" s="269"/>
+      <c r="M1" s="269"/>
+      <c r="N1" s="269"/>
       <c r="O1" s="90"/>
     </row>
-    <row r="2" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="91"/>
       <c r="B2" s="92"/>
       <c r="C2" s="93"/>
       <c r="D2" s="93" t="s">
         <v>126</v>
       </c>
-      <c r="E2" s="282">
+      <c r="E2" s="293">
         <v>4500000</v>
       </c>
-      <c r="F2" s="282"/>
+      <c r="F2" s="293"/>
       <c r="G2" s="93"/>
       <c r="H2" s="93"/>
       <c r="I2" s="93" t="s">
@@ -4393,7 +4347,7 @@
         <v>13312274.1</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="97"/>
       <c r="B3" s="98"/>
       <c r="C3" s="98"/>
@@ -4411,241 +4365,241 @@
       <c r="O3" s="101"/>
       <c r="P3" s="75"/>
     </row>
-    <row r="4" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="261" t="s">
+    <row r="4" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="270" t="s">
         <v>159</v>
       </c>
-      <c r="B4" s="262"/>
-      <c r="C4" s="262"/>
-      <c r="D4" s="262"/>
-      <c r="E4" s="262"/>
-      <c r="F4" s="262"/>
-      <c r="G4" s="262"/>
-      <c r="H4" s="262"/>
-      <c r="I4" s="262"/>
-      <c r="J4" s="262"/>
-      <c r="K4" s="262"/>
-      <c r="L4" s="262"/>
-      <c r="M4" s="262"/>
-      <c r="N4" s="262"/>
-      <c r="O4" s="263"/>
+      <c r="B4" s="271"/>
+      <c r="C4" s="271"/>
+      <c r="D4" s="271"/>
+      <c r="E4" s="271"/>
+      <c r="F4" s="271"/>
+      <c r="G4" s="271"/>
+      <c r="H4" s="271"/>
+      <c r="I4" s="271"/>
+      <c r="J4" s="271"/>
+      <c r="K4" s="271"/>
+      <c r="L4" s="271"/>
+      <c r="M4" s="271"/>
+      <c r="N4" s="271"/>
+      <c r="O4" s="272"/>
       <c r="P4" s="75"/>
     </row>
-    <row r="5" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="264"/>
-      <c r="B5" s="265"/>
-      <c r="C5" s="265"/>
-      <c r="D5" s="265"/>
-      <c r="E5" s="265"/>
-      <c r="F5" s="265"/>
-      <c r="G5" s="265"/>
-      <c r="H5" s="265"/>
-      <c r="I5" s="265"/>
-      <c r="J5" s="265"/>
-      <c r="K5" s="265"/>
-      <c r="L5" s="265"/>
-      <c r="M5" s="265"/>
-      <c r="N5" s="265"/>
-      <c r="O5" s="266"/>
+    <row r="5" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="273"/>
+      <c r="B5" s="274"/>
+      <c r="C5" s="274"/>
+      <c r="D5" s="274"/>
+      <c r="E5" s="274"/>
+      <c r="F5" s="274"/>
+      <c r="G5" s="274"/>
+      <c r="H5" s="274"/>
+      <c r="I5" s="274"/>
+      <c r="J5" s="274"/>
+      <c r="K5" s="274"/>
+      <c r="L5" s="274"/>
+      <c r="M5" s="274"/>
+      <c r="N5" s="274"/>
+      <c r="O5" s="275"/>
       <c r="P5" s="75"/>
     </row>
-    <row r="6" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="264"/>
-      <c r="B6" s="265"/>
-      <c r="C6" s="265"/>
-      <c r="D6" s="265"/>
-      <c r="E6" s="265"/>
-      <c r="F6" s="265"/>
-      <c r="G6" s="265"/>
-      <c r="H6" s="265"/>
-      <c r="I6" s="265"/>
-      <c r="J6" s="265"/>
-      <c r="K6" s="265"/>
-      <c r="L6" s="265"/>
-      <c r="M6" s="265"/>
-      <c r="N6" s="265"/>
-      <c r="O6" s="266"/>
+    <row r="6" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="273"/>
+      <c r="B6" s="274"/>
+      <c r="C6" s="274"/>
+      <c r="D6" s="274"/>
+      <c r="E6" s="274"/>
+      <c r="F6" s="274"/>
+      <c r="G6" s="274"/>
+      <c r="H6" s="274"/>
+      <c r="I6" s="274"/>
+      <c r="J6" s="274"/>
+      <c r="K6" s="274"/>
+      <c r="L6" s="274"/>
+      <c r="M6" s="274"/>
+      <c r="N6" s="274"/>
+      <c r="O6" s="275"/>
       <c r="P6" s="75"/>
     </row>
-    <row r="7" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="264"/>
-      <c r="B7" s="265"/>
-      <c r="C7" s="265"/>
-      <c r="D7" s="265"/>
-      <c r="E7" s="265"/>
-      <c r="F7" s="265"/>
-      <c r="G7" s="265"/>
-      <c r="H7" s="265"/>
-      <c r="I7" s="265"/>
-      <c r="J7" s="265"/>
-      <c r="K7" s="265"/>
-      <c r="L7" s="265"/>
-      <c r="M7" s="265"/>
-      <c r="N7" s="265"/>
-      <c r="O7" s="266"/>
+    <row r="7" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="273"/>
+      <c r="B7" s="274"/>
+      <c r="C7" s="274"/>
+      <c r="D7" s="274"/>
+      <c r="E7" s="274"/>
+      <c r="F7" s="274"/>
+      <c r="G7" s="274"/>
+      <c r="H7" s="274"/>
+      <c r="I7" s="274"/>
+      <c r="J7" s="274"/>
+      <c r="K7" s="274"/>
+      <c r="L7" s="274"/>
+      <c r="M7" s="274"/>
+      <c r="N7" s="274"/>
+      <c r="O7" s="275"/>
       <c r="P7" s="75"/>
     </row>
-    <row r="8" spans="1:17" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="267"/>
-      <c r="B8" s="268"/>
-      <c r="C8" s="268"/>
-      <c r="D8" s="268"/>
-      <c r="E8" s="268"/>
-      <c r="F8" s="268"/>
-      <c r="G8" s="268"/>
-      <c r="H8" s="268"/>
-      <c r="I8" s="268"/>
-      <c r="J8" s="268"/>
-      <c r="K8" s="268"/>
-      <c r="L8" s="268"/>
-      <c r="M8" s="268"/>
-      <c r="N8" s="268"/>
-      <c r="O8" s="269"/>
-    </row>
-    <row r="9" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="276" t="s">
+    <row r="8" spans="1:17" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="276"/>
+      <c r="B8" s="277"/>
+      <c r="C8" s="277"/>
+      <c r="D8" s="277"/>
+      <c r="E8" s="277"/>
+      <c r="F8" s="277"/>
+      <c r="G8" s="277"/>
+      <c r="H8" s="277"/>
+      <c r="I8" s="277"/>
+      <c r="J8" s="277"/>
+      <c r="K8" s="277"/>
+      <c r="L8" s="277"/>
+      <c r="M8" s="277"/>
+      <c r="N8" s="277"/>
+      <c r="O8" s="278"/>
+    </row>
+    <row r="9" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="287" t="s">
         <v>157</v>
       </c>
-      <c r="B9" s="277"/>
-      <c r="C9" s="277"/>
-      <c r="D9" s="277"/>
-      <c r="E9" s="277"/>
-      <c r="F9" s="277"/>
-      <c r="G9" s="277"/>
-      <c r="H9" s="277"/>
-      <c r="I9" s="277"/>
-      <c r="J9" s="277"/>
-      <c r="K9" s="277"/>
-      <c r="L9" s="277"/>
-      <c r="M9" s="277"/>
-      <c r="N9" s="277"/>
-      <c r="O9" s="278"/>
-    </row>
-    <row r="10" spans="1:17" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="249" t="s">
+      <c r="B9" s="288"/>
+      <c r="C9" s="288"/>
+      <c r="D9" s="288"/>
+      <c r="E9" s="288"/>
+      <c r="F9" s="288"/>
+      <c r="G9" s="288"/>
+      <c r="H9" s="288"/>
+      <c r="I9" s="288"/>
+      <c r="J9" s="288"/>
+      <c r="K9" s="288"/>
+      <c r="L9" s="288"/>
+      <c r="M9" s="288"/>
+      <c r="N9" s="288"/>
+      <c r="O9" s="289"/>
+    </row>
+    <row r="10" spans="1:17" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="298" t="s">
         <v>211</v>
       </c>
-      <c r="B10" s="250"/>
-      <c r="C10" s="250"/>
-      <c r="D10" s="250"/>
-      <c r="E10" s="250"/>
-      <c r="F10" s="250"/>
-      <c r="G10" s="250"/>
-      <c r="H10" s="250"/>
-      <c r="I10" s="250"/>
-      <c r="J10" s="250"/>
-      <c r="K10" s="250"/>
-      <c r="L10" s="250"/>
-      <c r="M10" s="250"/>
-      <c r="N10" s="250"/>
-      <c r="O10" s="251"/>
-    </row>
-    <row r="11" spans="1:17" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="252" t="s">
+      <c r="B10" s="299"/>
+      <c r="C10" s="299"/>
+      <c r="D10" s="299"/>
+      <c r="E10" s="299"/>
+      <c r="F10" s="299"/>
+      <c r="G10" s="299"/>
+      <c r="H10" s="299"/>
+      <c r="I10" s="299"/>
+      <c r="J10" s="299"/>
+      <c r="K10" s="299"/>
+      <c r="L10" s="299"/>
+      <c r="M10" s="299"/>
+      <c r="N10" s="299"/>
+      <c r="O10" s="300"/>
+    </row>
+    <row r="11" spans="1:17" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="301" t="s">
         <v>212</v>
       </c>
-      <c r="B11" s="253"/>
-      <c r="C11" s="253"/>
-      <c r="D11" s="253"/>
-      <c r="E11" s="253"/>
-      <c r="F11" s="253"/>
-      <c r="G11" s="253"/>
-      <c r="H11" s="253"/>
-      <c r="I11" s="253"/>
-      <c r="J11" s="253"/>
-      <c r="K11" s="253"/>
-      <c r="L11" s="253"/>
-      <c r="M11" s="253"/>
-      <c r="N11" s="253"/>
-      <c r="O11" s="254"/>
-    </row>
-    <row r="12" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="279" t="s">
+      <c r="B11" s="302"/>
+      <c r="C11" s="302"/>
+      <c r="D11" s="302"/>
+      <c r="E11" s="302"/>
+      <c r="F11" s="302"/>
+      <c r="G11" s="302"/>
+      <c r="H11" s="302"/>
+      <c r="I11" s="302"/>
+      <c r="J11" s="302"/>
+      <c r="K11" s="302"/>
+      <c r="L11" s="302"/>
+      <c r="M11" s="302"/>
+      <c r="N11" s="302"/>
+      <c r="O11" s="303"/>
+    </row>
+    <row r="12" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="290" t="s">
         <v>158</v>
       </c>
-      <c r="B12" s="280"/>
-      <c r="C12" s="280"/>
-      <c r="D12" s="280"/>
-      <c r="E12" s="280"/>
-      <c r="F12" s="280"/>
-      <c r="G12" s="280"/>
-      <c r="H12" s="280"/>
-      <c r="I12" s="280"/>
-      <c r="J12" s="280"/>
-      <c r="K12" s="280"/>
-      <c r="L12" s="280"/>
-      <c r="M12" s="280"/>
-      <c r="N12" s="280"/>
-      <c r="O12" s="281"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="270" t="s">
+      <c r="B12" s="291"/>
+      <c r="C12" s="291"/>
+      <c r="D12" s="291"/>
+      <c r="E12" s="291"/>
+      <c r="F12" s="291"/>
+      <c r="G12" s="291"/>
+      <c r="H12" s="291"/>
+      <c r="I12" s="291"/>
+      <c r="J12" s="291"/>
+      <c r="K12" s="291"/>
+      <c r="L12" s="291"/>
+      <c r="M12" s="291"/>
+      <c r="N12" s="291"/>
+      <c r="O12" s="292"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A13" s="279" t="s">
         <v>128</v>
       </c>
-      <c r="B13" s="272" t="s">
+      <c r="B13" s="281" t="s">
         <v>129</v>
       </c>
-      <c r="C13" s="272" t="s">
+      <c r="C13" s="281" t="s">
         <v>130</v>
       </c>
-      <c r="D13" s="272" t="s">
+      <c r="D13" s="281" t="s">
         <v>131</v>
       </c>
-      <c r="E13" s="247" t="s">
+      <c r="E13" s="283" t="s">
         <v>132</v>
       </c>
-      <c r="F13" s="272" t="s">
+      <c r="F13" s="281" t="s">
         <v>133</v>
       </c>
-      <c r="G13" s="274" t="s">
+      <c r="G13" s="285" t="s">
         <v>134</v>
       </c>
-      <c r="H13" s="247" t="s">
+      <c r="H13" s="283" t="s">
         <v>135</v>
       </c>
-      <c r="I13" s="247" t="s">
+      <c r="I13" s="283" t="s">
         <v>127</v>
       </c>
-      <c r="J13" s="247" t="s">
+      <c r="J13" s="283" t="s">
         <v>126</v>
       </c>
-      <c r="K13" s="257" t="s">
+      <c r="K13" s="306" t="s">
         <v>219</v>
       </c>
-      <c r="L13" s="283" t="s">
+      <c r="L13" s="294" t="s">
         <v>174</v>
       </c>
-      <c r="M13" s="245" t="s">
+      <c r="M13" s="296" t="s">
         <v>180</v>
       </c>
       <c r="N13" s="138" t="s">
         <v>207</v>
       </c>
-      <c r="O13" s="255" t="s">
+      <c r="O13" s="304" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="271"/>
-      <c r="B14" s="273"/>
-      <c r="C14" s="273"/>
-      <c r="D14" s="273"/>
-      <c r="E14" s="248"/>
-      <c r="F14" s="273"/>
-      <c r="G14" s="275"/>
-      <c r="H14" s="248"/>
-      <c r="I14" s="248"/>
-      <c r="J14" s="248"/>
-      <c r="K14" s="258"/>
-      <c r="L14" s="284"/>
-      <c r="M14" s="246"/>
+    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="280"/>
+      <c r="B14" s="282"/>
+      <c r="C14" s="282"/>
+      <c r="D14" s="282"/>
+      <c r="E14" s="284"/>
+      <c r="F14" s="282"/>
+      <c r="G14" s="286"/>
+      <c r="H14" s="284"/>
+      <c r="I14" s="284"/>
+      <c r="J14" s="284"/>
+      <c r="K14" s="307"/>
+      <c r="L14" s="295"/>
+      <c r="M14" s="297"/>
       <c r="N14" s="139" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 17/09</v>
       </c>
-      <c r="O14" s="256"/>
-    </row>
-    <row r="15" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O14" s="305"/>
+    </row>
+    <row r="15" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="124">
         <v>1</v>
       </c>
@@ -4697,7 +4651,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="179">
         <v>2</v>
       </c>
@@ -4750,11 +4704,11 @@
         <v>166</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="124">
+    <row r="17" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="240">
         <v>3</v>
       </c>
-      <c r="B17" s="76" t="s">
+      <c r="B17" s="241" t="s">
         <v>5</v>
       </c>
       <c r="C17" s="82"/>
@@ -4803,7 +4757,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="125">
         <v>4</v>
       </c>
@@ -4856,7 +4810,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="124">
         <v>5</v>
       </c>
@@ -4908,11 +4862,11 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="124">
+    <row r="20" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="247">
         <v>6</v>
       </c>
-      <c r="B20" s="76" t="s">
+      <c r="B20" s="248" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="76"/>
@@ -4960,7 +4914,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="124">
         <v>7</v>
       </c>
@@ -5013,7 +4967,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="124">
         <v>8</v>
       </c>
@@ -5066,7 +5020,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="124">
         <v>9</v>
       </c>
@@ -5118,7 +5072,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="124">
         <v>10</v>
       </c>
@@ -5171,7 +5125,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="124">
         <v>11</v>
       </c>
@@ -5224,7 +5178,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="179">
         <v>12</v>
       </c>
@@ -5276,7 +5230,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="124">
         <v>13</v>
       </c>
@@ -5329,7 +5283,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="124">
         <v>14</v>
       </c>
@@ -5379,7 +5333,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="125">
         <v>15</v>
       </c>
@@ -5432,7 +5386,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="124">
         <v>16</v>
       </c>
@@ -5485,7 +5439,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="124">
         <v>17</v>
       </c>
@@ -5537,7 +5491,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="125">
         <v>18</v>
       </c>
@@ -5590,7 +5544,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="125">
         <v>19</v>
       </c>
@@ -5645,7 +5599,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="126">
         <v>20</v>
       </c>
@@ -5696,10 +5650,10 @@
         <v>0.20000000000000004</v>
       </c>
       <c r="Q34" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="125">
         <v>21</v>
       </c>
@@ -5752,7 +5706,7 @@
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" s="125">
         <f>A35+1</f>
         <v>22</v>
@@ -5806,7 +5760,7 @@
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="124">
         <f t="shared" ref="A37:A100" si="10">A36+1</f>
         <v>23</v>
@@ -5860,7 +5814,7 @@
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="124">
         <f t="shared" si="10"/>
         <v>24</v>
@@ -5913,7 +5867,7 @@
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="124">
         <f t="shared" si="10"/>
         <v>25</v>
@@ -5966,7 +5920,7 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="124">
         <f t="shared" si="10"/>
         <v>26</v>
@@ -6020,12 +5974,12 @@
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A41" s="124">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A41" s="231">
         <f t="shared" si="10"/>
         <v>27</v>
       </c>
-      <c r="B41" s="83" t="s">
+      <c r="B41" s="232" t="s">
         <v>28</v>
       </c>
       <c r="C41" s="82"/>
@@ -6074,7 +6028,7 @@
         <v>0.27000000000000007</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="124">
         <f t="shared" si="10"/>
         <v>28</v>
@@ -6127,10 +6081,10 @@
         <v>0.28000000000000008</v>
       </c>
       <c r="Q42" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" s="125">
         <f t="shared" si="10"/>
         <v>29</v>
@@ -6187,7 +6141,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" s="125">
         <f t="shared" si="10"/>
         <v>30</v>
@@ -6241,7 +6195,7 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" s="124">
         <f t="shared" si="10"/>
         <v>31</v>
@@ -6295,7 +6249,7 @@
         <v>0.31000000000000011</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" s="124">
         <f t="shared" si="10"/>
         <v>32</v>
@@ -6349,7 +6303,7 @@
         <v>0.32000000000000012</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="126">
         <f t="shared" si="10"/>
         <v>33</v>
@@ -6402,10 +6356,10 @@
         <v>0.33000000000000013</v>
       </c>
       <c r="Q47" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" s="124">
         <f t="shared" si="10"/>
         <v>34</v>
@@ -6459,7 +6413,7 @@
         <v>0.34000000000000014</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" s="182">
         <f t="shared" si="10"/>
         <v>35</v>
@@ -6516,7 +6470,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" s="124">
         <f t="shared" si="10"/>
         <v>36</v>
@@ -6573,7 +6527,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" s="124">
         <f t="shared" si="10"/>
         <v>37</v>
@@ -6629,7 +6583,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" s="126">
         <f t="shared" si="10"/>
         <v>38</v>
@@ -6683,10 +6637,10 @@
         <v>0.38000000000000017</v>
       </c>
       <c r="Q52" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" s="124">
         <f t="shared" si="10"/>
         <v>39</v>
@@ -6739,7 +6693,7 @@
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" s="124">
         <f t="shared" si="10"/>
         <v>40</v>
@@ -6793,7 +6747,7 @@
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" s="124">
         <f t="shared" si="10"/>
         <v>41</v>
@@ -6847,7 +6801,7 @@
         <v>0.4100000000000002</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" s="126">
         <f t="shared" si="10"/>
         <v>42</v>
@@ -6902,10 +6856,10 @@
         <v>0.42000000000000021</v>
       </c>
       <c r="Q56" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" s="125">
         <f t="shared" si="10"/>
         <v>43</v>
@@ -6917,7 +6871,7 @@
       <c r="D57" s="105">
         <v>0.82</v>
       </c>
-      <c r="E57" s="292">
+      <c r="E57" s="205">
         <v>790470.43</v>
       </c>
       <c r="F57" s="79">
@@ -6961,10 +6915,10 @@
         <v>0.43000000000000022</v>
       </c>
       <c r="Q57" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" s="125">
         <f t="shared" si="10"/>
         <v>44</v>
@@ -7021,7 +6975,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" s="125">
         <f t="shared" si="10"/>
         <v>45</v>
@@ -7075,12 +7029,12 @@
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A60" s="125">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A60" s="314">
         <f t="shared" si="10"/>
         <v>46</v>
       </c>
-      <c r="B60" s="109" t="s">
+      <c r="B60" s="315" t="s">
         <v>45</v>
       </c>
       <c r="C60" s="108"/>
@@ -7131,7 +7085,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" s="126">
         <f t="shared" si="10"/>
         <v>47</v>
@@ -7186,7 +7140,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" s="125">
         <f t="shared" si="10"/>
         <v>48</v>
@@ -7243,7 +7197,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" s="125">
         <f t="shared" si="10"/>
         <v>49</v>
@@ -7297,7 +7251,7 @@
         <v>0.49000000000000027</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" s="125">
         <f t="shared" si="10"/>
         <v>50</v>
@@ -7351,7 +7305,7 @@
         <v>0.50000000000000022</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" s="125">
         <f t="shared" si="10"/>
         <v>51</v>
@@ -7405,7 +7359,7 @@
         <v>0.51000000000000023</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" s="125">
         <f t="shared" si="10"/>
         <v>52</v>
@@ -7459,7 +7413,7 @@
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" s="125">
         <f t="shared" si="10"/>
         <v>53</v>
@@ -7513,7 +7467,7 @@
         <v>0.53000000000000025</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" s="125">
         <f t="shared" si="10"/>
         <v>54</v>
@@ -7567,7 +7521,7 @@
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" s="125">
         <f t="shared" si="10"/>
         <v>55</v>
@@ -7621,7 +7575,7 @@
         <v>0.55000000000000027</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" s="125">
         <f t="shared" si="10"/>
         <v>56</v>
@@ -7674,7 +7628,7 @@
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" s="125">
         <f t="shared" si="10"/>
         <v>57</v>
@@ -7731,7 +7685,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" s="125">
         <f t="shared" si="10"/>
         <v>58</v>
@@ -7788,7 +7742,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" s="125">
         <f t="shared" si="10"/>
         <v>59</v>
@@ -7841,7 +7795,7 @@
         <v>0.5900000000000003</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" s="125">
         <f t="shared" si="10"/>
         <v>60</v>
@@ -7894,7 +7848,7 @@
         <v>0.60000000000000031</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" s="125">
         <f t="shared" si="10"/>
         <v>61</v>
@@ -7948,7 +7902,7 @@
         <v>0.61000000000000032</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" s="125">
         <f t="shared" si="10"/>
         <v>62</v>
@@ -8002,7 +7956,7 @@
         <v>0.62000000000000033</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" s="125">
         <f t="shared" si="10"/>
         <v>63</v>
@@ -8059,7 +8013,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" s="125">
         <f t="shared" si="10"/>
         <v>64</v>
@@ -8112,7 +8066,7 @@
         <v>0.64000000000000035</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" s="125">
         <f t="shared" si="10"/>
         <v>65</v>
@@ -8169,7 +8123,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" s="125">
         <f t="shared" si="10"/>
         <v>66</v>
@@ -8222,7 +8176,7 @@
         <v>0.66000000000000036</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" s="125">
         <f t="shared" si="10"/>
         <v>67</v>
@@ -8275,7 +8229,7 @@
         <v>0.67000000000000037</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" s="179">
         <f t="shared" si="10"/>
         <v>68</v>
@@ -8330,12 +8284,12 @@
         <v>0.68000000000000038</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A83" s="125">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A83" s="229">
         <f t="shared" si="10"/>
         <v>69</v>
       </c>
-      <c r="B83" s="109" t="s">
+      <c r="B83" s="230" t="s">
         <v>68</v>
       </c>
       <c r="C83" s="82"/>
@@ -8385,7 +8339,7 @@
         <v>0.69000000000000039</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84" s="125">
         <f t="shared" si="10"/>
         <v>70</v>
@@ -8441,7 +8395,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" s="125">
         <f t="shared" si="10"/>
         <v>71</v>
@@ -8495,7 +8449,7 @@
         <v>0.71000000000000041</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" s="125">
         <f t="shared" si="10"/>
         <v>72</v>
@@ -8549,7 +8503,7 @@
         <v>0.72000000000000042</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" s="125">
         <f t="shared" si="10"/>
         <v>73</v>
@@ -8603,7 +8557,7 @@
         <v>0.73000000000000043</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88" s="126">
         <f t="shared" si="10"/>
         <v>74</v>
@@ -8657,10 +8611,10 @@
         <v>0.74000000000000044</v>
       </c>
       <c r="Q88" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" s="124">
         <f t="shared" si="10"/>
         <v>75</v>
@@ -8713,7 +8667,7 @@
         <v>0.75000000000000044</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" s="125">
         <f t="shared" si="10"/>
         <v>76</v>
@@ -8767,7 +8721,7 @@
         <v>0.76000000000000045</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" s="124">
         <f t="shared" si="10"/>
         <v>77</v>
@@ -8821,7 +8775,7 @@
         <v>0.77000000000000046</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A92" s="126">
         <f t="shared" si="10"/>
         <v>78</v>
@@ -8874,10 +8828,10 @@
         <v>0.78000000000000047</v>
       </c>
       <c r="Q92" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93" s="124">
         <f t="shared" si="10"/>
         <v>79</v>
@@ -8933,7 +8887,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94" s="125">
         <f t="shared" si="10"/>
         <v>80</v>
@@ -8987,7 +8941,7 @@
         <v>0.80000000000000049</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A95" s="125">
         <f t="shared" si="10"/>
         <v>81</v>
@@ -9044,7 +8998,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A96" s="125">
         <f t="shared" si="10"/>
         <v>82</v>
@@ -9097,7 +9051,7 @@
         <v>0.82000000000000051</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A97" s="125">
         <f t="shared" si="10"/>
         <v>83</v>
@@ -9113,7 +9067,7 @@
         <v>283500.83</v>
       </c>
       <c r="F97" s="79">
-        <f>E97</f>
+        <f t="shared" ref="F97:F104" si="23">E97</f>
         <v>283500.83</v>
       </c>
       <c r="G97" s="80">
@@ -9151,7 +9105,7 @@
         <v>0.83000000000000052</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A98" s="125">
         <f t="shared" si="10"/>
         <v>84</v>
@@ -9167,7 +9121,7 @@
         <v>178463.84</v>
       </c>
       <c r="F98" s="79">
-        <f>E98</f>
+        <f t="shared" si="23"/>
         <v>178463.84</v>
       </c>
       <c r="G98" s="80">
@@ -9201,11 +9155,11 @@
         <v>253792.84</v>
       </c>
       <c r="P98" s="50">
-        <f t="shared" ref="P98:P117" si="23">P97+0.01</f>
+        <f t="shared" ref="P98:P117" si="24">P97+0.01</f>
         <v>0.84000000000000052</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A99" s="124">
         <f t="shared" si="10"/>
         <v>85</v>
@@ -9221,7 +9175,7 @@
         <v>172200.85</v>
       </c>
       <c r="F99" s="79">
-        <f>E99</f>
+        <f t="shared" si="23"/>
         <v>172200.85</v>
       </c>
       <c r="G99" s="80">
@@ -9255,11 +9209,11 @@
         <v>185812.85</v>
       </c>
       <c r="P99" s="50">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.85000000000000053</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A100" s="125">
         <f t="shared" si="10"/>
         <v>86</v>
@@ -9275,7 +9229,7 @@
         <v>167772.86</v>
       </c>
       <c r="F100" s="79">
-        <f>E100</f>
+        <f t="shared" si="23"/>
         <v>167772.86</v>
       </c>
       <c r="G100" s="106">
@@ -9305,17 +9259,17 @@
         <v>180400.86</v>
       </c>
       <c r="O100" s="135">
-        <f t="shared" ref="O100:O117" si="24">ROUND(N100*3%,0) + N100</f>
+        <f t="shared" ref="O100:O117" si="25">ROUND(N100*3%,0) + N100</f>
         <v>185812.86</v>
       </c>
       <c r="P100" s="50">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.86000000000000054</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A101" s="124">
-        <f t="shared" ref="A101:A117" si="25">A100+1</f>
+        <f t="shared" ref="A101:A117" si="26">A100+1</f>
         <v>87</v>
       </c>
       <c r="B101" s="83" t="s">
@@ -9329,7 +9283,7 @@
         <v>281400.87</v>
       </c>
       <c r="F101" s="79">
-        <f>E101</f>
+        <f t="shared" si="23"/>
         <v>281400.87</v>
       </c>
       <c r="G101" s="80">
@@ -9359,17 +9313,17 @@
         <v>294800.87</v>
       </c>
       <c r="O101" s="134">
+        <f t="shared" si="25"/>
+        <v>303644.87</v>
+      </c>
+      <c r="P101" s="50">
         <f t="shared" si="24"/>
-        <v>303644.87</v>
-      </c>
-      <c r="P101" s="50">
-        <f t="shared" si="23"/>
         <v>0.87000000000000055</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A102" s="124">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>88</v>
       </c>
       <c r="B102" s="83" t="s">
@@ -9383,7 +9337,7 @@
         <v>235200.88</v>
       </c>
       <c r="F102" s="79">
-        <f>E102</f>
+        <f t="shared" si="23"/>
         <v>235200.88</v>
       </c>
       <c r="G102" s="80">
@@ -9413,17 +9367,17 @@
         <v>246400.88</v>
       </c>
       <c r="O102" s="134">
+        <f t="shared" si="25"/>
+        <v>253792.88</v>
+      </c>
+      <c r="P102" s="50">
         <f t="shared" si="24"/>
-        <v>253792.88</v>
-      </c>
-      <c r="P102" s="50">
-        <f t="shared" si="23"/>
         <v>0.88000000000000056</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A103" s="124">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>89</v>
       </c>
       <c r="B103" s="83" t="s">
@@ -9437,7 +9391,7 @@
         <v>245700.89</v>
       </c>
       <c r="F103" s="79">
-        <f>E103</f>
+        <f t="shared" si="23"/>
         <v>245700.89</v>
       </c>
       <c r="G103" s="80">
@@ -9467,17 +9421,17 @@
         <v>257400.89</v>
       </c>
       <c r="O103" s="134">
+        <f t="shared" si="25"/>
+        <v>265122.89</v>
+      </c>
+      <c r="P103" s="50">
         <f t="shared" si="24"/>
-        <v>265122.89</v>
-      </c>
-      <c r="P103" s="50">
-        <f t="shared" si="23"/>
         <v>0.89000000000000057</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A104" s="124">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>90</v>
       </c>
       <c r="B104" s="83" t="s">
@@ -9491,7 +9445,7 @@
         <v>21000.9</v>
       </c>
       <c r="F104" s="79">
-        <f>E104</f>
+        <f t="shared" si="23"/>
         <v>21000.9</v>
       </c>
       <c r="G104" s="80">
@@ -9521,17 +9475,17 @@
         <v>22000.9</v>
       </c>
       <c r="O104" s="134">
+        <f t="shared" si="25"/>
+        <v>22660.9</v>
+      </c>
+      <c r="P104" s="50">
         <f t="shared" si="24"/>
-        <v>22660.9</v>
-      </c>
-      <c r="P104" s="50">
-        <f t="shared" si="23"/>
         <v>0.90000000000000058</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A105" s="124">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>91</v>
       </c>
       <c r="B105" s="83" t="s">
@@ -9574,17 +9528,17 @@
         <v>23591.91</v>
       </c>
       <c r="O105" s="134">
+        <f t="shared" si="25"/>
+        <v>24299.91</v>
+      </c>
+      <c r="P105" s="50">
         <f t="shared" si="24"/>
-        <v>24299.91</v>
-      </c>
-      <c r="P105" s="50">
-        <f t="shared" si="23"/>
         <v>0.91000000000000059</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A106" s="124">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>92</v>
       </c>
       <c r="B106" s="83" t="s">
@@ -9627,17 +9581,17 @@
         <v>21394.92</v>
       </c>
       <c r="O106" s="134">
+        <f t="shared" si="25"/>
+        <v>22036.92</v>
+      </c>
+      <c r="P106" s="50">
         <f t="shared" si="24"/>
-        <v>22036.92</v>
-      </c>
-      <c r="P106" s="50">
-        <f t="shared" si="23"/>
         <v>0.9200000000000006</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A107" s="125">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>93</v>
       </c>
       <c r="B107" s="109" t="s">
@@ -9681,17 +9635,17 @@
         <v>22000.93</v>
       </c>
       <c r="O107" s="135">
+        <f t="shared" si="25"/>
+        <v>22660.93</v>
+      </c>
+      <c r="P107" s="50">
         <f t="shared" si="24"/>
-        <v>22660.93</v>
-      </c>
-      <c r="P107" s="50">
-        <f t="shared" si="23"/>
         <v>0.9300000000000006</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A108" s="125">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>94</v>
       </c>
       <c r="B108" s="109" t="s">
@@ -9705,7 +9659,7 @@
         <v>21000.94</v>
       </c>
       <c r="F108" s="79">
-        <f t="shared" ref="F108:F113" si="26">E108</f>
+        <f t="shared" ref="F108:F113" si="27">E108</f>
         <v>21000.94</v>
       </c>
       <c r="G108" s="106">
@@ -9735,17 +9689,17 @@
         <v>22000.94</v>
       </c>
       <c r="O108" s="135">
+        <f t="shared" si="25"/>
+        <v>22660.94</v>
+      </c>
+      <c r="P108" s="50">
         <f t="shared" si="24"/>
-        <v>22660.94</v>
-      </c>
-      <c r="P108" s="50">
-        <f t="shared" si="23"/>
         <v>0.94000000000000061</v>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="125">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>95</v>
       </c>
       <c r="B109" s="109" t="s">
@@ -9759,7 +9713,7 @@
         <v>21000.95</v>
       </c>
       <c r="F109" s="79">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>21000.95</v>
       </c>
       <c r="G109" s="106">
@@ -9789,17 +9743,17 @@
         <v>22000.95</v>
       </c>
       <c r="O109" s="135">
+        <f t="shared" si="25"/>
+        <v>22660.95</v>
+      </c>
+      <c r="P109" s="50">
         <f t="shared" si="24"/>
-        <v>22660.95</v>
-      </c>
-      <c r="P109" s="50">
-        <f t="shared" si="23"/>
         <v>0.95000000000000062</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A110" s="125">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>96</v>
       </c>
       <c r="B110" s="109" t="s">
@@ -9843,20 +9797,20 @@
         <v>22000.959999999999</v>
       </c>
       <c r="O110" s="135">
+        <f t="shared" si="25"/>
+        <v>22660.959999999999</v>
+      </c>
+      <c r="P110" s="50">
         <f t="shared" si="24"/>
-        <v>22660.959999999999</v>
-      </c>
-      <c r="P110" s="50">
-        <f t="shared" si="23"/>
         <v>0.96000000000000063</v>
       </c>
       <c r="Q110" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A111" s="125">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>97</v>
       </c>
       <c r="B111" s="109" t="s">
@@ -9870,7 +9824,7 @@
         <v>21000.97</v>
       </c>
       <c r="F111" s="79">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>21000.97</v>
       </c>
       <c r="G111" s="106">
@@ -9882,11 +9836,11 @@
         <v>0</v>
       </c>
       <c r="I111" s="121">
-        <f t="shared" ref="I111:I117" si="27">J$2*D111/100</f>
+        <f t="shared" ref="I111:I117" si="28">J$2*D111/100</f>
         <v>11694.747559999998</v>
       </c>
       <c r="J111" s="121">
-        <f t="shared" ref="J111:J117" si="28">E$2*D111/100</f>
+        <f t="shared" ref="J111:J117" si="29">E$2*D111/100</f>
         <v>4500</v>
       </c>
       <c r="K111" s="120">
@@ -9900,17 +9854,17 @@
         <v>22000.97</v>
       </c>
       <c r="O111" s="135">
+        <f t="shared" si="25"/>
+        <v>22660.97</v>
+      </c>
+      <c r="P111" s="50">
         <f t="shared" si="24"/>
-        <v>22660.97</v>
-      </c>
-      <c r="P111" s="50">
-        <f t="shared" si="23"/>
         <v>0.97000000000000064</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A112" s="125">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>98</v>
       </c>
       <c r="B112" s="109" t="s">
@@ -9936,11 +9890,11 @@
         <v>0</v>
       </c>
       <c r="I112" s="121">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>11694.747559999998</v>
       </c>
       <c r="J112" s="121">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>4500</v>
       </c>
       <c r="K112" s="120">
@@ -9954,17 +9908,17 @@
         <v>22000.98</v>
       </c>
       <c r="O112" s="135">
+        <f t="shared" si="25"/>
+        <v>22660.98</v>
+      </c>
+      <c r="P112" s="50">
         <f t="shared" si="24"/>
-        <v>22660.98</v>
-      </c>
-      <c r="P112" s="50">
-        <f t="shared" si="23"/>
         <v>0.98000000000000065</v>
       </c>
     </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A113" s="125">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>99</v>
       </c>
       <c r="B113" s="109" t="s">
@@ -9978,7 +9932,7 @@
         <v>21000.99</v>
       </c>
       <c r="F113" s="79">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>21000.99</v>
       </c>
       <c r="G113" s="106">
@@ -9990,11 +9944,11 @@
         <v>0</v>
       </c>
       <c r="I113" s="121">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>11694.747559999998</v>
       </c>
       <c r="J113" s="121">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>4500</v>
       </c>
       <c r="K113" s="120">
@@ -10008,17 +9962,17 @@
         <v>22000.99</v>
       </c>
       <c r="O113" s="135">
+        <f t="shared" si="25"/>
+        <v>22660.99</v>
+      </c>
+      <c r="P113" s="50">
         <f t="shared" si="24"/>
-        <v>22660.99</v>
-      </c>
-      <c r="P113" s="50">
-        <f t="shared" si="23"/>
         <v>0.99000000000000066</v>
       </c>
     </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A114" s="125">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>100</v>
       </c>
       <c r="B114" s="109" t="s">
@@ -10044,11 +9998,11 @@
         <v>0</v>
       </c>
       <c r="I114" s="121">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>11694.747559999998</v>
       </c>
       <c r="J114" s="121">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>4500</v>
       </c>
       <c r="K114" s="120">
@@ -10062,17 +10016,17 @@
         <v>-4806</v>
       </c>
       <c r="O114" s="135">
+        <f t="shared" si="25"/>
+        <v>-4950</v>
+      </c>
+      <c r="P114" s="50">
         <f t="shared" si="24"/>
-        <v>-4950</v>
-      </c>
-      <c r="P114" s="50">
-        <f t="shared" si="23"/>
         <v>1.0000000000000007</v>
       </c>
     </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A115" s="125">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>101</v>
       </c>
       <c r="B115" s="103" t="s">
@@ -10098,11 +10052,11 @@
         <v>0</v>
       </c>
       <c r="I115" s="121">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>11694.747559999998</v>
       </c>
       <c r="J115" s="121">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>4500</v>
       </c>
       <c r="K115" s="120">
@@ -10116,17 +10070,17 @@
         <v>22001.01</v>
       </c>
       <c r="O115" s="135">
+        <f t="shared" si="25"/>
+        <v>22661.01</v>
+      </c>
+      <c r="P115" s="50">
         <f t="shared" si="24"/>
-        <v>22661.01</v>
-      </c>
-      <c r="P115" s="50">
-        <f t="shared" si="23"/>
         <v>1.0100000000000007</v>
       </c>
     </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A116" s="125">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>102</v>
       </c>
       <c r="B116" s="103" t="s">
@@ -10152,11 +10106,11 @@
         <v>0</v>
       </c>
       <c r="I116" s="121">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>11694.747559999998</v>
       </c>
       <c r="J116" s="121">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>4500</v>
       </c>
       <c r="K116" s="120">
@@ -10170,17 +10124,17 @@
         <v>22001.02</v>
       </c>
       <c r="O116" s="135">
+        <f t="shared" si="25"/>
+        <v>22661.02</v>
+      </c>
+      <c r="P116" s="50">
         <f t="shared" si="24"/>
-        <v>22661.02</v>
-      </c>
-      <c r="P116" s="50">
-        <f t="shared" si="23"/>
         <v>1.0200000000000007</v>
       </c>
     </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A117" s="125">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>103</v>
       </c>
       <c r="B117" s="109" t="s">
@@ -10206,11 +10160,11 @@
         <v>0</v>
       </c>
       <c r="I117" s="121">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>11694.747559999998</v>
       </c>
       <c r="J117" s="121">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>4500</v>
       </c>
       <c r="K117" s="120">
@@ -10224,15 +10178,15 @@
         <v>22001.03</v>
       </c>
       <c r="O117" s="135">
+        <f t="shared" si="25"/>
+        <v>22661.03</v>
+      </c>
+      <c r="P117" s="50">
         <f t="shared" si="24"/>
-        <v>22661.03</v>
-      </c>
-      <c r="P117" s="50">
-        <f t="shared" si="23"/>
         <v>1.0300000000000007</v>
       </c>
     </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A118" s="125"/>
       <c r="B118" s="103"/>
       <c r="C118" s="108"/>
@@ -10250,153 +10204,153 @@
       <c r="O118" s="135"/>
       <c r="P118" s="50"/>
     </row>
-    <row r="119" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A119" s="127"/>
       <c r="B119" s="128"/>
       <c r="C119" s="128"/>
       <c r="D119" s="129">
-        <f t="shared" ref="D119:O119" si="29">SUM(D15:D118)</f>
+        <f t="shared" ref="D119:O119" si="30">SUM(D15:D118)</f>
         <v>100.15999999999993</v>
       </c>
       <c r="E119" s="130">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>44844620.56000001</v>
       </c>
-      <c r="F119" s="315">
+      <c r="F119" s="228">
         <f>SUM(F15:F118)</f>
         <v>21426698.540000003</v>
       </c>
       <c r="G119" s="131">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>23417922.020000003</v>
       </c>
       <c r="H119" s="131">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>639868.71240000008</v>
       </c>
       <c r="I119" s="132">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>11713459.156095987</v>
       </c>
       <c r="J119" s="131">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>4507200</v>
       </c>
       <c r="K119" s="133"/>
       <c r="L119" s="133"/>
       <c r="M119" s="144"/>
       <c r="N119" s="140">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>47134342.559999995</v>
       </c>
       <c r="O119" s="137">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>48548373.560000002</v>
       </c>
     </row>
-    <row r="120" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B120" s="84"/>
       <c r="C120" s="84"/>
     </row>
-    <row r="121" spans="1:16" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="122" spans="1:16" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B122" s="259" t="s">
+    <row r="121" spans="1:16" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="122" spans="1:16" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B122" s="268" t="s">
         <v>103</v>
       </c>
-      <c r="C122" s="259"/>
-      <c r="D122" s="259"/>
-      <c r="E122" s="259"/>
-      <c r="F122" s="259"/>
-      <c r="G122" s="259"/>
-      <c r="H122" s="259"/>
-      <c r="I122" s="259"/>
-      <c r="J122" s="259"/>
-      <c r="K122" s="259"/>
-      <c r="L122" s="259"/>
-      <c r="M122" s="259"/>
-      <c r="N122" s="259"/>
-    </row>
-    <row r="123" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B123" s="259"/>
-      <c r="C123" s="259"/>
-      <c r="D123" s="259"/>
-      <c r="E123" s="259"/>
-      <c r="F123" s="259"/>
-      <c r="G123" s="259"/>
-      <c r="H123" s="259"/>
-      <c r="I123" s="259"/>
-      <c r="J123" s="259"/>
-      <c r="K123" s="259"/>
-      <c r="L123" s="259"/>
-      <c r="M123" s="259"/>
-      <c r="N123" s="259"/>
-    </row>
-    <row r="124" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B124" s="259"/>
-      <c r="C124" s="259"/>
-      <c r="D124" s="259"/>
-      <c r="E124" s="259"/>
-      <c r="F124" s="259"/>
-      <c r="G124" s="259"/>
-      <c r="H124" s="259"/>
-      <c r="I124" s="259"/>
-      <c r="J124" s="259"/>
-      <c r="K124" s="259"/>
-      <c r="L124" s="259"/>
-      <c r="M124" s="259"/>
-      <c r="N124" s="259"/>
-    </row>
-    <row r="125" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B125" s="259"/>
-      <c r="C125" s="259"/>
-      <c r="D125" s="259"/>
-      <c r="E125" s="259"/>
-      <c r="F125" s="259"/>
-      <c r="G125" s="259"/>
-      <c r="H125" s="259"/>
-      <c r="I125" s="259"/>
-      <c r="J125" s="259"/>
-      <c r="K125" s="259"/>
-      <c r="L125" s="259"/>
-      <c r="M125" s="259"/>
-      <c r="N125" s="259"/>
-    </row>
-    <row r="126" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B126" s="259"/>
-      <c r="C126" s="259"/>
-      <c r="D126" s="259"/>
-      <c r="E126" s="259"/>
-      <c r="F126" s="259"/>
-      <c r="G126" s="259"/>
-      <c r="H126" s="259"/>
-      <c r="I126" s="259"/>
-      <c r="J126" s="259"/>
-      <c r="K126" s="259"/>
-      <c r="L126" s="259"/>
-      <c r="M126" s="259"/>
-      <c r="N126" s="259"/>
-    </row>
-    <row r="127" spans="1:16" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B127" s="259"/>
-      <c r="C127" s="259"/>
-      <c r="D127" s="259"/>
-      <c r="E127" s="259"/>
-      <c r="F127" s="259"/>
-      <c r="G127" s="259"/>
-      <c r="H127" s="259"/>
-      <c r="I127" s="259"/>
-      <c r="J127" s="259"/>
-      <c r="K127" s="259"/>
-      <c r="L127" s="259"/>
-      <c r="M127" s="259"/>
-      <c r="N127" s="259"/>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C122" s="268"/>
+      <c r="D122" s="268"/>
+      <c r="E122" s="268"/>
+      <c r="F122" s="268"/>
+      <c r="G122" s="268"/>
+      <c r="H122" s="268"/>
+      <c r="I122" s="268"/>
+      <c r="J122" s="268"/>
+      <c r="K122" s="268"/>
+      <c r="L122" s="268"/>
+      <c r="M122" s="268"/>
+      <c r="N122" s="268"/>
+    </row>
+    <row r="123" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B123" s="268"/>
+      <c r="C123" s="268"/>
+      <c r="D123" s="268"/>
+      <c r="E123" s="268"/>
+      <c r="F123" s="268"/>
+      <c r="G123" s="268"/>
+      <c r="H123" s="268"/>
+      <c r="I123" s="268"/>
+      <c r="J123" s="268"/>
+      <c r="K123" s="268"/>
+      <c r="L123" s="268"/>
+      <c r="M123" s="268"/>
+      <c r="N123" s="268"/>
+    </row>
+    <row r="124" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B124" s="268"/>
+      <c r="C124" s="268"/>
+      <c r="D124" s="268"/>
+      <c r="E124" s="268"/>
+      <c r="F124" s="268"/>
+      <c r="G124" s="268"/>
+      <c r="H124" s="268"/>
+      <c r="I124" s="268"/>
+      <c r="J124" s="268"/>
+      <c r="K124" s="268"/>
+      <c r="L124" s="268"/>
+      <c r="M124" s="268"/>
+      <c r="N124" s="268"/>
+    </row>
+    <row r="125" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B125" s="268"/>
+      <c r="C125" s="268"/>
+      <c r="D125" s="268"/>
+      <c r="E125" s="268"/>
+      <c r="F125" s="268"/>
+      <c r="G125" s="268"/>
+      <c r="H125" s="268"/>
+      <c r="I125" s="268"/>
+      <c r="J125" s="268"/>
+      <c r="K125" s="268"/>
+      <c r="L125" s="268"/>
+      <c r="M125" s="268"/>
+      <c r="N125" s="268"/>
+    </row>
+    <row r="126" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B126" s="268"/>
+      <c r="C126" s="268"/>
+      <c r="D126" s="268"/>
+      <c r="E126" s="268"/>
+      <c r="F126" s="268"/>
+      <c r="G126" s="268"/>
+      <c r="H126" s="268"/>
+      <c r="I126" s="268"/>
+      <c r="J126" s="268"/>
+      <c r="K126" s="268"/>
+      <c r="L126" s="268"/>
+      <c r="M126" s="268"/>
+      <c r="N126" s="268"/>
+    </row>
+    <row r="127" spans="1:16" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B127" s="268"/>
+      <c r="C127" s="268"/>
+      <c r="D127" s="268"/>
+      <c r="E127" s="268"/>
+      <c r="F127" s="268"/>
+      <c r="G127" s="268"/>
+      <c r="H127" s="268"/>
+      <c r="I127" s="268"/>
+      <c r="J127" s="268"/>
+      <c r="K127" s="268"/>
+      <c r="L127" s="268"/>
+      <c r="M127" s="268"/>
+      <c r="N127" s="268"/>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B130">
         <v>1631378.049999997</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>218</v>
       </c>
@@ -10404,7 +10358,7 @@
         <v>-3942</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>217</v>
       </c>
@@ -10414,6 +10368,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="A10:O10"/>
+    <mergeCell ref="A11:O11"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="K13:K14"/>
     <mergeCell ref="B122:N127"/>
     <mergeCell ref="D1:N1"/>
     <mergeCell ref="A4:O8"/>
@@ -10430,12 +10390,6 @@
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="I13:I14"/>
     <mergeCell ref="L13:L14"/>
-    <mergeCell ref="M13:M14"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="A10:O10"/>
-    <mergeCell ref="A11:O11"/>
-    <mergeCell ref="O13:O14"/>
-    <mergeCell ref="K13:K14"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="70" orientation="landscape" r:id="rId1"/>
@@ -10444,17 +10398,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56D35F41-74CB-4294-A7A2-EC3C67574818}">
-  <dimension ref="C3:N65"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="C3:N51"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C3" s="19"/>
     </row>
-    <row r="4" spans="3:14" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:14" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="164" t="s">
         <v>189</v>
       </c>
@@ -10468,10 +10422,10 @@
       <c r="I4" s="161"/>
       <c r="J4" s="162"/>
       <c r="K4" s="19"/>
-      <c r="L4" s="224"/>
-      <c r="M4" s="224"/>
-    </row>
-    <row r="5" spans="3:14" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+    </row>
+    <row r="5" spans="3:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C5" s="166" t="s">
         <v>190</v>
       </c>
@@ -10484,11 +10438,11 @@
       </c>
       <c r="J5" s="163"/>
       <c r="K5" s="19"/>
-      <c r="L5" s="224"/>
-      <c r="M5" s="224"/>
+      <c r="L5" s="19"/>
+      <c r="M5" s="19"/>
       <c r="N5" s="19"/>
     </row>
-    <row r="6" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C6" s="166" t="s">
         <v>193</v>
       </c>
@@ -10506,57 +10460,85 @@
       </c>
       <c r="J6" s="163"/>
       <c r="K6" s="19"/>
-      <c r="L6" s="224"/>
-      <c r="M6" s="224"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19"/>
       <c r="N6" s="19"/>
     </row>
-    <row r="7" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C7" s="47" t="s">
         <v>196</v>
       </c>
       <c r="J7" s="163"/>
       <c r="K7" s="19"/>
-      <c r="L7" s="224"/>
-      <c r="M7" s="224"/>
+      <c r="L7" s="19"/>
+      <c r="M7" s="19"/>
       <c r="N7" s="19"/>
     </row>
-    <row r="8" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C8" s="285" t="s">
-        <v>222</v>
-      </c>
-      <c r="D8" s="286"/>
-      <c r="E8" s="286"/>
-      <c r="F8" s="286"/>
-      <c r="G8" s="286"/>
-      <c r="H8" s="286"/>
-      <c r="I8" s="286"/>
-      <c r="J8" s="287"/>
+    <row r="8" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C8" s="308" t="s">
+        <v>272</v>
+      </c>
+      <c r="D8" s="309"/>
+      <c r="E8" s="309"/>
+      <c r="F8" s="309"/>
+      <c r="G8" s="309"/>
+      <c r="H8" s="309"/>
+      <c r="I8" s="309"/>
+      <c r="J8" s="310"/>
       <c r="K8" s="19"/>
-      <c r="L8" s="224"/>
-      <c r="M8" s="224"/>
+      <c r="L8" s="19"/>
+      <c r="M8" s="19"/>
       <c r="N8" s="19"/>
     </row>
-    <row r="9" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="288"/>
-      <c r="D9" s="289"/>
-      <c r="E9" s="289"/>
-      <c r="F9" s="289"/>
-      <c r="G9" s="289"/>
-      <c r="H9" s="289"/>
-      <c r="I9" s="289"/>
-      <c r="J9" s="290"/>
+    <row r="9" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C9" s="311"/>
+      <c r="D9" s="312"/>
+      <c r="E9" s="312"/>
+      <c r="F9" s="312"/>
+      <c r="G9" s="312"/>
+      <c r="H9" s="312"/>
+      <c r="I9" s="312"/>
+      <c r="J9" s="313"/>
       <c r="K9" s="19"/>
       <c r="L9" s="19"/>
       <c r="M9" s="19"/>
       <c r="N9" s="19"/>
     </row>
-    <row r="11" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C12" s="202" t="s">
+    <row r="10" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C10" s="242"/>
+      <c r="D10" s="242"/>
+      <c r="E10" s="242"/>
+      <c r="F10" s="242"/>
+      <c r="G10" s="242"/>
+      <c r="H10" s="242"/>
+      <c r="I10" s="242"/>
+      <c r="J10" s="242"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="19"/>
+    </row>
+    <row r="11" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C11" s="242"/>
+      <c r="D11" s="242"/>
+      <c r="E11" s="242"/>
+      <c r="F11" s="242"/>
+      <c r="G11" s="242"/>
+      <c r="H11" s="242"/>
+      <c r="I11" s="242"/>
+      <c r="J11" s="242"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="19"/>
+    </row>
+    <row r="12" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C12" s="243" t="s">
         <v>189</v>
       </c>
-      <c r="D12" s="203">
-        <v>1</v>
+      <c r="D12" s="244">
+        <f>D4+1</f>
+        <v>2</v>
       </c>
       <c r="E12" s="161"/>
       <c r="F12" s="161"/>
@@ -10564,12 +10546,16 @@
       <c r="H12" s="161"/>
       <c r="I12" s="161"/>
       <c r="J12" s="162"/>
-    </row>
-    <row r="13" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C13" s="204" t="s">
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="19"/>
+    </row>
+    <row r="13" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C13" s="245" t="s">
         <v>190</v>
       </c>
-      <c r="D13" s="19"/>
+      <c r="D13" s="246"/>
       <c r="E13" t="s">
         <v>191</v>
       </c>
@@ -10577,13 +10563,16 @@
         <v>192</v>
       </c>
       <c r="J13" s="163"/>
-      <c r="L13" s="201"/>
-    </row>
-    <row r="14" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C14" s="204" t="s">
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
+      <c r="M13" s="19"/>
+      <c r="N13" s="19"/>
+    </row>
+    <row r="14" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C14" s="245" t="s">
         <v>193</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="246" t="s">
         <v>194</v>
       </c>
       <c r="E14" t="s">
@@ -10592,584 +10581,364 @@
       <c r="G14" t="s">
         <v>128</v>
       </c>
+      <c r="H14" t="s">
+        <v>278</v>
+      </c>
       <c r="J14" s="163"/>
-    </row>
-    <row r="15" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K14" s="19"/>
+      <c r="L14" s="19"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="19"/>
+    </row>
+    <row r="15" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C15" s="47" t="s">
         <v>196</v>
       </c>
       <c r="J15" s="163"/>
-    </row>
-    <row r="16" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C16" s="291" t="s">
-        <v>223</v>
-      </c>
-      <c r="D16" s="286"/>
-      <c r="E16" s="286"/>
-      <c r="F16" s="286"/>
-      <c r="G16" s="286"/>
-      <c r="H16" s="286"/>
-      <c r="I16" s="286"/>
-      <c r="J16" s="287"/>
-    </row>
-    <row r="17" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C17" s="288"/>
-      <c r="D17" s="289"/>
-      <c r="E17" s="289"/>
-      <c r="F17" s="289"/>
-      <c r="G17" s="289"/>
-      <c r="H17" s="289"/>
-      <c r="I17" s="289"/>
-      <c r="J17" s="290"/>
-    </row>
-    <row r="19" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C20" s="205" t="s">
+      <c r="K15" s="19"/>
+      <c r="L15" s="19"/>
+      <c r="M15" s="19"/>
+      <c r="N15" s="19"/>
+    </row>
+    <row r="16" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C16" s="308" t="s">
+        <v>277</v>
+      </c>
+      <c r="D16" s="309"/>
+      <c r="E16" s="309"/>
+      <c r="F16" s="309"/>
+      <c r="G16" s="309"/>
+      <c r="H16" s="309"/>
+      <c r="I16" s="309"/>
+      <c r="J16" s="310"/>
+      <c r="K16" s="19"/>
+      <c r="L16" s="19"/>
+      <c r="M16" s="19"/>
+      <c r="N16" s="19"/>
+    </row>
+    <row r="17" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C17" s="311"/>
+      <c r="D17" s="312"/>
+      <c r="E17" s="312"/>
+      <c r="F17" s="312"/>
+      <c r="G17" s="312"/>
+      <c r="H17" s="312"/>
+      <c r="I17" s="312"/>
+      <c r="J17" s="313"/>
+    </row>
+    <row r="21" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C22" s="201" t="s">
         <v>189</v>
       </c>
-      <c r="D20" s="206">
-        <v>1</v>
-      </c>
-      <c r="E20" s="161"/>
-      <c r="F20" s="161"/>
-      <c r="G20" s="161"/>
-      <c r="H20" s="161"/>
-      <c r="I20" s="161"/>
-      <c r="J20" s="162"/>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C21" s="207" t="s">
+      <c r="D22" s="202">
+        <f>D4+1</f>
+        <v>2</v>
+      </c>
+      <c r="E22" s="161"/>
+      <c r="F22" s="161"/>
+      <c r="G22" s="161"/>
+      <c r="H22" s="161"/>
+      <c r="I22" s="161"/>
+      <c r="J22" s="162"/>
+    </row>
+    <row r="23" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C23" s="203" t="s">
         <v>190</v>
       </c>
-      <c r="D21" s="208"/>
-      <c r="E21" t="s">
+      <c r="D23" s="204"/>
+      <c r="E23" t="s">
         <v>191</v>
       </c>
-      <c r="G21" t="s">
+      <c r="G23" t="s">
         <v>192</v>
       </c>
-      <c r="J21" s="163"/>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C22" s="207" t="s">
+      <c r="J23" s="163"/>
+    </row>
+    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C24" s="203" t="s">
         <v>193</v>
       </c>
-      <c r="D22" s="208" t="s">
+      <c r="D24" s="204" t="s">
         <v>194</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E24" t="s">
         <v>195</v>
       </c>
-      <c r="G22" t="s">
+      <c r="G24" t="s">
         <v>128</v>
       </c>
-      <c r="H22" t="s">
-        <v>224</v>
-      </c>
-      <c r="J22" s="163"/>
-      <c r="K22" s="224"/>
-      <c r="L22" s="224"/>
-      <c r="M22" s="224"/>
-    </row>
-    <row r="23" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C23" s="207" t="s">
+      <c r="H24" t="s">
+        <v>221</v>
+      </c>
+      <c r="J24" s="163"/>
+    </row>
+    <row r="25" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C25" s="47" t="s">
         <v>196</v>
       </c>
-      <c r="D23" s="208"/>
-      <c r="J23" s="163"/>
-      <c r="K23" s="224"/>
-      <c r="L23" s="224"/>
-      <c r="M23" s="224"/>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C24" s="285" t="s">
-        <v>228</v>
-      </c>
-      <c r="D24" s="286"/>
-      <c r="E24" s="286"/>
-      <c r="F24" s="286"/>
-      <c r="G24" s="286"/>
-      <c r="H24" s="286"/>
-      <c r="I24" s="286"/>
-      <c r="J24" s="287"/>
-      <c r="K24" s="224"/>
-      <c r="L24" s="224"/>
-      <c r="M24" s="224"/>
-    </row>
-    <row r="25" spans="3:14" ht="57.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C25" s="288"/>
-      <c r="D25" s="289"/>
-      <c r="E25" s="289"/>
-      <c r="F25" s="289"/>
-      <c r="G25" s="289"/>
-      <c r="H25" s="289"/>
-      <c r="I25" s="289"/>
-      <c r="J25" s="290"/>
-      <c r="K25" s="224"/>
-      <c r="L25" s="224"/>
-      <c r="M25" s="224"/>
-    </row>
-    <row r="27" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C28" s="209" t="s">
+      <c r="J25" s="163"/>
+    </row>
+    <row r="26" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C26" s="308" t="s">
+        <v>273</v>
+      </c>
+      <c r="D26" s="309"/>
+      <c r="E26" s="309"/>
+      <c r="F26" s="309"/>
+      <c r="G26" s="309"/>
+      <c r="H26" s="309"/>
+      <c r="I26" s="309"/>
+      <c r="J26" s="310"/>
+    </row>
+    <row r="27" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C27" s="311"/>
+      <c r="D27" s="312"/>
+      <c r="E27" s="312"/>
+      <c r="F27" s="312"/>
+      <c r="G27" s="312"/>
+      <c r="H27" s="312"/>
+      <c r="I27" s="312"/>
+      <c r="J27" s="313"/>
+    </row>
+    <row r="29" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="30" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C30" s="233" t="s">
         <v>189</v>
       </c>
-      <c r="D28" s="210">
-        <v>1</v>
-      </c>
-      <c r="E28" s="161"/>
-      <c r="F28" s="161"/>
-      <c r="G28" s="161"/>
-      <c r="H28" s="161"/>
-      <c r="I28" s="161"/>
-      <c r="J28" s="162"/>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C29" s="211" t="s">
+      <c r="D30" s="234">
+        <f>D22+1</f>
+        <v>3</v>
+      </c>
+      <c r="E30" s="161"/>
+      <c r="F30" s="161"/>
+      <c r="G30" s="161"/>
+      <c r="H30" s="161"/>
+      <c r="I30" s="161"/>
+      <c r="J30" s="162"/>
+    </row>
+    <row r="31" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C31" s="235" t="s">
         <v>190</v>
       </c>
-      <c r="D29" s="212"/>
-      <c r="E29" t="s">
+      <c r="D31" s="19"/>
+      <c r="E31" t="s">
         <v>191</v>
       </c>
-      <c r="G29" t="s">
+      <c r="G31" t="s">
         <v>192</v>
       </c>
-      <c r="J29" s="163"/>
-      <c r="K29" s="224"/>
-      <c r="L29" s="224"/>
-      <c r="M29" s="224"/>
-      <c r="N29" s="224"/>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C30" s="211" t="s">
+      <c r="J31" s="163"/>
+    </row>
+    <row r="32" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C32" s="235" t="s">
         <v>193</v>
       </c>
-      <c r="D30" s="212" t="s">
+      <c r="D32" s="19" t="s">
         <v>194</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E32" t="s">
         <v>195</v>
       </c>
-      <c r="G30" t="s">
+      <c r="G32" t="s">
         <v>128</v>
       </c>
-      <c r="H30" t="s">
-        <v>225</v>
-      </c>
-      <c r="J30" s="163"/>
-      <c r="K30" s="224"/>
-      <c r="L30" s="224"/>
-      <c r="M30" s="224"/>
-      <c r="N30" s="224"/>
-    </row>
-    <row r="31" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C31" s="211" t="s">
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="J32" s="163"/>
+    </row>
+    <row r="33" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C33" s="235" t="s">
         <v>196</v>
       </c>
-      <c r="D31" s="212"/>
-      <c r="J31" s="163"/>
-      <c r="K31" s="224"/>
-      <c r="L31" s="224"/>
-      <c r="M31" s="224"/>
-      <c r="N31" s="224"/>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C32" s="285" t="s">
-        <v>226</v>
-      </c>
-      <c r="D32" s="286"/>
-      <c r="E32" s="286"/>
-      <c r="F32" s="286"/>
-      <c r="G32" s="286"/>
-      <c r="H32" s="286"/>
-      <c r="I32" s="286"/>
-      <c r="J32" s="287"/>
-      <c r="K32" s="224"/>
-      <c r="L32" s="224"/>
-      <c r="M32" s="224"/>
-      <c r="N32" s="224"/>
-    </row>
-    <row r="33" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C33" s="288"/>
-      <c r="D33" s="289"/>
-      <c r="E33" s="289"/>
-      <c r="F33" s="289"/>
-      <c r="G33" s="289"/>
-      <c r="H33" s="289"/>
-      <c r="I33" s="289"/>
-      <c r="J33" s="290"/>
-      <c r="K33" s="224"/>
-      <c r="L33" s="224"/>
-      <c r="M33" s="224"/>
-      <c r="N33" s="224"/>
-    </row>
-    <row r="35" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="36" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C36" s="205" t="s">
+      <c r="D33" s="19"/>
+      <c r="J33" s="163"/>
+    </row>
+    <row r="34" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C34" s="308" t="s">
+        <v>274</v>
+      </c>
+      <c r="D34" s="309"/>
+      <c r="E34" s="309"/>
+      <c r="F34" s="309"/>
+      <c r="G34" s="309"/>
+      <c r="H34" s="309"/>
+      <c r="I34" s="309"/>
+      <c r="J34" s="310"/>
+    </row>
+    <row r="35" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C35" s="311"/>
+      <c r="D35" s="312"/>
+      <c r="E35" s="312"/>
+      <c r="F35" s="312"/>
+      <c r="G35" s="312"/>
+      <c r="H35" s="312"/>
+      <c r="I35" s="312"/>
+      <c r="J35" s="313"/>
+    </row>
+    <row r="37" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="38" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C38" s="236" t="s">
         <v>189</v>
       </c>
-      <c r="D36" s="206">
-        <v>1</v>
-      </c>
-      <c r="E36" s="161"/>
-      <c r="F36" s="161"/>
-      <c r="G36" s="161"/>
-      <c r="H36" s="161"/>
-      <c r="I36" s="161"/>
-      <c r="J36" s="162"/>
-    </row>
-    <row r="37" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C37" s="207" t="s">
+      <c r="D38" s="237">
+        <f>D30+1</f>
+        <v>4</v>
+      </c>
+      <c r="E38" s="161"/>
+      <c r="F38" s="161"/>
+      <c r="G38" s="161"/>
+      <c r="H38" s="161"/>
+      <c r="I38" s="161"/>
+      <c r="J38" s="162"/>
+    </row>
+    <row r="39" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C39" s="238" t="s">
         <v>190</v>
       </c>
-      <c r="D37" s="208"/>
-      <c r="E37" t="s">
+      <c r="D39" s="239"/>
+      <c r="E39" t="s">
         <v>191</v>
       </c>
-      <c r="G37" t="s">
+      <c r="G39" t="s">
         <v>192</v>
       </c>
-      <c r="J37" s="163"/>
-      <c r="K37" s="224"/>
-      <c r="L37" s="224"/>
-      <c r="M37" s="224"/>
-      <c r="N37" s="224"/>
-    </row>
-    <row r="38" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C38" s="207" t="s">
+      <c r="J39" s="163"/>
+    </row>
+    <row r="40" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C40" s="238" t="s">
         <v>193</v>
       </c>
-      <c r="D38" s="208" t="s">
+      <c r="D40" s="239" t="s">
         <v>194</v>
       </c>
-      <c r="E38" t="s">
+      <c r="E40" t="s">
         <v>195</v>
       </c>
-      <c r="G38" t="s">
+      <c r="G40" t="s">
         <v>128</v>
       </c>
-      <c r="H38">
-        <v>74</v>
-      </c>
-      <c r="J38" s="163"/>
-      <c r="K38" s="224"/>
-      <c r="L38" s="224"/>
-      <c r="M38" s="224"/>
-      <c r="N38" s="224"/>
-    </row>
-    <row r="39" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C39" s="207" t="s">
+      <c r="H40" t="s">
+        <v>275</v>
+      </c>
+      <c r="J40" s="163"/>
+    </row>
+    <row r="41" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C41" s="235" t="s">
         <v>196</v>
       </c>
-      <c r="D39" s="208"/>
-      <c r="J39" s="163"/>
-      <c r="K39" s="224"/>
-      <c r="L39" s="224"/>
-      <c r="M39" s="224"/>
-      <c r="N39" s="224"/>
-    </row>
-    <row r="40" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C40" s="285" t="s">
-        <v>227</v>
-      </c>
-      <c r="D40" s="286"/>
-      <c r="E40" s="286"/>
-      <c r="F40" s="286"/>
-      <c r="G40" s="286"/>
-      <c r="H40" s="286"/>
-      <c r="I40" s="286"/>
-      <c r="J40" s="287"/>
-      <c r="K40" s="224"/>
-      <c r="L40" s="224"/>
-      <c r="M40" s="224"/>
-      <c r="N40" s="224"/>
-    </row>
-    <row r="41" spans="3:14" ht="24.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="288"/>
-      <c r="D41" s="289"/>
-      <c r="E41" s="289"/>
-      <c r="F41" s="289"/>
-      <c r="G41" s="289"/>
-      <c r="H41" s="289"/>
-      <c r="I41" s="289"/>
-      <c r="J41" s="290"/>
-      <c r="K41" s="224"/>
-      <c r="L41" s="224"/>
-      <c r="M41" s="224"/>
-      <c r="N41" s="224"/>
-    </row>
-    <row r="43" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="44" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C44" s="213" t="s">
+      <c r="D41" s="19"/>
+      <c r="J41" s="163"/>
+    </row>
+    <row r="42" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C42" s="308" t="s">
+        <v>276</v>
+      </c>
+      <c r="D42" s="309"/>
+      <c r="E42" s="309"/>
+      <c r="F42" s="309"/>
+      <c r="G42" s="309"/>
+      <c r="H42" s="309"/>
+      <c r="I42" s="309"/>
+      <c r="J42" s="310"/>
+    </row>
+    <row r="43" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C43" s="311"/>
+      <c r="D43" s="312"/>
+      <c r="E43" s="312"/>
+      <c r="F43" s="312"/>
+      <c r="G43" s="312"/>
+      <c r="H43" s="312"/>
+      <c r="I43" s="312"/>
+      <c r="J43" s="313"/>
+    </row>
+    <row r="45" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="46" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C46" s="316" t="s">
         <v>189</v>
       </c>
-      <c r="D44" s="214">
-        <v>1</v>
-      </c>
-      <c r="E44" s="161"/>
-      <c r="F44" s="161"/>
-      <c r="G44" s="161"/>
-      <c r="H44" s="161"/>
-      <c r="I44" s="161"/>
-      <c r="J44" s="162"/>
-      <c r="K44" s="224"/>
-      <c r="L44" s="224"/>
-      <c r="M44" s="224"/>
-    </row>
-    <row r="45" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C45" s="215" t="s">
+      <c r="D46" s="317">
+        <f>D38+1</f>
+        <v>5</v>
+      </c>
+      <c r="E46" s="161"/>
+      <c r="F46" s="161"/>
+      <c r="G46" s="161"/>
+      <c r="H46" s="161"/>
+      <c r="I46" s="161"/>
+      <c r="J46" s="162"/>
+    </row>
+    <row r="47" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C47" s="318" t="s">
         <v>190</v>
       </c>
-      <c r="D45" s="216"/>
-      <c r="E45" t="s">
+      <c r="D47" s="319"/>
+      <c r="E47" t="s">
         <v>191</v>
       </c>
-      <c r="G45" t="s">
+      <c r="G47" t="s">
         <v>192</v>
       </c>
-      <c r="J45" s="163"/>
-      <c r="K45" s="224"/>
-      <c r="L45" s="224"/>
-      <c r="M45" s="224"/>
-    </row>
-    <row r="46" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C46" s="215" t="s">
+      <c r="J47" s="163"/>
+    </row>
+    <row r="48" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C48" s="318" t="s">
         <v>193</v>
       </c>
-      <c r="D46" s="216" t="s">
+      <c r="D48" s="319" t="s">
         <v>194</v>
       </c>
-      <c r="E46" t="s">
+      <c r="E48" t="s">
         <v>195</v>
       </c>
-      <c r="G46" t="s">
+      <c r="G48" t="s">
         <v>128</v>
       </c>
-      <c r="H46" t="s">
-        <v>229</v>
-      </c>
-      <c r="J46" s="163"/>
-      <c r="K46" s="224"/>
-      <c r="L46" s="224"/>
-      <c r="M46" s="224"/>
-    </row>
-    <row r="47" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C47" s="215" t="s">
+      <c r="H48" t="s">
+        <v>279</v>
+      </c>
+      <c r="J48" s="163"/>
+    </row>
+    <row r="49" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C49" s="318" t="s">
         <v>196</v>
       </c>
-      <c r="D47" s="216"/>
-      <c r="J47" s="163"/>
-      <c r="K47" s="224"/>
-      <c r="L47" s="224"/>
-      <c r="M47" s="224"/>
-    </row>
-    <row r="48" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C48" s="285" t="s">
-        <v>230</v>
-      </c>
-      <c r="D48" s="286"/>
-      <c r="E48" s="286"/>
-      <c r="F48" s="286"/>
-      <c r="G48" s="286"/>
-      <c r="H48" s="286"/>
-      <c r="I48" s="286"/>
-      <c r="J48" s="287"/>
-      <c r="K48" s="224"/>
-      <c r="L48" s="224"/>
-      <c r="M48" s="224"/>
-    </row>
-    <row r="49" spans="3:13" ht="29.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C49" s="288"/>
-      <c r="D49" s="289"/>
-      <c r="E49" s="289"/>
-      <c r="F49" s="289"/>
-      <c r="G49" s="289"/>
-      <c r="H49" s="289"/>
-      <c r="I49" s="289"/>
-      <c r="J49" s="290"/>
-      <c r="K49" s="224"/>
-      <c r="L49" s="224"/>
-      <c r="M49" s="224"/>
-    </row>
-    <row r="51" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="K51" s="224"/>
-      <c r="L51" s="224"/>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C52" s="217" t="s">
-        <v>189</v>
-      </c>
-      <c r="D52" s="218">
-        <v>1</v>
-      </c>
-      <c r="E52" s="161"/>
-      <c r="F52" s="161"/>
-      <c r="G52" s="161"/>
-      <c r="H52" s="161"/>
-      <c r="I52" s="161"/>
-      <c r="J52" s="162"/>
-      <c r="K52" s="224"/>
-      <c r="L52" s="224"/>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C53" s="219" t="s">
-        <v>190</v>
-      </c>
-      <c r="D53" s="220"/>
-      <c r="E53" t="s">
-        <v>191</v>
-      </c>
-      <c r="G53" t="s">
-        <v>192</v>
-      </c>
-      <c r="J53" s="163"/>
-      <c r="K53" s="224"/>
-      <c r="L53" s="224"/>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C54" s="219" t="s">
-        <v>193</v>
-      </c>
-      <c r="D54" s="220" t="s">
-        <v>194</v>
-      </c>
-      <c r="E54" t="s">
-        <v>195</v>
-      </c>
-      <c r="G54" t="s">
-        <v>128</v>
-      </c>
-      <c r="H54" t="s">
-        <v>231</v>
-      </c>
-      <c r="J54" s="163"/>
-      <c r="K54" s="224"/>
-      <c r="L54" s="224"/>
-    </row>
-    <row r="55" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C55" s="219" t="s">
-        <v>196</v>
-      </c>
-      <c r="D55" s="220"/>
-      <c r="J55" s="163"/>
-      <c r="K55" s="224"/>
-      <c r="L55" s="224"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C56" s="285" t="s">
-        <v>232</v>
-      </c>
-      <c r="D56" s="286"/>
-      <c r="E56" s="286"/>
-      <c r="F56" s="286"/>
-      <c r="G56" s="286"/>
-      <c r="H56" s="286"/>
-      <c r="I56" s="286"/>
-      <c r="J56" s="287"/>
-      <c r="K56" s="224"/>
-      <c r="L56" s="224"/>
-    </row>
-    <row r="57" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C57" s="288"/>
-      <c r="D57" s="289"/>
-      <c r="E57" s="289"/>
-      <c r="F57" s="289"/>
-      <c r="G57" s="289"/>
-      <c r="H57" s="289"/>
-      <c r="I57" s="289"/>
-      <c r="J57" s="290"/>
-    </row>
-    <row r="59" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C60" s="221" t="s">
-        <v>189</v>
-      </c>
-      <c r="D60" s="222">
-        <v>1</v>
-      </c>
-      <c r="E60" s="161"/>
-      <c r="F60" s="161"/>
-      <c r="G60" s="161"/>
-      <c r="H60" s="161"/>
-      <c r="I60" s="161"/>
-      <c r="J60" s="162"/>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C61" s="223" t="s">
-        <v>190</v>
-      </c>
-      <c r="D61" s="224"/>
-      <c r="E61" t="s">
-        <v>191</v>
-      </c>
-      <c r="G61" t="s">
-        <v>192</v>
-      </c>
-      <c r="J61" s="163"/>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C62" s="223" t="s">
-        <v>193</v>
-      </c>
-      <c r="D62" s="224" t="s">
-        <v>194</v>
-      </c>
-      <c r="E62" t="s">
-        <v>195</v>
-      </c>
-      <c r="G62" t="s">
-        <v>128</v>
-      </c>
-      <c r="H62" t="s">
-        <v>234</v>
-      </c>
-      <c r="J62" s="163"/>
-    </row>
-    <row r="63" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C63" s="223" t="s">
-        <v>196</v>
-      </c>
-      <c r="D63" s="224"/>
-      <c r="J63" s="163"/>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C64" s="285" t="s">
-        <v>233</v>
-      </c>
-      <c r="D64" s="286"/>
-      <c r="E64" s="286"/>
-      <c r="F64" s="286"/>
-      <c r="G64" s="286"/>
-      <c r="H64" s="286"/>
-      <c r="I64" s="286"/>
-      <c r="J64" s="287"/>
-    </row>
-    <row r="65" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C65" s="288"/>
-      <c r="D65" s="289"/>
-      <c r="E65" s="289"/>
-      <c r="F65" s="289"/>
-      <c r="G65" s="289"/>
-      <c r="H65" s="289"/>
-      <c r="I65" s="289"/>
-      <c r="J65" s="290"/>
+      <c r="D49" s="319"/>
+      <c r="J49" s="163"/>
+    </row>
+    <row r="50" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C50" s="308" t="s">
+        <v>280</v>
+      </c>
+      <c r="D50" s="309"/>
+      <c r="E50" s="309"/>
+      <c r="F50" s="309"/>
+      <c r="G50" s="309"/>
+      <c r="H50" s="309"/>
+      <c r="I50" s="309"/>
+      <c r="J50" s="310"/>
+    </row>
+    <row r="51" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C51" s="311"/>
+      <c r="D51" s="312"/>
+      <c r="E51" s="312"/>
+      <c r="F51" s="312"/>
+      <c r="G51" s="312"/>
+      <c r="H51" s="312"/>
+      <c r="I51" s="312"/>
+      <c r="J51" s="313"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="C48:J49"/>
-    <mergeCell ref="C56:J57"/>
-    <mergeCell ref="C64:J65"/>
+  <mergeCells count="6">
+    <mergeCell ref="C50:J51"/>
     <mergeCell ref="C8:J9"/>
+    <mergeCell ref="C26:J27"/>
+    <mergeCell ref="C34:J35"/>
+    <mergeCell ref="C42:J43"/>
     <mergeCell ref="C16:J17"/>
-    <mergeCell ref="C24:J25"/>
-    <mergeCell ref="C32:J33"/>
-    <mergeCell ref="C40:J41"/>
   </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="C16" r:id="rId1" xr:uid="{B42D2017-051D-4825-8324-9401A9A4F856}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>